--- a/regularite_history.xlsx
+++ b/regularite_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y223"/>
+  <dimension ref="A1:Y232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18081,6 +18081,717 @@
         <v>11</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:11:59</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="C224" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D224" t="n">
+        <v>368</v>
+      </c>
+      <c r="E224" t="n">
+        <v>314</v>
+      </c>
+      <c r="F224" t="n">
+        <v>63</v>
+      </c>
+      <c r="G224" t="n">
+        <v>47</v>
+      </c>
+      <c r="H224" t="n">
+        <v>81</v>
+      </c>
+      <c r="I224" t="n">
+        <v>137</v>
+      </c>
+      <c r="J224" t="n">
+        <v>120</v>
+      </c>
+      <c r="K224" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L224" t="n">
+        <v>45</v>
+      </c>
+      <c r="M224" t="n">
+        <v>36</v>
+      </c>
+      <c r="N224" t="n">
+        <v>73.67</v>
+      </c>
+      <c r="O224" t="n">
+        <v>205</v>
+      </c>
+      <c r="P224" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R224" t="n">
+        <v>42</v>
+      </c>
+      <c r="S224" t="n">
+        <v>29</v>
+      </c>
+      <c r="T224" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U224" t="n">
+        <v>12</v>
+      </c>
+      <c r="V224" t="n">
+        <v>8</v>
+      </c>
+      <c r="W224" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X224" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:14:00</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="C225" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D225" t="n">
+        <v>366</v>
+      </c>
+      <c r="E225" t="n">
+        <v>314</v>
+      </c>
+      <c r="F225" t="n">
+        <v>63</v>
+      </c>
+      <c r="G225" t="n">
+        <v>47</v>
+      </c>
+      <c r="H225" t="n">
+        <v>81</v>
+      </c>
+      <c r="I225" t="n">
+        <v>137</v>
+      </c>
+      <c r="J225" t="n">
+        <v>120</v>
+      </c>
+      <c r="K225" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L225" t="n">
+        <v>45</v>
+      </c>
+      <c r="M225" t="n">
+        <v>36</v>
+      </c>
+      <c r="N225" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="O225" t="n">
+        <v>203</v>
+      </c>
+      <c r="P225" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R225" t="n">
+        <v>42</v>
+      </c>
+      <c r="S225" t="n">
+        <v>29</v>
+      </c>
+      <c r="T225" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U225" t="n">
+        <v>12</v>
+      </c>
+      <c r="V225" t="n">
+        <v>8</v>
+      </c>
+      <c r="W225" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X225" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:16:01</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="C226" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D226" t="n">
+        <v>366</v>
+      </c>
+      <c r="E226" t="n">
+        <v>314</v>
+      </c>
+      <c r="F226" t="n">
+        <v>63</v>
+      </c>
+      <c r="G226" t="n">
+        <v>47</v>
+      </c>
+      <c r="H226" t="n">
+        <v>81</v>
+      </c>
+      <c r="I226" t="n">
+        <v>137</v>
+      </c>
+      <c r="J226" t="n">
+        <v>120</v>
+      </c>
+      <c r="K226" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L226" t="n">
+        <v>45</v>
+      </c>
+      <c r="M226" t="n">
+        <v>36</v>
+      </c>
+      <c r="N226" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="O226" t="n">
+        <v>203</v>
+      </c>
+      <c r="P226" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R226" t="n">
+        <v>42</v>
+      </c>
+      <c r="S226" t="n">
+        <v>29</v>
+      </c>
+      <c r="T226" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U226" t="n">
+        <v>12</v>
+      </c>
+      <c r="V226" t="n">
+        <v>8</v>
+      </c>
+      <c r="W226" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X226" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:17:59</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="C227" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D227" t="n">
+        <v>366</v>
+      </c>
+      <c r="E227" t="n">
+        <v>314</v>
+      </c>
+      <c r="F227" t="n">
+        <v>63</v>
+      </c>
+      <c r="G227" t="n">
+        <v>47</v>
+      </c>
+      <c r="H227" t="n">
+        <v>81</v>
+      </c>
+      <c r="I227" t="n">
+        <v>137</v>
+      </c>
+      <c r="J227" t="n">
+        <v>120</v>
+      </c>
+      <c r="K227" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L227" t="n">
+        <v>45</v>
+      </c>
+      <c r="M227" t="n">
+        <v>36</v>
+      </c>
+      <c r="N227" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="O227" t="n">
+        <v>203</v>
+      </c>
+      <c r="P227" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R227" t="n">
+        <v>42</v>
+      </c>
+      <c r="S227" t="n">
+        <v>29</v>
+      </c>
+      <c r="T227" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U227" t="n">
+        <v>12</v>
+      </c>
+      <c r="V227" t="n">
+        <v>8</v>
+      </c>
+      <c r="W227" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X227" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:20:00</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="C228" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D228" t="n">
+        <v>368</v>
+      </c>
+      <c r="E228" t="n">
+        <v>316</v>
+      </c>
+      <c r="F228" t="n">
+        <v>63</v>
+      </c>
+      <c r="G228" t="n">
+        <v>47</v>
+      </c>
+      <c r="H228" t="n">
+        <v>81</v>
+      </c>
+      <c r="I228" t="n">
+        <v>138</v>
+      </c>
+      <c r="J228" t="n">
+        <v>121</v>
+      </c>
+      <c r="K228" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L228" t="n">
+        <v>46</v>
+      </c>
+      <c r="M228" t="n">
+        <v>37</v>
+      </c>
+      <c r="N228" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="O228" t="n">
+        <v>204</v>
+      </c>
+      <c r="P228" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R228" t="n">
+        <v>42</v>
+      </c>
+      <c r="S228" t="n">
+        <v>29</v>
+      </c>
+      <c r="T228" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U228" t="n">
+        <v>12</v>
+      </c>
+      <c r="V228" t="n">
+        <v>8</v>
+      </c>
+      <c r="W228" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X228" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:21:59</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="C229" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D229" t="n">
+        <v>368</v>
+      </c>
+      <c r="E229" t="n">
+        <v>316</v>
+      </c>
+      <c r="F229" t="n">
+        <v>63</v>
+      </c>
+      <c r="G229" t="n">
+        <v>47</v>
+      </c>
+      <c r="H229" t="n">
+        <v>81</v>
+      </c>
+      <c r="I229" t="n">
+        <v>138</v>
+      </c>
+      <c r="J229" t="n">
+        <v>121</v>
+      </c>
+      <c r="K229" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L229" t="n">
+        <v>46</v>
+      </c>
+      <c r="M229" t="n">
+        <v>37</v>
+      </c>
+      <c r="N229" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="O229" t="n">
+        <v>204</v>
+      </c>
+      <c r="P229" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R229" t="n">
+        <v>42</v>
+      </c>
+      <c r="S229" t="n">
+        <v>29</v>
+      </c>
+      <c r="T229" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U229" t="n">
+        <v>12</v>
+      </c>
+      <c r="V229" t="n">
+        <v>8</v>
+      </c>
+      <c r="W229" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X229" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:23:59</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="C230" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D230" t="n">
+        <v>369</v>
+      </c>
+      <c r="E230" t="n">
+        <v>317</v>
+      </c>
+      <c r="F230" t="n">
+        <v>63</v>
+      </c>
+      <c r="G230" t="n">
+        <v>47</v>
+      </c>
+      <c r="H230" t="n">
+        <v>81</v>
+      </c>
+      <c r="I230" t="n">
+        <v>138</v>
+      </c>
+      <c r="J230" t="n">
+        <v>121</v>
+      </c>
+      <c r="K230" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L230" t="n">
+        <v>46</v>
+      </c>
+      <c r="M230" t="n">
+        <v>37</v>
+      </c>
+      <c r="N230" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="O230" t="n">
+        <v>205</v>
+      </c>
+      <c r="P230" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R230" t="n">
+        <v>42</v>
+      </c>
+      <c r="S230" t="n">
+        <v>29</v>
+      </c>
+      <c r="T230" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U230" t="n">
+        <v>12</v>
+      </c>
+      <c r="V230" t="n">
+        <v>8</v>
+      </c>
+      <c r="W230" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X230" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:25:59</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="C231" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D231" t="n">
+        <v>370</v>
+      </c>
+      <c r="E231" t="n">
+        <v>318</v>
+      </c>
+      <c r="F231" t="n">
+        <v>63</v>
+      </c>
+      <c r="G231" t="n">
+        <v>47</v>
+      </c>
+      <c r="H231" t="n">
+        <v>81</v>
+      </c>
+      <c r="I231" t="n">
+        <v>139</v>
+      </c>
+      <c r="J231" t="n">
+        <v>122</v>
+      </c>
+      <c r="K231" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L231" t="n">
+        <v>46</v>
+      </c>
+      <c r="M231" t="n">
+        <v>37</v>
+      </c>
+      <c r="N231" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="O231" t="n">
+        <v>205</v>
+      </c>
+      <c r="P231" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R231" t="n">
+        <v>42</v>
+      </c>
+      <c r="S231" t="n">
+        <v>29</v>
+      </c>
+      <c r="T231" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U231" t="n">
+        <v>12</v>
+      </c>
+      <c r="V231" t="n">
+        <v>8</v>
+      </c>
+      <c r="W231" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X231" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:28:05</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="C232" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D232" t="n">
+        <v>372</v>
+      </c>
+      <c r="E232" t="n">
+        <v>318</v>
+      </c>
+      <c r="F232" t="n">
+        <v>63</v>
+      </c>
+      <c r="G232" t="n">
+        <v>47</v>
+      </c>
+      <c r="H232" t="n">
+        <v>81</v>
+      </c>
+      <c r="I232" t="n">
+        <v>139</v>
+      </c>
+      <c r="J232" t="n">
+        <v>122</v>
+      </c>
+      <c r="K232" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L232" t="n">
+        <v>46</v>
+      </c>
+      <c r="M232" t="n">
+        <v>37</v>
+      </c>
+      <c r="N232" t="n">
+        <v>74.02</v>
+      </c>
+      <c r="O232" t="n">
+        <v>207</v>
+      </c>
+      <c r="P232" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R232" t="n">
+        <v>42</v>
+      </c>
+      <c r="S232" t="n">
+        <v>29</v>
+      </c>
+      <c r="T232" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U232" t="n">
+        <v>12</v>
+      </c>
+      <c r="V232" t="n">
+        <v>8</v>
+      </c>
+      <c r="W232" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X232" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/regularite_history.xlsx
+++ b/regularite_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y232"/>
+  <dimension ref="A1:Y295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18792,6 +18792,4983 @@
         <v>11</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:30:08</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="C233" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="D233" t="n">
+        <v>374</v>
+      </c>
+      <c r="E233" t="n">
+        <v>320</v>
+      </c>
+      <c r="F233" t="n">
+        <v>63</v>
+      </c>
+      <c r="G233" t="n">
+        <v>47</v>
+      </c>
+      <c r="H233" t="n">
+        <v>81</v>
+      </c>
+      <c r="I233" t="n">
+        <v>139</v>
+      </c>
+      <c r="J233" t="n">
+        <v>122</v>
+      </c>
+      <c r="K233" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L233" t="n">
+        <v>46</v>
+      </c>
+      <c r="M233" t="n">
+        <v>37</v>
+      </c>
+      <c r="N233" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="O233" t="n">
+        <v>209</v>
+      </c>
+      <c r="P233" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="R233" t="n">
+        <v>42</v>
+      </c>
+      <c r="S233" t="n">
+        <v>29</v>
+      </c>
+      <c r="T233" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U233" t="n">
+        <v>12</v>
+      </c>
+      <c r="V233" t="n">
+        <v>8</v>
+      </c>
+      <c r="W233" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X233" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:32:06</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C234" t="n">
+        <v>79.20999999999999</v>
+      </c>
+      <c r="D234" t="n">
+        <v>376</v>
+      </c>
+      <c r="E234" t="n">
+        <v>321</v>
+      </c>
+      <c r="F234" t="n">
+        <v>64</v>
+      </c>
+      <c r="G234" t="n">
+        <v>47</v>
+      </c>
+      <c r="H234" t="n">
+        <v>80.01000000000001</v>
+      </c>
+      <c r="I234" t="n">
+        <v>141</v>
+      </c>
+      <c r="J234" t="n">
+        <v>123</v>
+      </c>
+      <c r="K234" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L234" t="n">
+        <v>46</v>
+      </c>
+      <c r="M234" t="n">
+        <v>37</v>
+      </c>
+      <c r="N234" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="O234" t="n">
+        <v>209</v>
+      </c>
+      <c r="P234" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="R234" t="n">
+        <v>43</v>
+      </c>
+      <c r="S234" t="n">
+        <v>29</v>
+      </c>
+      <c r="T234" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U234" t="n">
+        <v>12</v>
+      </c>
+      <c r="V234" t="n">
+        <v>8</v>
+      </c>
+      <c r="W234" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X234" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:34:09</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="C235" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="D235" t="n">
+        <v>377</v>
+      </c>
+      <c r="E235" t="n">
+        <v>322</v>
+      </c>
+      <c r="F235" t="n">
+        <v>65</v>
+      </c>
+      <c r="G235" t="n">
+        <v>48</v>
+      </c>
+      <c r="H235" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="I235" t="n">
+        <v>142</v>
+      </c>
+      <c r="J235" t="n">
+        <v>124</v>
+      </c>
+      <c r="K235" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="L235" t="n">
+        <v>46</v>
+      </c>
+      <c r="M235" t="n">
+        <v>37</v>
+      </c>
+      <c r="N235" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="O235" t="n">
+        <v>209</v>
+      </c>
+      <c r="P235" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="R235" t="n">
+        <v>44</v>
+      </c>
+      <c r="S235" t="n">
+        <v>30</v>
+      </c>
+      <c r="T235" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U235" t="n">
+        <v>12</v>
+      </c>
+      <c r="V235" t="n">
+        <v>8</v>
+      </c>
+      <c r="W235" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X235" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:35:22</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="C236" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="D236" t="n">
+        <v>377</v>
+      </c>
+      <c r="E236" t="n">
+        <v>323</v>
+      </c>
+      <c r="F236" t="n">
+        <v>65</v>
+      </c>
+      <c r="G236" t="n">
+        <v>48</v>
+      </c>
+      <c r="H236" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="I236" t="n">
+        <v>142</v>
+      </c>
+      <c r="J236" t="n">
+        <v>124</v>
+      </c>
+      <c r="K236" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="L236" t="n">
+        <v>46</v>
+      </c>
+      <c r="M236" t="n">
+        <v>38</v>
+      </c>
+      <c r="N236" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="O236" t="n">
+        <v>209</v>
+      </c>
+      <c r="P236" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="R236" t="n">
+        <v>44</v>
+      </c>
+      <c r="S236" t="n">
+        <v>30</v>
+      </c>
+      <c r="T236" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U236" t="n">
+        <v>12</v>
+      </c>
+      <c r="V236" t="n">
+        <v>8</v>
+      </c>
+      <c r="W236" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X236" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:37:23</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="C237" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="D237" t="n">
+        <v>377</v>
+      </c>
+      <c r="E237" t="n">
+        <v>323</v>
+      </c>
+      <c r="F237" t="n">
+        <v>65</v>
+      </c>
+      <c r="G237" t="n">
+        <v>48</v>
+      </c>
+      <c r="H237" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="I237" t="n">
+        <v>142</v>
+      </c>
+      <c r="J237" t="n">
+        <v>124</v>
+      </c>
+      <c r="K237" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="L237" t="n">
+        <v>46</v>
+      </c>
+      <c r="M237" t="n">
+        <v>38</v>
+      </c>
+      <c r="N237" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="O237" t="n">
+        <v>209</v>
+      </c>
+      <c r="P237" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="R237" t="n">
+        <v>44</v>
+      </c>
+      <c r="S237" t="n">
+        <v>30</v>
+      </c>
+      <c r="T237" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U237" t="n">
+        <v>12</v>
+      </c>
+      <c r="V237" t="n">
+        <v>8</v>
+      </c>
+      <c r="W237" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X237" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:39:24</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="C238" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="D238" t="n">
+        <v>377</v>
+      </c>
+      <c r="E238" t="n">
+        <v>323</v>
+      </c>
+      <c r="F238" t="n">
+        <v>65</v>
+      </c>
+      <c r="G238" t="n">
+        <v>48</v>
+      </c>
+      <c r="H238" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="I238" t="n">
+        <v>142</v>
+      </c>
+      <c r="J238" t="n">
+        <v>124</v>
+      </c>
+      <c r="K238" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="L238" t="n">
+        <v>46</v>
+      </c>
+      <c r="M238" t="n">
+        <v>38</v>
+      </c>
+      <c r="N238" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="O238" t="n">
+        <v>209</v>
+      </c>
+      <c r="P238" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="R238" t="n">
+        <v>44</v>
+      </c>
+      <c r="S238" t="n">
+        <v>30</v>
+      </c>
+      <c r="T238" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="U238" t="n">
+        <v>12</v>
+      </c>
+      <c r="V238" t="n">
+        <v>8</v>
+      </c>
+      <c r="W238" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="X238" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:19:19</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="C239" t="n">
+        <v>100</v>
+      </c>
+      <c r="D239" t="n">
+        <v>112</v>
+      </c>
+      <c r="E239" t="n">
+        <v>106</v>
+      </c>
+      <c r="F239" t="n">
+        <v>12</v>
+      </c>
+      <c r="G239" t="n">
+        <v>12</v>
+      </c>
+      <c r="H239" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="I239" t="n">
+        <v>47</v>
+      </c>
+      <c r="J239" t="n">
+        <v>44</v>
+      </c>
+      <c r="K239" t="n">
+        <v>100</v>
+      </c>
+      <c r="L239" t="n">
+        <v>19</v>
+      </c>
+      <c r="M239" t="n">
+        <v>16</v>
+      </c>
+      <c r="N239" t="n">
+        <v>100</v>
+      </c>
+      <c r="O239" t="n">
+        <v>52</v>
+      </c>
+      <c r="P239" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>100</v>
+      </c>
+      <c r="R239" t="n">
+        <v>9</v>
+      </c>
+      <c r="S239" t="n">
+        <v>9</v>
+      </c>
+      <c r="T239" t="n">
+        <v>100</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0</v>
+      </c>
+      <c r="V239" t="n">
+        <v>0</v>
+      </c>
+      <c r="W239" t="n">
+        <v>100</v>
+      </c>
+      <c r="X239" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:21:23</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="C240" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="D240" t="n">
+        <v>114</v>
+      </c>
+      <c r="E240" t="n">
+        <v>107</v>
+      </c>
+      <c r="F240" t="n">
+        <v>13</v>
+      </c>
+      <c r="G240" t="n">
+        <v>12</v>
+      </c>
+      <c r="H240" t="n">
+        <v>85.55</v>
+      </c>
+      <c r="I240" t="n">
+        <v>49</v>
+      </c>
+      <c r="J240" t="n">
+        <v>45</v>
+      </c>
+      <c r="K240" t="n">
+        <v>100</v>
+      </c>
+      <c r="L240" t="n">
+        <v>19</v>
+      </c>
+      <c r="M240" t="n">
+        <v>16</v>
+      </c>
+      <c r="N240" t="n">
+        <v>100</v>
+      </c>
+      <c r="O240" t="n">
+        <v>52</v>
+      </c>
+      <c r="P240" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="R240" t="n">
+        <v>10</v>
+      </c>
+      <c r="S240" t="n">
+        <v>9</v>
+      </c>
+      <c r="T240" t="n">
+        <v>100</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" t="n">
+        <v>0</v>
+      </c>
+      <c r="W240" t="n">
+        <v>100</v>
+      </c>
+      <c r="X240" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:23:21</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="C241" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="D241" t="n">
+        <v>116</v>
+      </c>
+      <c r="E241" t="n">
+        <v>108</v>
+      </c>
+      <c r="F241" t="n">
+        <v>13</v>
+      </c>
+      <c r="G241" t="n">
+        <v>12</v>
+      </c>
+      <c r="H241" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="I241" t="n">
+        <v>50</v>
+      </c>
+      <c r="J241" t="n">
+        <v>45</v>
+      </c>
+      <c r="K241" t="n">
+        <v>100</v>
+      </c>
+      <c r="L241" t="n">
+        <v>19</v>
+      </c>
+      <c r="M241" t="n">
+        <v>16</v>
+      </c>
+      <c r="N241" t="n">
+        <v>100</v>
+      </c>
+      <c r="O241" t="n">
+        <v>53</v>
+      </c>
+      <c r="P241" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="R241" t="n">
+        <v>10</v>
+      </c>
+      <c r="S241" t="n">
+        <v>9</v>
+      </c>
+      <c r="T241" t="n">
+        <v>100</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" t="n">
+        <v>0</v>
+      </c>
+      <c r="W241" t="n">
+        <v>100</v>
+      </c>
+      <c r="X241" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:23:40</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="C242" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="D242" t="n">
+        <v>116</v>
+      </c>
+      <c r="E242" t="n">
+        <v>108</v>
+      </c>
+      <c r="F242" t="n">
+        <v>13</v>
+      </c>
+      <c r="G242" t="n">
+        <v>12</v>
+      </c>
+      <c r="H242" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="I242" t="n">
+        <v>50</v>
+      </c>
+      <c r="J242" t="n">
+        <v>45</v>
+      </c>
+      <c r="K242" t="n">
+        <v>100</v>
+      </c>
+      <c r="L242" t="n">
+        <v>19</v>
+      </c>
+      <c r="M242" t="n">
+        <v>16</v>
+      </c>
+      <c r="N242" t="n">
+        <v>100</v>
+      </c>
+      <c r="O242" t="n">
+        <v>53</v>
+      </c>
+      <c r="P242" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="R242" t="n">
+        <v>10</v>
+      </c>
+      <c r="S242" t="n">
+        <v>9</v>
+      </c>
+      <c r="T242" t="n">
+        <v>100</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
+      <c r="V242" t="n">
+        <v>0</v>
+      </c>
+      <c r="W242" t="n">
+        <v>100</v>
+      </c>
+      <c r="X242" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:25:44</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="C243" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="D243" t="n">
+        <v>117</v>
+      </c>
+      <c r="E243" t="n">
+        <v>109</v>
+      </c>
+      <c r="F243" t="n">
+        <v>13</v>
+      </c>
+      <c r="G243" t="n">
+        <v>12</v>
+      </c>
+      <c r="H243" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="I243" t="n">
+        <v>51</v>
+      </c>
+      <c r="J243" t="n">
+        <v>46</v>
+      </c>
+      <c r="K243" t="n">
+        <v>100</v>
+      </c>
+      <c r="L243" t="n">
+        <v>19</v>
+      </c>
+      <c r="M243" t="n">
+        <v>16</v>
+      </c>
+      <c r="N243" t="n">
+        <v>100</v>
+      </c>
+      <c r="O243" t="n">
+        <v>53</v>
+      </c>
+      <c r="P243" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="R243" t="n">
+        <v>10</v>
+      </c>
+      <c r="S243" t="n">
+        <v>9</v>
+      </c>
+      <c r="T243" t="n">
+        <v>100</v>
+      </c>
+      <c r="U243" t="n">
+        <v>0</v>
+      </c>
+      <c r="V243" t="n">
+        <v>0</v>
+      </c>
+      <c r="W243" t="n">
+        <v>100</v>
+      </c>
+      <c r="X243" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:27:44</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="C244" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="D244" t="n">
+        <v>117</v>
+      </c>
+      <c r="E244" t="n">
+        <v>109</v>
+      </c>
+      <c r="F244" t="n">
+        <v>13</v>
+      </c>
+      <c r="G244" t="n">
+        <v>12</v>
+      </c>
+      <c r="H244" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="I244" t="n">
+        <v>51</v>
+      </c>
+      <c r="J244" t="n">
+        <v>46</v>
+      </c>
+      <c r="K244" t="n">
+        <v>100</v>
+      </c>
+      <c r="L244" t="n">
+        <v>19</v>
+      </c>
+      <c r="M244" t="n">
+        <v>16</v>
+      </c>
+      <c r="N244" t="n">
+        <v>100</v>
+      </c>
+      <c r="O244" t="n">
+        <v>53</v>
+      </c>
+      <c r="P244" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="R244" t="n">
+        <v>10</v>
+      </c>
+      <c r="S244" t="n">
+        <v>9</v>
+      </c>
+      <c r="T244" t="n">
+        <v>100</v>
+      </c>
+      <c r="U244" t="n">
+        <v>0</v>
+      </c>
+      <c r="V244" t="n">
+        <v>0</v>
+      </c>
+      <c r="W244" t="n">
+        <v>100</v>
+      </c>
+      <c r="X244" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:29:41</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="C245" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="D245" t="n">
+        <v>118</v>
+      </c>
+      <c r="E245" t="n">
+        <v>110</v>
+      </c>
+      <c r="F245" t="n">
+        <v>13</v>
+      </c>
+      <c r="G245" t="n">
+        <v>12</v>
+      </c>
+      <c r="H245" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="I245" t="n">
+        <v>51</v>
+      </c>
+      <c r="J245" t="n">
+        <v>46</v>
+      </c>
+      <c r="K245" t="n">
+        <v>100</v>
+      </c>
+      <c r="L245" t="n">
+        <v>19</v>
+      </c>
+      <c r="M245" t="n">
+        <v>16</v>
+      </c>
+      <c r="N245" t="n">
+        <v>100</v>
+      </c>
+      <c r="O245" t="n">
+        <v>54</v>
+      </c>
+      <c r="P245" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="R245" t="n">
+        <v>10</v>
+      </c>
+      <c r="S245" t="n">
+        <v>9</v>
+      </c>
+      <c r="T245" t="n">
+        <v>100</v>
+      </c>
+      <c r="U245" t="n">
+        <v>0</v>
+      </c>
+      <c r="V245" t="n">
+        <v>0</v>
+      </c>
+      <c r="W245" t="n">
+        <v>100</v>
+      </c>
+      <c r="X245" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:31:43</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="C246" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="D246" t="n">
+        <v>123</v>
+      </c>
+      <c r="E246" t="n">
+        <v>114</v>
+      </c>
+      <c r="F246" t="n">
+        <v>14</v>
+      </c>
+      <c r="G246" t="n">
+        <v>13</v>
+      </c>
+      <c r="H246" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="I246" t="n">
+        <v>53</v>
+      </c>
+      <c r="J246" t="n">
+        <v>47</v>
+      </c>
+      <c r="K246" t="n">
+        <v>100</v>
+      </c>
+      <c r="L246" t="n">
+        <v>19</v>
+      </c>
+      <c r="M246" t="n">
+        <v>16</v>
+      </c>
+      <c r="N246" t="n">
+        <v>100</v>
+      </c>
+      <c r="O246" t="n">
+        <v>57</v>
+      </c>
+      <c r="P246" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="R246" t="n">
+        <v>11</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="n">
+        <v>100</v>
+      </c>
+      <c r="U246" t="n">
+        <v>0</v>
+      </c>
+      <c r="V246" t="n">
+        <v>0</v>
+      </c>
+      <c r="W246" t="n">
+        <v>100</v>
+      </c>
+      <c r="X246" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:33:41</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="C247" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="D247" t="n">
+        <v>123</v>
+      </c>
+      <c r="E247" t="n">
+        <v>114</v>
+      </c>
+      <c r="F247" t="n">
+        <v>14</v>
+      </c>
+      <c r="G247" t="n">
+        <v>13</v>
+      </c>
+      <c r="H247" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="I247" t="n">
+        <v>53</v>
+      </c>
+      <c r="J247" t="n">
+        <v>47</v>
+      </c>
+      <c r="K247" t="n">
+        <v>100</v>
+      </c>
+      <c r="L247" t="n">
+        <v>19</v>
+      </c>
+      <c r="M247" t="n">
+        <v>16</v>
+      </c>
+      <c r="N247" t="n">
+        <v>100</v>
+      </c>
+      <c r="O247" t="n">
+        <v>57</v>
+      </c>
+      <c r="P247" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="R247" t="n">
+        <v>11</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="n">
+        <v>100</v>
+      </c>
+      <c r="U247" t="n">
+        <v>0</v>
+      </c>
+      <c r="V247" t="n">
+        <v>0</v>
+      </c>
+      <c r="W247" t="n">
+        <v>100</v>
+      </c>
+      <c r="X247" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:35:42</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="C248" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="D248" t="n">
+        <v>124</v>
+      </c>
+      <c r="E248" t="n">
+        <v>115</v>
+      </c>
+      <c r="F248" t="n">
+        <v>15</v>
+      </c>
+      <c r="G248" t="n">
+        <v>14</v>
+      </c>
+      <c r="H248" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="I248" t="n">
+        <v>53</v>
+      </c>
+      <c r="J248" t="n">
+        <v>47</v>
+      </c>
+      <c r="K248" t="n">
+        <v>100</v>
+      </c>
+      <c r="L248" t="n">
+        <v>20</v>
+      </c>
+      <c r="M248" t="n">
+        <v>17</v>
+      </c>
+      <c r="N248" t="n">
+        <v>100</v>
+      </c>
+      <c r="O248" t="n">
+        <v>57</v>
+      </c>
+      <c r="P248" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="R248" t="n">
+        <v>11</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="n">
+        <v>100</v>
+      </c>
+      <c r="U248" t="n">
+        <v>1</v>
+      </c>
+      <c r="V248" t="n">
+        <v>1</v>
+      </c>
+      <c r="W248" t="n">
+        <v>100</v>
+      </c>
+      <c r="X248" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:38:06</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="C249" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="D249" t="n">
+        <v>124</v>
+      </c>
+      <c r="E249" t="n">
+        <v>115</v>
+      </c>
+      <c r="F249" t="n">
+        <v>15</v>
+      </c>
+      <c r="G249" t="n">
+        <v>14</v>
+      </c>
+      <c r="H249" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="I249" t="n">
+        <v>53</v>
+      </c>
+      <c r="J249" t="n">
+        <v>47</v>
+      </c>
+      <c r="K249" t="n">
+        <v>100</v>
+      </c>
+      <c r="L249" t="n">
+        <v>20</v>
+      </c>
+      <c r="M249" t="n">
+        <v>17</v>
+      </c>
+      <c r="N249" t="n">
+        <v>100</v>
+      </c>
+      <c r="O249" t="n">
+        <v>57</v>
+      </c>
+      <c r="P249" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="R249" t="n">
+        <v>11</v>
+      </c>
+      <c r="S249" t="n">
+        <v>10</v>
+      </c>
+      <c r="T249" t="n">
+        <v>100</v>
+      </c>
+      <c r="U249" t="n">
+        <v>1</v>
+      </c>
+      <c r="V249" t="n">
+        <v>1</v>
+      </c>
+      <c r="W249" t="n">
+        <v>100</v>
+      </c>
+      <c r="X249" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:40:05</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="C250" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="D250" t="n">
+        <v>125</v>
+      </c>
+      <c r="E250" t="n">
+        <v>116</v>
+      </c>
+      <c r="F250" t="n">
+        <v>15</v>
+      </c>
+      <c r="G250" t="n">
+        <v>14</v>
+      </c>
+      <c r="H250" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="I250" t="n">
+        <v>53</v>
+      </c>
+      <c r="J250" t="n">
+        <v>47</v>
+      </c>
+      <c r="K250" t="n">
+        <v>100</v>
+      </c>
+      <c r="L250" t="n">
+        <v>20</v>
+      </c>
+      <c r="M250" t="n">
+        <v>17</v>
+      </c>
+      <c r="N250" t="n">
+        <v>100</v>
+      </c>
+      <c r="O250" t="n">
+        <v>58</v>
+      </c>
+      <c r="P250" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="R250" t="n">
+        <v>11</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="n">
+        <v>100</v>
+      </c>
+      <c r="U250" t="n">
+        <v>1</v>
+      </c>
+      <c r="V250" t="n">
+        <v>1</v>
+      </c>
+      <c r="W250" t="n">
+        <v>100</v>
+      </c>
+      <c r="X250" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:42:06</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="C251" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="D251" t="n">
+        <v>126</v>
+      </c>
+      <c r="E251" t="n">
+        <v>117</v>
+      </c>
+      <c r="F251" t="n">
+        <v>15</v>
+      </c>
+      <c r="G251" t="n">
+        <v>14</v>
+      </c>
+      <c r="H251" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="I251" t="n">
+        <v>54</v>
+      </c>
+      <c r="J251" t="n">
+        <v>48</v>
+      </c>
+      <c r="K251" t="n">
+        <v>100</v>
+      </c>
+      <c r="L251" t="n">
+        <v>20</v>
+      </c>
+      <c r="M251" t="n">
+        <v>17</v>
+      </c>
+      <c r="N251" t="n">
+        <v>100</v>
+      </c>
+      <c r="O251" t="n">
+        <v>58</v>
+      </c>
+      <c r="P251" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="R251" t="n">
+        <v>11</v>
+      </c>
+      <c r="S251" t="n">
+        <v>10</v>
+      </c>
+      <c r="T251" t="n">
+        <v>100</v>
+      </c>
+      <c r="U251" t="n">
+        <v>1</v>
+      </c>
+      <c r="V251" t="n">
+        <v>1</v>
+      </c>
+      <c r="W251" t="n">
+        <v>100</v>
+      </c>
+      <c r="X251" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:44:06</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="C252" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>126</v>
+      </c>
+      <c r="E252" t="n">
+        <v>117</v>
+      </c>
+      <c r="F252" t="n">
+        <v>16</v>
+      </c>
+      <c r="G252" t="n">
+        <v>15</v>
+      </c>
+      <c r="H252" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="I252" t="n">
+        <v>54</v>
+      </c>
+      <c r="J252" t="n">
+        <v>48</v>
+      </c>
+      <c r="K252" t="n">
+        <v>100</v>
+      </c>
+      <c r="L252" t="n">
+        <v>20</v>
+      </c>
+      <c r="M252" t="n">
+        <v>17</v>
+      </c>
+      <c r="N252" t="n">
+        <v>100</v>
+      </c>
+      <c r="O252" t="n">
+        <v>58</v>
+      </c>
+      <c r="P252" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="R252" t="n">
+        <v>12</v>
+      </c>
+      <c r="S252" t="n">
+        <v>11</v>
+      </c>
+      <c r="T252" t="n">
+        <v>100</v>
+      </c>
+      <c r="U252" t="n">
+        <v>1</v>
+      </c>
+      <c r="V252" t="n">
+        <v>1</v>
+      </c>
+      <c r="W252" t="n">
+        <v>100</v>
+      </c>
+      <c r="X252" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:46:05</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="C253" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D253" t="n">
+        <v>126</v>
+      </c>
+      <c r="E253" t="n">
+        <v>117</v>
+      </c>
+      <c r="F253" t="n">
+        <v>16</v>
+      </c>
+      <c r="G253" t="n">
+        <v>15</v>
+      </c>
+      <c r="H253" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="I253" t="n">
+        <v>54</v>
+      </c>
+      <c r="J253" t="n">
+        <v>48</v>
+      </c>
+      <c r="K253" t="n">
+        <v>100</v>
+      </c>
+      <c r="L253" t="n">
+        <v>20</v>
+      </c>
+      <c r="M253" t="n">
+        <v>17</v>
+      </c>
+      <c r="N253" t="n">
+        <v>100</v>
+      </c>
+      <c r="O253" t="n">
+        <v>58</v>
+      </c>
+      <c r="P253" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="R253" t="n">
+        <v>12</v>
+      </c>
+      <c r="S253" t="n">
+        <v>11</v>
+      </c>
+      <c r="T253" t="n">
+        <v>100</v>
+      </c>
+      <c r="U253" t="n">
+        <v>1</v>
+      </c>
+      <c r="V253" t="n">
+        <v>1</v>
+      </c>
+      <c r="W253" t="n">
+        <v>100</v>
+      </c>
+      <c r="X253" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:47:42</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="C254" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D254" t="n">
+        <v>126</v>
+      </c>
+      <c r="E254" t="n">
+        <v>117</v>
+      </c>
+      <c r="F254" t="n">
+        <v>16</v>
+      </c>
+      <c r="G254" t="n">
+        <v>15</v>
+      </c>
+      <c r="H254" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="I254" t="n">
+        <v>54</v>
+      </c>
+      <c r="J254" t="n">
+        <v>48</v>
+      </c>
+      <c r="K254" t="n">
+        <v>100</v>
+      </c>
+      <c r="L254" t="n">
+        <v>20</v>
+      </c>
+      <c r="M254" t="n">
+        <v>17</v>
+      </c>
+      <c r="N254" t="n">
+        <v>100</v>
+      </c>
+      <c r="O254" t="n">
+        <v>58</v>
+      </c>
+      <c r="P254" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="R254" t="n">
+        <v>12</v>
+      </c>
+      <c r="S254" t="n">
+        <v>11</v>
+      </c>
+      <c r="T254" t="n">
+        <v>100</v>
+      </c>
+      <c r="U254" t="n">
+        <v>1</v>
+      </c>
+      <c r="V254" t="n">
+        <v>1</v>
+      </c>
+      <c r="W254" t="n">
+        <v>100</v>
+      </c>
+      <c r="X254" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:50:05</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="C255" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D255" t="n">
+        <v>126</v>
+      </c>
+      <c r="E255" t="n">
+        <v>117</v>
+      </c>
+      <c r="F255" t="n">
+        <v>16</v>
+      </c>
+      <c r="G255" t="n">
+        <v>15</v>
+      </c>
+      <c r="H255" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="I255" t="n">
+        <v>54</v>
+      </c>
+      <c r="J255" t="n">
+        <v>48</v>
+      </c>
+      <c r="K255" t="n">
+        <v>100</v>
+      </c>
+      <c r="L255" t="n">
+        <v>20</v>
+      </c>
+      <c r="M255" t="n">
+        <v>17</v>
+      </c>
+      <c r="N255" t="n">
+        <v>100</v>
+      </c>
+      <c r="O255" t="n">
+        <v>58</v>
+      </c>
+      <c r="P255" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="R255" t="n">
+        <v>12</v>
+      </c>
+      <c r="S255" t="n">
+        <v>11</v>
+      </c>
+      <c r="T255" t="n">
+        <v>100</v>
+      </c>
+      <c r="U255" t="n">
+        <v>1</v>
+      </c>
+      <c r="V255" t="n">
+        <v>1</v>
+      </c>
+      <c r="W255" t="n">
+        <v>100</v>
+      </c>
+      <c r="X255" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:52:06</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="C256" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D256" t="n">
+        <v>128</v>
+      </c>
+      <c r="E256" t="n">
+        <v>119</v>
+      </c>
+      <c r="F256" t="n">
+        <v>16</v>
+      </c>
+      <c r="G256" t="n">
+        <v>15</v>
+      </c>
+      <c r="H256" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="I256" t="n">
+        <v>55</v>
+      </c>
+      <c r="J256" t="n">
+        <v>49</v>
+      </c>
+      <c r="K256" t="n">
+        <v>100</v>
+      </c>
+      <c r="L256" t="n">
+        <v>20</v>
+      </c>
+      <c r="M256" t="n">
+        <v>17</v>
+      </c>
+      <c r="N256" t="n">
+        <v>100</v>
+      </c>
+      <c r="O256" t="n">
+        <v>59</v>
+      </c>
+      <c r="P256" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="R256" t="n">
+        <v>12</v>
+      </c>
+      <c r="S256" t="n">
+        <v>11</v>
+      </c>
+      <c r="T256" t="n">
+        <v>100</v>
+      </c>
+      <c r="U256" t="n">
+        <v>1</v>
+      </c>
+      <c r="V256" t="n">
+        <v>1</v>
+      </c>
+      <c r="W256" t="n">
+        <v>100</v>
+      </c>
+      <c r="X256" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:54:05</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="C257" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D257" t="n">
+        <v>130</v>
+      </c>
+      <c r="E257" t="n">
+        <v>121</v>
+      </c>
+      <c r="F257" t="n">
+        <v>16</v>
+      </c>
+      <c r="G257" t="n">
+        <v>15</v>
+      </c>
+      <c r="H257" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="I257" t="n">
+        <v>55</v>
+      </c>
+      <c r="J257" t="n">
+        <v>49</v>
+      </c>
+      <c r="K257" t="n">
+        <v>100</v>
+      </c>
+      <c r="L257" t="n">
+        <v>20</v>
+      </c>
+      <c r="M257" t="n">
+        <v>17</v>
+      </c>
+      <c r="N257" t="n">
+        <v>100</v>
+      </c>
+      <c r="O257" t="n">
+        <v>61</v>
+      </c>
+      <c r="P257" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="R257" t="n">
+        <v>12</v>
+      </c>
+      <c r="S257" t="n">
+        <v>11</v>
+      </c>
+      <c r="T257" t="n">
+        <v>100</v>
+      </c>
+      <c r="U257" t="n">
+        <v>1</v>
+      </c>
+      <c r="V257" t="n">
+        <v>1</v>
+      </c>
+      <c r="W257" t="n">
+        <v>100</v>
+      </c>
+      <c r="X257" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:55:44</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="C258" t="n">
+        <v>89.01000000000001</v>
+      </c>
+      <c r="D258" t="n">
+        <v>131</v>
+      </c>
+      <c r="E258" t="n">
+        <v>121</v>
+      </c>
+      <c r="F258" t="n">
+        <v>17</v>
+      </c>
+      <c r="G258" t="n">
+        <v>15</v>
+      </c>
+      <c r="H258" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="I258" t="n">
+        <v>56</v>
+      </c>
+      <c r="J258" t="n">
+        <v>49</v>
+      </c>
+      <c r="K258" t="n">
+        <v>100</v>
+      </c>
+      <c r="L258" t="n">
+        <v>20</v>
+      </c>
+      <c r="M258" t="n">
+        <v>17</v>
+      </c>
+      <c r="N258" t="n">
+        <v>100</v>
+      </c>
+      <c r="O258" t="n">
+        <v>61</v>
+      </c>
+      <c r="P258" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="R258" t="n">
+        <v>13</v>
+      </c>
+      <c r="S258" t="n">
+        <v>11</v>
+      </c>
+      <c r="T258" t="n">
+        <v>100</v>
+      </c>
+      <c r="U258" t="n">
+        <v>1</v>
+      </c>
+      <c r="V258" t="n">
+        <v>1</v>
+      </c>
+      <c r="W258" t="n">
+        <v>100</v>
+      </c>
+      <c r="X258" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:57:40</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="C259" t="n">
+        <v>83.95999999999999</v>
+      </c>
+      <c r="D259" t="n">
+        <v>135</v>
+      </c>
+      <c r="E259" t="n">
+        <v>124</v>
+      </c>
+      <c r="F259" t="n">
+        <v>18</v>
+      </c>
+      <c r="G259" t="n">
+        <v>15</v>
+      </c>
+      <c r="H259" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="I259" t="n">
+        <v>56</v>
+      </c>
+      <c r="J259" t="n">
+        <v>49</v>
+      </c>
+      <c r="K259" t="n">
+        <v>100</v>
+      </c>
+      <c r="L259" t="n">
+        <v>20</v>
+      </c>
+      <c r="M259" t="n">
+        <v>17</v>
+      </c>
+      <c r="N259" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="O259" t="n">
+        <v>65</v>
+      </c>
+      <c r="P259" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="R259" t="n">
+        <v>13</v>
+      </c>
+      <c r="S259" t="n">
+        <v>11</v>
+      </c>
+      <c r="T259" t="n">
+        <v>100</v>
+      </c>
+      <c r="U259" t="n">
+        <v>1</v>
+      </c>
+      <c r="V259" t="n">
+        <v>1</v>
+      </c>
+      <c r="W259" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X259" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:59:40</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="C260" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="D260" t="n">
+        <v>138</v>
+      </c>
+      <c r="E260" t="n">
+        <v>127</v>
+      </c>
+      <c r="F260" t="n">
+        <v>19</v>
+      </c>
+      <c r="G260" t="n">
+        <v>16</v>
+      </c>
+      <c r="H260" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I260" t="n">
+        <v>57</v>
+      </c>
+      <c r="J260" t="n">
+        <v>50</v>
+      </c>
+      <c r="K260" t="n">
+        <v>100</v>
+      </c>
+      <c r="L260" t="n">
+        <v>21</v>
+      </c>
+      <c r="M260" t="n">
+        <v>18</v>
+      </c>
+      <c r="N260" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="O260" t="n">
+        <v>66</v>
+      </c>
+      <c r="P260" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="R260" t="n">
+        <v>14</v>
+      </c>
+      <c r="S260" t="n">
+        <v>12</v>
+      </c>
+      <c r="T260" t="n">
+        <v>100</v>
+      </c>
+      <c r="U260" t="n">
+        <v>1</v>
+      </c>
+      <c r="V260" t="n">
+        <v>1</v>
+      </c>
+      <c r="W260" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X260" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:01:40</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="C261" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D261" t="n">
+        <v>141</v>
+      </c>
+      <c r="E261" t="n">
+        <v>130</v>
+      </c>
+      <c r="F261" t="n">
+        <v>20</v>
+      </c>
+      <c r="G261" t="n">
+        <v>17</v>
+      </c>
+      <c r="H261" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I261" t="n">
+        <v>58</v>
+      </c>
+      <c r="J261" t="n">
+        <v>51</v>
+      </c>
+      <c r="K261" t="n">
+        <v>100</v>
+      </c>
+      <c r="L261" t="n">
+        <v>22</v>
+      </c>
+      <c r="M261" t="n">
+        <v>19</v>
+      </c>
+      <c r="N261" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="O261" t="n">
+        <v>67</v>
+      </c>
+      <c r="P261" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="R261" t="n">
+        <v>14</v>
+      </c>
+      <c r="S261" t="n">
+        <v>12</v>
+      </c>
+      <c r="T261" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2</v>
+      </c>
+      <c r="V261" t="n">
+        <v>1</v>
+      </c>
+      <c r="W261" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X261" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:03:40</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="C262" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D262" t="n">
+        <v>141</v>
+      </c>
+      <c r="E262" t="n">
+        <v>130</v>
+      </c>
+      <c r="F262" t="n">
+        <v>20</v>
+      </c>
+      <c r="G262" t="n">
+        <v>17</v>
+      </c>
+      <c r="H262" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I262" t="n">
+        <v>58</v>
+      </c>
+      <c r="J262" t="n">
+        <v>51</v>
+      </c>
+      <c r="K262" t="n">
+        <v>100</v>
+      </c>
+      <c r="L262" t="n">
+        <v>22</v>
+      </c>
+      <c r="M262" t="n">
+        <v>19</v>
+      </c>
+      <c r="N262" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="O262" t="n">
+        <v>67</v>
+      </c>
+      <c r="P262" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="R262" t="n">
+        <v>14</v>
+      </c>
+      <c r="S262" t="n">
+        <v>12</v>
+      </c>
+      <c r="T262" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2</v>
+      </c>
+      <c r="V262" t="n">
+        <v>1</v>
+      </c>
+      <c r="W262" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X262" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:05:39</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="C263" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="D263" t="n">
+        <v>142</v>
+      </c>
+      <c r="E263" t="n">
+        <v>131</v>
+      </c>
+      <c r="F263" t="n">
+        <v>21</v>
+      </c>
+      <c r="G263" t="n">
+        <v>18</v>
+      </c>
+      <c r="H263" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="I263" t="n">
+        <v>59</v>
+      </c>
+      <c r="J263" t="n">
+        <v>52</v>
+      </c>
+      <c r="K263" t="n">
+        <v>100</v>
+      </c>
+      <c r="L263" t="n">
+        <v>23</v>
+      </c>
+      <c r="M263" t="n">
+        <v>20</v>
+      </c>
+      <c r="N263" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="O263" t="n">
+        <v>67</v>
+      </c>
+      <c r="P263" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="R263" t="n">
+        <v>15</v>
+      </c>
+      <c r="S263" t="n">
+        <v>13</v>
+      </c>
+      <c r="T263" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="U263" t="n">
+        <v>3</v>
+      </c>
+      <c r="V263" t="n">
+        <v>2</v>
+      </c>
+      <c r="W263" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X263" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:07:41</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="C264" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="D264" t="n">
+        <v>142</v>
+      </c>
+      <c r="E264" t="n">
+        <v>131</v>
+      </c>
+      <c r="F264" t="n">
+        <v>21</v>
+      </c>
+      <c r="G264" t="n">
+        <v>18</v>
+      </c>
+      <c r="H264" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="I264" t="n">
+        <v>59</v>
+      </c>
+      <c r="J264" t="n">
+        <v>52</v>
+      </c>
+      <c r="K264" t="n">
+        <v>100</v>
+      </c>
+      <c r="L264" t="n">
+        <v>23</v>
+      </c>
+      <c r="M264" t="n">
+        <v>20</v>
+      </c>
+      <c r="N264" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="O264" t="n">
+        <v>67</v>
+      </c>
+      <c r="P264" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="R264" t="n">
+        <v>15</v>
+      </c>
+      <c r="S264" t="n">
+        <v>13</v>
+      </c>
+      <c r="T264" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="U264" t="n">
+        <v>3</v>
+      </c>
+      <c r="V264" t="n">
+        <v>2</v>
+      </c>
+      <c r="W264" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X264" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:09:40</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="C265" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="D265" t="n">
+        <v>144</v>
+      </c>
+      <c r="E265" t="n">
+        <v>133</v>
+      </c>
+      <c r="F265" t="n">
+        <v>21</v>
+      </c>
+      <c r="G265" t="n">
+        <v>18</v>
+      </c>
+      <c r="H265" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="I265" t="n">
+        <v>61</v>
+      </c>
+      <c r="J265" t="n">
+        <v>54</v>
+      </c>
+      <c r="K265" t="n">
+        <v>100</v>
+      </c>
+      <c r="L265" t="n">
+        <v>23</v>
+      </c>
+      <c r="M265" t="n">
+        <v>20</v>
+      </c>
+      <c r="N265" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="O265" t="n">
+        <v>67</v>
+      </c>
+      <c r="P265" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="R265" t="n">
+        <v>15</v>
+      </c>
+      <c r="S265" t="n">
+        <v>13</v>
+      </c>
+      <c r="T265" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="U265" t="n">
+        <v>3</v>
+      </c>
+      <c r="V265" t="n">
+        <v>2</v>
+      </c>
+      <c r="W265" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="X265" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:11:41</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>87.67</v>
+      </c>
+      <c r="C266" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="D266" t="n">
+        <v>146</v>
+      </c>
+      <c r="E266" t="n">
+        <v>135</v>
+      </c>
+      <c r="F266" t="n">
+        <v>22</v>
+      </c>
+      <c r="G266" t="n">
+        <v>19</v>
+      </c>
+      <c r="H266" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="I266" t="n">
+        <v>62</v>
+      </c>
+      <c r="J266" t="n">
+        <v>55</v>
+      </c>
+      <c r="K266" t="n">
+        <v>100</v>
+      </c>
+      <c r="L266" t="n">
+        <v>23</v>
+      </c>
+      <c r="M266" t="n">
+        <v>20</v>
+      </c>
+      <c r="N266" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="O266" t="n">
+        <v>68</v>
+      </c>
+      <c r="P266" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="R266" t="n">
+        <v>15</v>
+      </c>
+      <c r="S266" t="n">
+        <v>13</v>
+      </c>
+      <c r="T266" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2</v>
+      </c>
+      <c r="W266" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X266" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:13:40</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>87.67</v>
+      </c>
+      <c r="C267" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="D267" t="n">
+        <v>146</v>
+      </c>
+      <c r="E267" t="n">
+        <v>135</v>
+      </c>
+      <c r="F267" t="n">
+        <v>22</v>
+      </c>
+      <c r="G267" t="n">
+        <v>19</v>
+      </c>
+      <c r="H267" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="I267" t="n">
+        <v>62</v>
+      </c>
+      <c r="J267" t="n">
+        <v>55</v>
+      </c>
+      <c r="K267" t="n">
+        <v>100</v>
+      </c>
+      <c r="L267" t="n">
+        <v>23</v>
+      </c>
+      <c r="M267" t="n">
+        <v>20</v>
+      </c>
+      <c r="N267" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="O267" t="n">
+        <v>68</v>
+      </c>
+      <c r="P267" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="R267" t="n">
+        <v>15</v>
+      </c>
+      <c r="S267" t="n">
+        <v>13</v>
+      </c>
+      <c r="T267" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="U267" t="n">
+        <v>3</v>
+      </c>
+      <c r="V267" t="n">
+        <v>2</v>
+      </c>
+      <c r="W267" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X267" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:15:40</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="C268" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="D268" t="n">
+        <v>147</v>
+      </c>
+      <c r="E268" t="n">
+        <v>135</v>
+      </c>
+      <c r="F268" t="n">
+        <v>23</v>
+      </c>
+      <c r="G268" t="n">
+        <v>20</v>
+      </c>
+      <c r="H268" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I268" t="n">
+        <v>63</v>
+      </c>
+      <c r="J268" t="n">
+        <v>55</v>
+      </c>
+      <c r="K268" t="n">
+        <v>100</v>
+      </c>
+      <c r="L268" t="n">
+        <v>23</v>
+      </c>
+      <c r="M268" t="n">
+        <v>20</v>
+      </c>
+      <c r="N268" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="O268" t="n">
+        <v>68</v>
+      </c>
+      <c r="P268" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="R268" t="n">
+        <v>16</v>
+      </c>
+      <c r="S268" t="n">
+        <v>14</v>
+      </c>
+      <c r="T268" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="U268" t="n">
+        <v>4</v>
+      </c>
+      <c r="V268" t="n">
+        <v>3</v>
+      </c>
+      <c r="W268" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X268" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:17:40</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="C269" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="D269" t="n">
+        <v>148</v>
+      </c>
+      <c r="E269" t="n">
+        <v>136</v>
+      </c>
+      <c r="F269" t="n">
+        <v>23</v>
+      </c>
+      <c r="G269" t="n">
+        <v>20</v>
+      </c>
+      <c r="H269" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I269" t="n">
+        <v>63</v>
+      </c>
+      <c r="J269" t="n">
+        <v>55</v>
+      </c>
+      <c r="K269" t="n">
+        <v>100</v>
+      </c>
+      <c r="L269" t="n">
+        <v>23</v>
+      </c>
+      <c r="M269" t="n">
+        <v>20</v>
+      </c>
+      <c r="N269" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="O269" t="n">
+        <v>69</v>
+      </c>
+      <c r="P269" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="R269" t="n">
+        <v>16</v>
+      </c>
+      <c r="S269" t="n">
+        <v>14</v>
+      </c>
+      <c r="T269" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="U269" t="n">
+        <v>4</v>
+      </c>
+      <c r="V269" t="n">
+        <v>3</v>
+      </c>
+      <c r="W269" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X269" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:19:40</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="C270" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="D270" t="n">
+        <v>150</v>
+      </c>
+      <c r="E270" t="n">
+        <v>138</v>
+      </c>
+      <c r="F270" t="n">
+        <v>23</v>
+      </c>
+      <c r="G270" t="n">
+        <v>20</v>
+      </c>
+      <c r="H270" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I270" t="n">
+        <v>63</v>
+      </c>
+      <c r="J270" t="n">
+        <v>55</v>
+      </c>
+      <c r="K270" t="n">
+        <v>100</v>
+      </c>
+      <c r="L270" t="n">
+        <v>23</v>
+      </c>
+      <c r="M270" t="n">
+        <v>20</v>
+      </c>
+      <c r="N270" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="O270" t="n">
+        <v>71</v>
+      </c>
+      <c r="P270" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="R270" t="n">
+        <v>16</v>
+      </c>
+      <c r="S270" t="n">
+        <v>14</v>
+      </c>
+      <c r="T270" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="U270" t="n">
+        <v>4</v>
+      </c>
+      <c r="V270" t="n">
+        <v>3</v>
+      </c>
+      <c r="W270" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X270" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:21:54</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C271" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="D271" t="n">
+        <v>151</v>
+      </c>
+      <c r="E271" t="n">
+        <v>139</v>
+      </c>
+      <c r="F271" t="n">
+        <v>23</v>
+      </c>
+      <c r="G271" t="n">
+        <v>20</v>
+      </c>
+      <c r="H271" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I271" t="n">
+        <v>63</v>
+      </c>
+      <c r="J271" t="n">
+        <v>55</v>
+      </c>
+      <c r="K271" t="n">
+        <v>100</v>
+      </c>
+      <c r="L271" t="n">
+        <v>23</v>
+      </c>
+      <c r="M271" t="n">
+        <v>20</v>
+      </c>
+      <c r="N271" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="O271" t="n">
+        <v>72</v>
+      </c>
+      <c r="P271" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="R271" t="n">
+        <v>16</v>
+      </c>
+      <c r="S271" t="n">
+        <v>14</v>
+      </c>
+      <c r="T271" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="U271" t="n">
+        <v>4</v>
+      </c>
+      <c r="V271" t="n">
+        <v>3</v>
+      </c>
+      <c r="W271" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X271" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:23:38</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C272" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="D272" t="n">
+        <v>151</v>
+      </c>
+      <c r="E272" t="n">
+        <v>139</v>
+      </c>
+      <c r="F272" t="n">
+        <v>23</v>
+      </c>
+      <c r="G272" t="n">
+        <v>20</v>
+      </c>
+      <c r="H272" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="I272" t="n">
+        <v>63</v>
+      </c>
+      <c r="J272" t="n">
+        <v>55</v>
+      </c>
+      <c r="K272" t="n">
+        <v>100</v>
+      </c>
+      <c r="L272" t="n">
+        <v>23</v>
+      </c>
+      <c r="M272" t="n">
+        <v>20</v>
+      </c>
+      <c r="N272" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="O272" t="n">
+        <v>72</v>
+      </c>
+      <c r="P272" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="R272" t="n">
+        <v>16</v>
+      </c>
+      <c r="S272" t="n">
+        <v>14</v>
+      </c>
+      <c r="T272" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="U272" t="n">
+        <v>4</v>
+      </c>
+      <c r="V272" t="n">
+        <v>3</v>
+      </c>
+      <c r="W272" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X272" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:26:03</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="C273" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="D273" t="n">
+        <v>152</v>
+      </c>
+      <c r="E273" t="n">
+        <v>140</v>
+      </c>
+      <c r="F273" t="n">
+        <v>24</v>
+      </c>
+      <c r="G273" t="n">
+        <v>21</v>
+      </c>
+      <c r="H273" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="I273" t="n">
+        <v>64</v>
+      </c>
+      <c r="J273" t="n">
+        <v>56</v>
+      </c>
+      <c r="K273" t="n">
+        <v>100</v>
+      </c>
+      <c r="L273" t="n">
+        <v>23</v>
+      </c>
+      <c r="M273" t="n">
+        <v>20</v>
+      </c>
+      <c r="N273" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="O273" t="n">
+        <v>72</v>
+      </c>
+      <c r="P273" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>88.41</v>
+      </c>
+      <c r="R273" t="n">
+        <v>17</v>
+      </c>
+      <c r="S273" t="n">
+        <v>15</v>
+      </c>
+      <c r="T273" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="U273" t="n">
+        <v>4</v>
+      </c>
+      <c r="V273" t="n">
+        <v>3</v>
+      </c>
+      <c r="W273" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X273" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:27:28</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>87.19</v>
+      </c>
+      <c r="C274" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D274" t="n">
+        <v>152</v>
+      </c>
+      <c r="E274" t="n">
+        <v>140</v>
+      </c>
+      <c r="F274" t="n">
+        <v>24</v>
+      </c>
+      <c r="G274" t="n">
+        <v>21</v>
+      </c>
+      <c r="H274" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="I274" t="n">
+        <v>64</v>
+      </c>
+      <c r="J274" t="n">
+        <v>56</v>
+      </c>
+      <c r="K274" t="n">
+        <v>100</v>
+      </c>
+      <c r="L274" t="n">
+        <v>23</v>
+      </c>
+      <c r="M274" t="n">
+        <v>20</v>
+      </c>
+      <c r="N274" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="O274" t="n">
+        <v>72</v>
+      </c>
+      <c r="P274" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R274" t="n">
+        <v>17</v>
+      </c>
+      <c r="S274" t="n">
+        <v>15</v>
+      </c>
+      <c r="T274" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U274" t="n">
+        <v>4</v>
+      </c>
+      <c r="V274" t="n">
+        <v>3</v>
+      </c>
+      <c r="W274" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X274" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:29:28</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="C275" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D275" t="n">
+        <v>154</v>
+      </c>
+      <c r="E275" t="n">
+        <v>141</v>
+      </c>
+      <c r="F275" t="n">
+        <v>24</v>
+      </c>
+      <c r="G275" t="n">
+        <v>21</v>
+      </c>
+      <c r="H275" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="I275" t="n">
+        <v>65</v>
+      </c>
+      <c r="J275" t="n">
+        <v>57</v>
+      </c>
+      <c r="K275" t="n">
+        <v>100</v>
+      </c>
+      <c r="L275" t="n">
+        <v>23</v>
+      </c>
+      <c r="M275" t="n">
+        <v>20</v>
+      </c>
+      <c r="N275" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="O275" t="n">
+        <v>73</v>
+      </c>
+      <c r="P275" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R275" t="n">
+        <v>17</v>
+      </c>
+      <c r="S275" t="n">
+        <v>15</v>
+      </c>
+      <c r="T275" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U275" t="n">
+        <v>4</v>
+      </c>
+      <c r="V275" t="n">
+        <v>3</v>
+      </c>
+      <c r="W275" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X275" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:31:28</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="C276" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D276" t="n">
+        <v>157</v>
+      </c>
+      <c r="E276" t="n">
+        <v>144</v>
+      </c>
+      <c r="F276" t="n">
+        <v>24</v>
+      </c>
+      <c r="G276" t="n">
+        <v>21</v>
+      </c>
+      <c r="H276" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="I276" t="n">
+        <v>68</v>
+      </c>
+      <c r="J276" t="n">
+        <v>60</v>
+      </c>
+      <c r="K276" t="n">
+        <v>100</v>
+      </c>
+      <c r="L276" t="n">
+        <v>23</v>
+      </c>
+      <c r="M276" t="n">
+        <v>20</v>
+      </c>
+      <c r="N276" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="O276" t="n">
+        <v>73</v>
+      </c>
+      <c r="P276" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R276" t="n">
+        <v>17</v>
+      </c>
+      <c r="S276" t="n">
+        <v>15</v>
+      </c>
+      <c r="T276" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U276" t="n">
+        <v>4</v>
+      </c>
+      <c r="V276" t="n">
+        <v>3</v>
+      </c>
+      <c r="W276" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X276" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:32:46</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="C277" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D277" t="n">
+        <v>157</v>
+      </c>
+      <c r="E277" t="n">
+        <v>144</v>
+      </c>
+      <c r="F277" t="n">
+        <v>24</v>
+      </c>
+      <c r="G277" t="n">
+        <v>21</v>
+      </c>
+      <c r="H277" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="I277" t="n">
+        <v>68</v>
+      </c>
+      <c r="J277" t="n">
+        <v>60</v>
+      </c>
+      <c r="K277" t="n">
+        <v>100</v>
+      </c>
+      <c r="L277" t="n">
+        <v>23</v>
+      </c>
+      <c r="M277" t="n">
+        <v>20</v>
+      </c>
+      <c r="N277" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="O277" t="n">
+        <v>73</v>
+      </c>
+      <c r="P277" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R277" t="n">
+        <v>17</v>
+      </c>
+      <c r="S277" t="n">
+        <v>15</v>
+      </c>
+      <c r="T277" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U277" t="n">
+        <v>4</v>
+      </c>
+      <c r="V277" t="n">
+        <v>3</v>
+      </c>
+      <c r="W277" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X277" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:34:46</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="C278" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D278" t="n">
+        <v>159</v>
+      </c>
+      <c r="E278" t="n">
+        <v>146</v>
+      </c>
+      <c r="F278" t="n">
+        <v>24</v>
+      </c>
+      <c r="G278" t="n">
+        <v>21</v>
+      </c>
+      <c r="H278" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="I278" t="n">
+        <v>68</v>
+      </c>
+      <c r="J278" t="n">
+        <v>60</v>
+      </c>
+      <c r="K278" t="n">
+        <v>100</v>
+      </c>
+      <c r="L278" t="n">
+        <v>23</v>
+      </c>
+      <c r="M278" t="n">
+        <v>20</v>
+      </c>
+      <c r="N278" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="O278" t="n">
+        <v>75</v>
+      </c>
+      <c r="P278" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R278" t="n">
+        <v>17</v>
+      </c>
+      <c r="S278" t="n">
+        <v>15</v>
+      </c>
+      <c r="T278" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U278" t="n">
+        <v>4</v>
+      </c>
+      <c r="V278" t="n">
+        <v>3</v>
+      </c>
+      <c r="W278" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X278" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:36:46</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="C279" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D279" t="n">
+        <v>160</v>
+      </c>
+      <c r="E279" t="n">
+        <v>147</v>
+      </c>
+      <c r="F279" t="n">
+        <v>24</v>
+      </c>
+      <c r="G279" t="n">
+        <v>21</v>
+      </c>
+      <c r="H279" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="I279" t="n">
+        <v>68</v>
+      </c>
+      <c r="J279" t="n">
+        <v>60</v>
+      </c>
+      <c r="K279" t="n">
+        <v>100</v>
+      </c>
+      <c r="L279" t="n">
+        <v>23</v>
+      </c>
+      <c r="M279" t="n">
+        <v>20</v>
+      </c>
+      <c r="N279" t="n">
+        <v>89</v>
+      </c>
+      <c r="O279" t="n">
+        <v>76</v>
+      </c>
+      <c r="P279" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R279" t="n">
+        <v>17</v>
+      </c>
+      <c r="S279" t="n">
+        <v>15</v>
+      </c>
+      <c r="T279" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U279" t="n">
+        <v>4</v>
+      </c>
+      <c r="V279" t="n">
+        <v>3</v>
+      </c>
+      <c r="W279" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X279" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:38:47</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="C280" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D280" t="n">
+        <v>161</v>
+      </c>
+      <c r="E280" t="n">
+        <v>147</v>
+      </c>
+      <c r="F280" t="n">
+        <v>24</v>
+      </c>
+      <c r="G280" t="n">
+        <v>21</v>
+      </c>
+      <c r="H280" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="I280" t="n">
+        <v>69</v>
+      </c>
+      <c r="J280" t="n">
+        <v>60</v>
+      </c>
+      <c r="K280" t="n">
+        <v>100</v>
+      </c>
+      <c r="L280" t="n">
+        <v>23</v>
+      </c>
+      <c r="M280" t="n">
+        <v>20</v>
+      </c>
+      <c r="N280" t="n">
+        <v>89</v>
+      </c>
+      <c r="O280" t="n">
+        <v>76</v>
+      </c>
+      <c r="P280" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R280" t="n">
+        <v>17</v>
+      </c>
+      <c r="S280" t="n">
+        <v>15</v>
+      </c>
+      <c r="T280" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U280" t="n">
+        <v>4</v>
+      </c>
+      <c r="V280" t="n">
+        <v>3</v>
+      </c>
+      <c r="W280" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X280" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:40:46</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="C281" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D281" t="n">
+        <v>162</v>
+      </c>
+      <c r="E281" t="n">
+        <v>148</v>
+      </c>
+      <c r="F281" t="n">
+        <v>24</v>
+      </c>
+      <c r="G281" t="n">
+        <v>21</v>
+      </c>
+      <c r="H281" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="I281" t="n">
+        <v>70</v>
+      </c>
+      <c r="J281" t="n">
+        <v>61</v>
+      </c>
+      <c r="K281" t="n">
+        <v>100</v>
+      </c>
+      <c r="L281" t="n">
+        <v>23</v>
+      </c>
+      <c r="M281" t="n">
+        <v>20</v>
+      </c>
+      <c r="N281" t="n">
+        <v>89</v>
+      </c>
+      <c r="O281" t="n">
+        <v>76</v>
+      </c>
+      <c r="P281" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R281" t="n">
+        <v>17</v>
+      </c>
+      <c r="S281" t="n">
+        <v>15</v>
+      </c>
+      <c r="T281" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U281" t="n">
+        <v>4</v>
+      </c>
+      <c r="V281" t="n">
+        <v>3</v>
+      </c>
+      <c r="W281" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X281" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:42:46</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="C282" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D282" t="n">
+        <v>163</v>
+      </c>
+      <c r="E282" t="n">
+        <v>149</v>
+      </c>
+      <c r="F282" t="n">
+        <v>25</v>
+      </c>
+      <c r="G282" t="n">
+        <v>22</v>
+      </c>
+      <c r="H282" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="I282" t="n">
+        <v>71</v>
+      </c>
+      <c r="J282" t="n">
+        <v>62</v>
+      </c>
+      <c r="K282" t="n">
+        <v>100</v>
+      </c>
+      <c r="L282" t="n">
+        <v>24</v>
+      </c>
+      <c r="M282" t="n">
+        <v>21</v>
+      </c>
+      <c r="N282" t="n">
+        <v>89</v>
+      </c>
+      <c r="O282" t="n">
+        <v>76</v>
+      </c>
+      <c r="P282" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R282" t="n">
+        <v>18</v>
+      </c>
+      <c r="S282" t="n">
+        <v>16</v>
+      </c>
+      <c r="T282" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U282" t="n">
+        <v>5</v>
+      </c>
+      <c r="V282" t="n">
+        <v>4</v>
+      </c>
+      <c r="W282" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X282" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:44:46</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="C283" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D283" t="n">
+        <v>163</v>
+      </c>
+      <c r="E283" t="n">
+        <v>149</v>
+      </c>
+      <c r="F283" t="n">
+        <v>25</v>
+      </c>
+      <c r="G283" t="n">
+        <v>22</v>
+      </c>
+      <c r="H283" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="I283" t="n">
+        <v>71</v>
+      </c>
+      <c r="J283" t="n">
+        <v>62</v>
+      </c>
+      <c r="K283" t="n">
+        <v>100</v>
+      </c>
+      <c r="L283" t="n">
+        <v>24</v>
+      </c>
+      <c r="M283" t="n">
+        <v>21</v>
+      </c>
+      <c r="N283" t="n">
+        <v>89</v>
+      </c>
+      <c r="O283" t="n">
+        <v>76</v>
+      </c>
+      <c r="P283" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R283" t="n">
+        <v>18</v>
+      </c>
+      <c r="S283" t="n">
+        <v>16</v>
+      </c>
+      <c r="T283" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U283" t="n">
+        <v>5</v>
+      </c>
+      <c r="V283" t="n">
+        <v>4</v>
+      </c>
+      <c r="W283" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X283" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:46:48</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>87</v>
+      </c>
+      <c r="C284" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D284" t="n">
+        <v>164</v>
+      </c>
+      <c r="E284" t="n">
+        <v>150</v>
+      </c>
+      <c r="F284" t="n">
+        <v>25</v>
+      </c>
+      <c r="G284" t="n">
+        <v>22</v>
+      </c>
+      <c r="H284" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I284" t="n">
+        <v>72</v>
+      </c>
+      <c r="J284" t="n">
+        <v>63</v>
+      </c>
+      <c r="K284" t="n">
+        <v>100</v>
+      </c>
+      <c r="L284" t="n">
+        <v>25</v>
+      </c>
+      <c r="M284" t="n">
+        <v>22</v>
+      </c>
+      <c r="N284" t="n">
+        <v>89</v>
+      </c>
+      <c r="O284" t="n">
+        <v>76</v>
+      </c>
+      <c r="P284" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R284" t="n">
+        <v>18</v>
+      </c>
+      <c r="S284" t="n">
+        <v>16</v>
+      </c>
+      <c r="T284" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U284" t="n">
+        <v>5</v>
+      </c>
+      <c r="V284" t="n">
+        <v>4</v>
+      </c>
+      <c r="W284" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X284" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:47:27</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>87</v>
+      </c>
+      <c r="C285" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D285" t="n">
+        <v>164</v>
+      </c>
+      <c r="E285" t="n">
+        <v>150</v>
+      </c>
+      <c r="F285" t="n">
+        <v>25</v>
+      </c>
+      <c r="G285" t="n">
+        <v>22</v>
+      </c>
+      <c r="H285" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I285" t="n">
+        <v>72</v>
+      </c>
+      <c r="J285" t="n">
+        <v>63</v>
+      </c>
+      <c r="K285" t="n">
+        <v>100</v>
+      </c>
+      <c r="L285" t="n">
+        <v>25</v>
+      </c>
+      <c r="M285" t="n">
+        <v>22</v>
+      </c>
+      <c r="N285" t="n">
+        <v>89</v>
+      </c>
+      <c r="O285" t="n">
+        <v>76</v>
+      </c>
+      <c r="P285" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R285" t="n">
+        <v>18</v>
+      </c>
+      <c r="S285" t="n">
+        <v>16</v>
+      </c>
+      <c r="T285" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U285" t="n">
+        <v>5</v>
+      </c>
+      <c r="V285" t="n">
+        <v>4</v>
+      </c>
+      <c r="W285" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X285" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:49:28</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>87</v>
+      </c>
+      <c r="C286" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D286" t="n">
+        <v>164</v>
+      </c>
+      <c r="E286" t="n">
+        <v>150</v>
+      </c>
+      <c r="F286" t="n">
+        <v>25</v>
+      </c>
+      <c r="G286" t="n">
+        <v>22</v>
+      </c>
+      <c r="H286" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I286" t="n">
+        <v>72</v>
+      </c>
+      <c r="J286" t="n">
+        <v>63</v>
+      </c>
+      <c r="K286" t="n">
+        <v>100</v>
+      </c>
+      <c r="L286" t="n">
+        <v>25</v>
+      </c>
+      <c r="M286" t="n">
+        <v>22</v>
+      </c>
+      <c r="N286" t="n">
+        <v>89</v>
+      </c>
+      <c r="O286" t="n">
+        <v>76</v>
+      </c>
+      <c r="P286" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R286" t="n">
+        <v>18</v>
+      </c>
+      <c r="S286" t="n">
+        <v>16</v>
+      </c>
+      <c r="T286" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U286" t="n">
+        <v>5</v>
+      </c>
+      <c r="V286" t="n">
+        <v>4</v>
+      </c>
+      <c r="W286" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X286" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:51:28</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="C287" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D287" t="n">
+        <v>166</v>
+      </c>
+      <c r="E287" t="n">
+        <v>151</v>
+      </c>
+      <c r="F287" t="n">
+        <v>25</v>
+      </c>
+      <c r="G287" t="n">
+        <v>22</v>
+      </c>
+      <c r="H287" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I287" t="n">
+        <v>72</v>
+      </c>
+      <c r="J287" t="n">
+        <v>63</v>
+      </c>
+      <c r="K287" t="n">
+        <v>100</v>
+      </c>
+      <c r="L287" t="n">
+        <v>25</v>
+      </c>
+      <c r="M287" t="n">
+        <v>22</v>
+      </c>
+      <c r="N287" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="O287" t="n">
+        <v>78</v>
+      </c>
+      <c r="P287" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R287" t="n">
+        <v>18</v>
+      </c>
+      <c r="S287" t="n">
+        <v>16</v>
+      </c>
+      <c r="T287" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U287" t="n">
+        <v>5</v>
+      </c>
+      <c r="V287" t="n">
+        <v>4</v>
+      </c>
+      <c r="W287" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X287" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:53:34</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="C288" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D288" t="n">
+        <v>168</v>
+      </c>
+      <c r="E288" t="n">
+        <v>153</v>
+      </c>
+      <c r="F288" t="n">
+        <v>25</v>
+      </c>
+      <c r="G288" t="n">
+        <v>22</v>
+      </c>
+      <c r="H288" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I288" t="n">
+        <v>74</v>
+      </c>
+      <c r="J288" t="n">
+        <v>65</v>
+      </c>
+      <c r="K288" t="n">
+        <v>100</v>
+      </c>
+      <c r="L288" t="n">
+        <v>26</v>
+      </c>
+      <c r="M288" t="n">
+        <v>23</v>
+      </c>
+      <c r="N288" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="O288" t="n">
+        <v>78</v>
+      </c>
+      <c r="P288" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="R288" t="n">
+        <v>18</v>
+      </c>
+      <c r="S288" t="n">
+        <v>16</v>
+      </c>
+      <c r="T288" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U288" t="n">
+        <v>5</v>
+      </c>
+      <c r="V288" t="n">
+        <v>4</v>
+      </c>
+      <c r="W288" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X288" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:54:17</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="C289" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="D289" t="n">
+        <v>171</v>
+      </c>
+      <c r="E289" t="n">
+        <v>156</v>
+      </c>
+      <c r="F289" t="n">
+        <v>26</v>
+      </c>
+      <c r="G289" t="n">
+        <v>23</v>
+      </c>
+      <c r="H289" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="I289" t="n">
+        <v>75</v>
+      </c>
+      <c r="J289" t="n">
+        <v>66</v>
+      </c>
+      <c r="K289" t="n">
+        <v>100</v>
+      </c>
+      <c r="L289" t="n">
+        <v>26</v>
+      </c>
+      <c r="M289" t="n">
+        <v>23</v>
+      </c>
+      <c r="N289" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="O289" t="n">
+        <v>80</v>
+      </c>
+      <c r="P289" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="R289" t="n">
+        <v>19</v>
+      </c>
+      <c r="S289" t="n">
+        <v>17</v>
+      </c>
+      <c r="T289" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U289" t="n">
+        <v>5</v>
+      </c>
+      <c r="V289" t="n">
+        <v>4</v>
+      </c>
+      <c r="W289" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X289" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:56:17</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="C290" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="D290" t="n">
+        <v>171</v>
+      </c>
+      <c r="E290" t="n">
+        <v>156</v>
+      </c>
+      <c r="F290" t="n">
+        <v>26</v>
+      </c>
+      <c r="G290" t="n">
+        <v>23</v>
+      </c>
+      <c r="H290" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="I290" t="n">
+        <v>75</v>
+      </c>
+      <c r="J290" t="n">
+        <v>66</v>
+      </c>
+      <c r="K290" t="n">
+        <v>100</v>
+      </c>
+      <c r="L290" t="n">
+        <v>26</v>
+      </c>
+      <c r="M290" t="n">
+        <v>23</v>
+      </c>
+      <c r="N290" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="O290" t="n">
+        <v>80</v>
+      </c>
+      <c r="P290" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="R290" t="n">
+        <v>19</v>
+      </c>
+      <c r="S290" t="n">
+        <v>17</v>
+      </c>
+      <c r="T290" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U290" t="n">
+        <v>5</v>
+      </c>
+      <c r="V290" t="n">
+        <v>4</v>
+      </c>
+      <c r="W290" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X290" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:58:18</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="C291" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="D291" t="n">
+        <v>173</v>
+      </c>
+      <c r="E291" t="n">
+        <v>158</v>
+      </c>
+      <c r="F291" t="n">
+        <v>26</v>
+      </c>
+      <c r="G291" t="n">
+        <v>23</v>
+      </c>
+      <c r="H291" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="I291" t="n">
+        <v>75</v>
+      </c>
+      <c r="J291" t="n">
+        <v>66</v>
+      </c>
+      <c r="K291" t="n">
+        <v>100</v>
+      </c>
+      <c r="L291" t="n">
+        <v>26</v>
+      </c>
+      <c r="M291" t="n">
+        <v>23</v>
+      </c>
+      <c r="N291" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="O291" t="n">
+        <v>82</v>
+      </c>
+      <c r="P291" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="R291" t="n">
+        <v>19</v>
+      </c>
+      <c r="S291" t="n">
+        <v>17</v>
+      </c>
+      <c r="T291" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U291" t="n">
+        <v>5</v>
+      </c>
+      <c r="V291" t="n">
+        <v>4</v>
+      </c>
+      <c r="W291" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X291" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:00:18</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="C292" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="D292" t="n">
+        <v>174</v>
+      </c>
+      <c r="E292" t="n">
+        <v>159</v>
+      </c>
+      <c r="F292" t="n">
+        <v>26</v>
+      </c>
+      <c r="G292" t="n">
+        <v>23</v>
+      </c>
+      <c r="H292" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="I292" t="n">
+        <v>75</v>
+      </c>
+      <c r="J292" t="n">
+        <v>66</v>
+      </c>
+      <c r="K292" t="n">
+        <v>100</v>
+      </c>
+      <c r="L292" t="n">
+        <v>26</v>
+      </c>
+      <c r="M292" t="n">
+        <v>23</v>
+      </c>
+      <c r="N292" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="O292" t="n">
+        <v>83</v>
+      </c>
+      <c r="P292" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="R292" t="n">
+        <v>19</v>
+      </c>
+      <c r="S292" t="n">
+        <v>17</v>
+      </c>
+      <c r="T292" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U292" t="n">
+        <v>5</v>
+      </c>
+      <c r="V292" t="n">
+        <v>4</v>
+      </c>
+      <c r="W292" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X292" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:02:18</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="C293" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="D293" t="n">
+        <v>174</v>
+      </c>
+      <c r="E293" t="n">
+        <v>159</v>
+      </c>
+      <c r="F293" t="n">
+        <v>26</v>
+      </c>
+      <c r="G293" t="n">
+        <v>23</v>
+      </c>
+      <c r="H293" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="I293" t="n">
+        <v>75</v>
+      </c>
+      <c r="J293" t="n">
+        <v>66</v>
+      </c>
+      <c r="K293" t="n">
+        <v>100</v>
+      </c>
+      <c r="L293" t="n">
+        <v>26</v>
+      </c>
+      <c r="M293" t="n">
+        <v>23</v>
+      </c>
+      <c r="N293" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="O293" t="n">
+        <v>83</v>
+      </c>
+      <c r="P293" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="R293" t="n">
+        <v>19</v>
+      </c>
+      <c r="S293" t="n">
+        <v>17</v>
+      </c>
+      <c r="T293" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U293" t="n">
+        <v>5</v>
+      </c>
+      <c r="V293" t="n">
+        <v>4</v>
+      </c>
+      <c r="W293" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X293" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:04:18</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="C294" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D294" t="n">
+        <v>178</v>
+      </c>
+      <c r="E294" t="n">
+        <v>162</v>
+      </c>
+      <c r="F294" t="n">
+        <v>27</v>
+      </c>
+      <c r="G294" t="n">
+        <v>23</v>
+      </c>
+      <c r="H294" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="I294" t="n">
+        <v>78</v>
+      </c>
+      <c r="J294" t="n">
+        <v>68</v>
+      </c>
+      <c r="K294" t="n">
+        <v>100</v>
+      </c>
+      <c r="L294" t="n">
+        <v>27</v>
+      </c>
+      <c r="M294" t="n">
+        <v>24</v>
+      </c>
+      <c r="N294" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="O294" t="n">
+        <v>83</v>
+      </c>
+      <c r="P294" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R294" t="n">
+        <v>20</v>
+      </c>
+      <c r="S294" t="n">
+        <v>17</v>
+      </c>
+      <c r="T294" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U294" t="n">
+        <v>5</v>
+      </c>
+      <c r="V294" t="n">
+        <v>4</v>
+      </c>
+      <c r="W294" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X294" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:05:37</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="C295" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D295" t="n">
+        <v>178</v>
+      </c>
+      <c r="E295" t="n">
+        <v>162</v>
+      </c>
+      <c r="F295" t="n">
+        <v>27</v>
+      </c>
+      <c r="G295" t="n">
+        <v>23</v>
+      </c>
+      <c r="H295" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="I295" t="n">
+        <v>78</v>
+      </c>
+      <c r="J295" t="n">
+        <v>68</v>
+      </c>
+      <c r="K295" t="n">
+        <v>100</v>
+      </c>
+      <c r="L295" t="n">
+        <v>27</v>
+      </c>
+      <c r="M295" t="n">
+        <v>24</v>
+      </c>
+      <c r="N295" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="O295" t="n">
+        <v>83</v>
+      </c>
+      <c r="P295" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R295" t="n">
+        <v>20</v>
+      </c>
+      <c r="S295" t="n">
+        <v>17</v>
+      </c>
+      <c r="T295" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U295" t="n">
+        <v>5</v>
+      </c>
+      <c r="V295" t="n">
+        <v>4</v>
+      </c>
+      <c r="W295" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X295" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/regularite_history.xlsx
+++ b/regularite_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y295"/>
+  <dimension ref="A1:Y302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23769,6 +23769,559 @@
         <v>4</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:07:36</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="C296" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D296" t="n">
+        <v>179</v>
+      </c>
+      <c r="E296" t="n">
+        <v>163</v>
+      </c>
+      <c r="F296" t="n">
+        <v>27</v>
+      </c>
+      <c r="G296" t="n">
+        <v>23</v>
+      </c>
+      <c r="H296" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="I296" t="n">
+        <v>78</v>
+      </c>
+      <c r="J296" t="n">
+        <v>68</v>
+      </c>
+      <c r="K296" t="n">
+        <v>100</v>
+      </c>
+      <c r="L296" t="n">
+        <v>28</v>
+      </c>
+      <c r="M296" t="n">
+        <v>25</v>
+      </c>
+      <c r="N296" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="O296" t="n">
+        <v>83</v>
+      </c>
+      <c r="P296" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R296" t="n">
+        <v>20</v>
+      </c>
+      <c r="S296" t="n">
+        <v>17</v>
+      </c>
+      <c r="T296" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U296" t="n">
+        <v>5</v>
+      </c>
+      <c r="V296" t="n">
+        <v>4</v>
+      </c>
+      <c r="W296" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X296" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:09:36</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="C297" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D297" t="n">
+        <v>180</v>
+      </c>
+      <c r="E297" t="n">
+        <v>164</v>
+      </c>
+      <c r="F297" t="n">
+        <v>27</v>
+      </c>
+      <c r="G297" t="n">
+        <v>23</v>
+      </c>
+      <c r="H297" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="I297" t="n">
+        <v>78</v>
+      </c>
+      <c r="J297" t="n">
+        <v>68</v>
+      </c>
+      <c r="K297" t="n">
+        <v>100</v>
+      </c>
+      <c r="L297" t="n">
+        <v>28</v>
+      </c>
+      <c r="M297" t="n">
+        <v>25</v>
+      </c>
+      <c r="N297" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O297" t="n">
+        <v>84</v>
+      </c>
+      <c r="P297" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R297" t="n">
+        <v>20</v>
+      </c>
+      <c r="S297" t="n">
+        <v>17</v>
+      </c>
+      <c r="T297" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U297" t="n">
+        <v>5</v>
+      </c>
+      <c r="V297" t="n">
+        <v>4</v>
+      </c>
+      <c r="W297" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X297" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:09:55</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="C298" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D298" t="n">
+        <v>180</v>
+      </c>
+      <c r="E298" t="n">
+        <v>164</v>
+      </c>
+      <c r="F298" t="n">
+        <v>27</v>
+      </c>
+      <c r="G298" t="n">
+        <v>23</v>
+      </c>
+      <c r="H298" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="I298" t="n">
+        <v>78</v>
+      </c>
+      <c r="J298" t="n">
+        <v>68</v>
+      </c>
+      <c r="K298" t="n">
+        <v>100</v>
+      </c>
+      <c r="L298" t="n">
+        <v>28</v>
+      </c>
+      <c r="M298" t="n">
+        <v>25</v>
+      </c>
+      <c r="N298" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O298" t="n">
+        <v>84</v>
+      </c>
+      <c r="P298" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R298" t="n">
+        <v>20</v>
+      </c>
+      <c r="S298" t="n">
+        <v>17</v>
+      </c>
+      <c r="T298" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U298" t="n">
+        <v>5</v>
+      </c>
+      <c r="V298" t="n">
+        <v>4</v>
+      </c>
+      <c r="W298" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X298" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:11:56</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="C299" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D299" t="n">
+        <v>181</v>
+      </c>
+      <c r="E299" t="n">
+        <v>165</v>
+      </c>
+      <c r="F299" t="n">
+        <v>27</v>
+      </c>
+      <c r="G299" t="n">
+        <v>23</v>
+      </c>
+      <c r="H299" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="I299" t="n">
+        <v>79</v>
+      </c>
+      <c r="J299" t="n">
+        <v>69</v>
+      </c>
+      <c r="K299" t="n">
+        <v>100</v>
+      </c>
+      <c r="L299" t="n">
+        <v>28</v>
+      </c>
+      <c r="M299" t="n">
+        <v>25</v>
+      </c>
+      <c r="N299" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O299" t="n">
+        <v>84</v>
+      </c>
+      <c r="P299" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R299" t="n">
+        <v>20</v>
+      </c>
+      <c r="S299" t="n">
+        <v>17</v>
+      </c>
+      <c r="T299" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U299" t="n">
+        <v>5</v>
+      </c>
+      <c r="V299" t="n">
+        <v>4</v>
+      </c>
+      <c r="W299" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X299" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:13:56</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="C300" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="D300" t="n">
+        <v>181</v>
+      </c>
+      <c r="E300" t="n">
+        <v>165</v>
+      </c>
+      <c r="F300" t="n">
+        <v>27</v>
+      </c>
+      <c r="G300" t="n">
+        <v>23</v>
+      </c>
+      <c r="H300" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="I300" t="n">
+        <v>79</v>
+      </c>
+      <c r="J300" t="n">
+        <v>69</v>
+      </c>
+      <c r="K300" t="n">
+        <v>100</v>
+      </c>
+      <c r="L300" t="n">
+        <v>28</v>
+      </c>
+      <c r="M300" t="n">
+        <v>25</v>
+      </c>
+      <c r="N300" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O300" t="n">
+        <v>84</v>
+      </c>
+      <c r="P300" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="R300" t="n">
+        <v>20</v>
+      </c>
+      <c r="S300" t="n">
+        <v>17</v>
+      </c>
+      <c r="T300" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U300" t="n">
+        <v>5</v>
+      </c>
+      <c r="V300" t="n">
+        <v>4</v>
+      </c>
+      <c r="W300" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X300" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:15:56</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="C301" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D301" t="n">
+        <v>184</v>
+      </c>
+      <c r="E301" t="n">
+        <v>167</v>
+      </c>
+      <c r="F301" t="n">
+        <v>28</v>
+      </c>
+      <c r="G301" t="n">
+        <v>24</v>
+      </c>
+      <c r="H301" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I301" t="n">
+        <v>80</v>
+      </c>
+      <c r="J301" t="n">
+        <v>70</v>
+      </c>
+      <c r="K301" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L301" t="n">
+        <v>29</v>
+      </c>
+      <c r="M301" t="n">
+        <v>25</v>
+      </c>
+      <c r="N301" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O301" t="n">
+        <v>85</v>
+      </c>
+      <c r="P301" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="R301" t="n">
+        <v>21</v>
+      </c>
+      <c r="S301" t="n">
+        <v>18</v>
+      </c>
+      <c r="T301" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U301" t="n">
+        <v>5</v>
+      </c>
+      <c r="V301" t="n">
+        <v>4</v>
+      </c>
+      <c r="W301" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X301" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:17:56</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="C302" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D302" t="n">
+        <v>184</v>
+      </c>
+      <c r="E302" t="n">
+        <v>167</v>
+      </c>
+      <c r="F302" t="n">
+        <v>28</v>
+      </c>
+      <c r="G302" t="n">
+        <v>24</v>
+      </c>
+      <c r="H302" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I302" t="n">
+        <v>80</v>
+      </c>
+      <c r="J302" t="n">
+        <v>70</v>
+      </c>
+      <c r="K302" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L302" t="n">
+        <v>29</v>
+      </c>
+      <c r="M302" t="n">
+        <v>25</v>
+      </c>
+      <c r="N302" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O302" t="n">
+        <v>85</v>
+      </c>
+      <c r="P302" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="R302" t="n">
+        <v>21</v>
+      </c>
+      <c r="S302" t="n">
+        <v>18</v>
+      </c>
+      <c r="T302" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U302" t="n">
+        <v>5</v>
+      </c>
+      <c r="V302" t="n">
+        <v>4</v>
+      </c>
+      <c r="W302" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X302" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/regularite_history.xlsx
+++ b/regularite_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y302"/>
+  <dimension ref="A1:Y367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24322,6 +24322,5141 @@
         <v>4</v>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:19:56</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="C303" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D303" t="n">
+        <v>184</v>
+      </c>
+      <c r="E303" t="n">
+        <v>167</v>
+      </c>
+      <c r="F303" t="n">
+        <v>28</v>
+      </c>
+      <c r="G303" t="n">
+        <v>24</v>
+      </c>
+      <c r="H303" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I303" t="n">
+        <v>80</v>
+      </c>
+      <c r="J303" t="n">
+        <v>70</v>
+      </c>
+      <c r="K303" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L303" t="n">
+        <v>29</v>
+      </c>
+      <c r="M303" t="n">
+        <v>25</v>
+      </c>
+      <c r="N303" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O303" t="n">
+        <v>85</v>
+      </c>
+      <c r="P303" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="R303" t="n">
+        <v>21</v>
+      </c>
+      <c r="S303" t="n">
+        <v>18</v>
+      </c>
+      <c r="T303" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U303" t="n">
+        <v>5</v>
+      </c>
+      <c r="V303" t="n">
+        <v>4</v>
+      </c>
+      <c r="W303" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X303" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:21:57</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="C304" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D304" t="n">
+        <v>186</v>
+      </c>
+      <c r="E304" t="n">
+        <v>168</v>
+      </c>
+      <c r="F304" t="n">
+        <v>28</v>
+      </c>
+      <c r="G304" t="n">
+        <v>24</v>
+      </c>
+      <c r="H304" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I304" t="n">
+        <v>80</v>
+      </c>
+      <c r="J304" t="n">
+        <v>70</v>
+      </c>
+      <c r="K304" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L304" t="n">
+        <v>29</v>
+      </c>
+      <c r="M304" t="n">
+        <v>25</v>
+      </c>
+      <c r="N304" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="O304" t="n">
+        <v>87</v>
+      </c>
+      <c r="P304" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="R304" t="n">
+        <v>21</v>
+      </c>
+      <c r="S304" t="n">
+        <v>18</v>
+      </c>
+      <c r="T304" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U304" t="n">
+        <v>5</v>
+      </c>
+      <c r="V304" t="n">
+        <v>4</v>
+      </c>
+      <c r="W304" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X304" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:24:01</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="C305" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D305" t="n">
+        <v>187</v>
+      </c>
+      <c r="E305" t="n">
+        <v>169</v>
+      </c>
+      <c r="F305" t="n">
+        <v>28</v>
+      </c>
+      <c r="G305" t="n">
+        <v>24</v>
+      </c>
+      <c r="H305" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I305" t="n">
+        <v>80</v>
+      </c>
+      <c r="J305" t="n">
+        <v>70</v>
+      </c>
+      <c r="K305" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L305" t="n">
+        <v>29</v>
+      </c>
+      <c r="M305" t="n">
+        <v>25</v>
+      </c>
+      <c r="N305" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="O305" t="n">
+        <v>88</v>
+      </c>
+      <c r="P305" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="R305" t="n">
+        <v>21</v>
+      </c>
+      <c r="S305" t="n">
+        <v>18</v>
+      </c>
+      <c r="T305" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="U305" t="n">
+        <v>5</v>
+      </c>
+      <c r="V305" t="n">
+        <v>4</v>
+      </c>
+      <c r="W305" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X305" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:25:57</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="C306" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D306" t="n">
+        <v>187</v>
+      </c>
+      <c r="E306" t="n">
+        <v>169</v>
+      </c>
+      <c r="F306" t="n">
+        <v>29</v>
+      </c>
+      <c r="G306" t="n">
+        <v>25</v>
+      </c>
+      <c r="H306" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I306" t="n">
+        <v>80</v>
+      </c>
+      <c r="J306" t="n">
+        <v>70</v>
+      </c>
+      <c r="K306" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L306" t="n">
+        <v>29</v>
+      </c>
+      <c r="M306" t="n">
+        <v>25</v>
+      </c>
+      <c r="N306" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="O306" t="n">
+        <v>88</v>
+      </c>
+      <c r="P306" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R306" t="n">
+        <v>22</v>
+      </c>
+      <c r="S306" t="n">
+        <v>19</v>
+      </c>
+      <c r="T306" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U306" t="n">
+        <v>6</v>
+      </c>
+      <c r="V306" t="n">
+        <v>5</v>
+      </c>
+      <c r="W306" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X306" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:27:57</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="C307" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D307" t="n">
+        <v>187</v>
+      </c>
+      <c r="E307" t="n">
+        <v>169</v>
+      </c>
+      <c r="F307" t="n">
+        <v>29</v>
+      </c>
+      <c r="G307" t="n">
+        <v>25</v>
+      </c>
+      <c r="H307" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I307" t="n">
+        <v>80</v>
+      </c>
+      <c r="J307" t="n">
+        <v>70</v>
+      </c>
+      <c r="K307" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L307" t="n">
+        <v>29</v>
+      </c>
+      <c r="M307" t="n">
+        <v>25</v>
+      </c>
+      <c r="N307" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="O307" t="n">
+        <v>88</v>
+      </c>
+      <c r="P307" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R307" t="n">
+        <v>22</v>
+      </c>
+      <c r="S307" t="n">
+        <v>19</v>
+      </c>
+      <c r="T307" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U307" t="n">
+        <v>6</v>
+      </c>
+      <c r="V307" t="n">
+        <v>5</v>
+      </c>
+      <c r="W307" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X307" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:29:19</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="C308" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D308" t="n">
+        <v>189</v>
+      </c>
+      <c r="E308" t="n">
+        <v>171</v>
+      </c>
+      <c r="F308" t="n">
+        <v>29</v>
+      </c>
+      <c r="G308" t="n">
+        <v>25</v>
+      </c>
+      <c r="H308" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I308" t="n">
+        <v>80</v>
+      </c>
+      <c r="J308" t="n">
+        <v>70</v>
+      </c>
+      <c r="K308" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L308" t="n">
+        <v>29</v>
+      </c>
+      <c r="M308" t="n">
+        <v>25</v>
+      </c>
+      <c r="N308" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="O308" t="n">
+        <v>90</v>
+      </c>
+      <c r="P308" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R308" t="n">
+        <v>22</v>
+      </c>
+      <c r="S308" t="n">
+        <v>19</v>
+      </c>
+      <c r="T308" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U308" t="n">
+        <v>6</v>
+      </c>
+      <c r="V308" t="n">
+        <v>5</v>
+      </c>
+      <c r="W308" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X308" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:31:19</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="C309" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D309" t="n">
+        <v>189</v>
+      </c>
+      <c r="E309" t="n">
+        <v>171</v>
+      </c>
+      <c r="F309" t="n">
+        <v>29</v>
+      </c>
+      <c r="G309" t="n">
+        <v>25</v>
+      </c>
+      <c r="H309" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I309" t="n">
+        <v>80</v>
+      </c>
+      <c r="J309" t="n">
+        <v>70</v>
+      </c>
+      <c r="K309" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L309" t="n">
+        <v>29</v>
+      </c>
+      <c r="M309" t="n">
+        <v>25</v>
+      </c>
+      <c r="N309" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="O309" t="n">
+        <v>90</v>
+      </c>
+      <c r="P309" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R309" t="n">
+        <v>22</v>
+      </c>
+      <c r="S309" t="n">
+        <v>19</v>
+      </c>
+      <c r="T309" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U309" t="n">
+        <v>6</v>
+      </c>
+      <c r="V309" t="n">
+        <v>5</v>
+      </c>
+      <c r="W309" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X309" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:33:20</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>87</v>
+      </c>
+      <c r="C310" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D310" t="n">
+        <v>190</v>
+      </c>
+      <c r="E310" t="n">
+        <v>172</v>
+      </c>
+      <c r="F310" t="n">
+        <v>29</v>
+      </c>
+      <c r="G310" t="n">
+        <v>25</v>
+      </c>
+      <c r="H310" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I310" t="n">
+        <v>80</v>
+      </c>
+      <c r="J310" t="n">
+        <v>70</v>
+      </c>
+      <c r="K310" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L310" t="n">
+        <v>29</v>
+      </c>
+      <c r="M310" t="n">
+        <v>25</v>
+      </c>
+      <c r="N310" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="O310" t="n">
+        <v>91</v>
+      </c>
+      <c r="P310" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R310" t="n">
+        <v>22</v>
+      </c>
+      <c r="S310" t="n">
+        <v>19</v>
+      </c>
+      <c r="T310" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U310" t="n">
+        <v>6</v>
+      </c>
+      <c r="V310" t="n">
+        <v>5</v>
+      </c>
+      <c r="W310" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X310" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:34:55</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>87</v>
+      </c>
+      <c r="C311" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D311" t="n">
+        <v>190</v>
+      </c>
+      <c r="E311" t="n">
+        <v>172</v>
+      </c>
+      <c r="F311" t="n">
+        <v>29</v>
+      </c>
+      <c r="G311" t="n">
+        <v>25</v>
+      </c>
+      <c r="H311" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I311" t="n">
+        <v>80</v>
+      </c>
+      <c r="J311" t="n">
+        <v>70</v>
+      </c>
+      <c r="K311" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L311" t="n">
+        <v>29</v>
+      </c>
+      <c r="M311" t="n">
+        <v>25</v>
+      </c>
+      <c r="N311" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="O311" t="n">
+        <v>91</v>
+      </c>
+      <c r="P311" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R311" t="n">
+        <v>22</v>
+      </c>
+      <c r="S311" t="n">
+        <v>19</v>
+      </c>
+      <c r="T311" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U311" t="n">
+        <v>6</v>
+      </c>
+      <c r="V311" t="n">
+        <v>5</v>
+      </c>
+      <c r="W311" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X311" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:36:44</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>87</v>
+      </c>
+      <c r="C312" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D312" t="n">
+        <v>190</v>
+      </c>
+      <c r="E312" t="n">
+        <v>172</v>
+      </c>
+      <c r="F312" t="n">
+        <v>29</v>
+      </c>
+      <c r="G312" t="n">
+        <v>25</v>
+      </c>
+      <c r="H312" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I312" t="n">
+        <v>80</v>
+      </c>
+      <c r="J312" t="n">
+        <v>70</v>
+      </c>
+      <c r="K312" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L312" t="n">
+        <v>29</v>
+      </c>
+      <c r="M312" t="n">
+        <v>25</v>
+      </c>
+      <c r="N312" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="O312" t="n">
+        <v>91</v>
+      </c>
+      <c r="P312" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R312" t="n">
+        <v>22</v>
+      </c>
+      <c r="S312" t="n">
+        <v>19</v>
+      </c>
+      <c r="T312" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U312" t="n">
+        <v>6</v>
+      </c>
+      <c r="V312" t="n">
+        <v>5</v>
+      </c>
+      <c r="W312" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X312" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:38:26</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>87</v>
+      </c>
+      <c r="C313" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D313" t="n">
+        <v>190</v>
+      </c>
+      <c r="E313" t="n">
+        <v>172</v>
+      </c>
+      <c r="F313" t="n">
+        <v>29</v>
+      </c>
+      <c r="G313" t="n">
+        <v>25</v>
+      </c>
+      <c r="H313" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I313" t="n">
+        <v>80</v>
+      </c>
+      <c r="J313" t="n">
+        <v>70</v>
+      </c>
+      <c r="K313" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L313" t="n">
+        <v>29</v>
+      </c>
+      <c r="M313" t="n">
+        <v>25</v>
+      </c>
+      <c r="N313" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="O313" t="n">
+        <v>91</v>
+      </c>
+      <c r="P313" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R313" t="n">
+        <v>22</v>
+      </c>
+      <c r="S313" t="n">
+        <v>19</v>
+      </c>
+      <c r="T313" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U313" t="n">
+        <v>6</v>
+      </c>
+      <c r="V313" t="n">
+        <v>5</v>
+      </c>
+      <c r="W313" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X313" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:40:25</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>87</v>
+      </c>
+      <c r="C314" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D314" t="n">
+        <v>190</v>
+      </c>
+      <c r="E314" t="n">
+        <v>172</v>
+      </c>
+      <c r="F314" t="n">
+        <v>29</v>
+      </c>
+      <c r="G314" t="n">
+        <v>25</v>
+      </c>
+      <c r="H314" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I314" t="n">
+        <v>80</v>
+      </c>
+      <c r="J314" t="n">
+        <v>70</v>
+      </c>
+      <c r="K314" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L314" t="n">
+        <v>29</v>
+      </c>
+      <c r="M314" t="n">
+        <v>25</v>
+      </c>
+      <c r="N314" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="O314" t="n">
+        <v>91</v>
+      </c>
+      <c r="P314" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R314" t="n">
+        <v>22</v>
+      </c>
+      <c r="S314" t="n">
+        <v>19</v>
+      </c>
+      <c r="T314" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U314" t="n">
+        <v>6</v>
+      </c>
+      <c r="V314" t="n">
+        <v>5</v>
+      </c>
+      <c r="W314" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X314" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:42:25</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="C315" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D315" t="n">
+        <v>191</v>
+      </c>
+      <c r="E315" t="n">
+        <v>173</v>
+      </c>
+      <c r="F315" t="n">
+        <v>29</v>
+      </c>
+      <c r="G315" t="n">
+        <v>25</v>
+      </c>
+      <c r="H315" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I315" t="n">
+        <v>80</v>
+      </c>
+      <c r="J315" t="n">
+        <v>70</v>
+      </c>
+      <c r="K315" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L315" t="n">
+        <v>29</v>
+      </c>
+      <c r="M315" t="n">
+        <v>25</v>
+      </c>
+      <c r="N315" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="O315" t="n">
+        <v>92</v>
+      </c>
+      <c r="P315" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R315" t="n">
+        <v>22</v>
+      </c>
+      <c r="S315" t="n">
+        <v>19</v>
+      </c>
+      <c r="T315" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U315" t="n">
+        <v>6</v>
+      </c>
+      <c r="V315" t="n">
+        <v>5</v>
+      </c>
+      <c r="W315" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X315" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:44:26</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="C316" t="n">
+        <v>86.77</v>
+      </c>
+      <c r="D316" t="n">
+        <v>191</v>
+      </c>
+      <c r="E316" t="n">
+        <v>173</v>
+      </c>
+      <c r="F316" t="n">
+        <v>29</v>
+      </c>
+      <c r="G316" t="n">
+        <v>25</v>
+      </c>
+      <c r="H316" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I316" t="n">
+        <v>80</v>
+      </c>
+      <c r="J316" t="n">
+        <v>70</v>
+      </c>
+      <c r="K316" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L316" t="n">
+        <v>29</v>
+      </c>
+      <c r="M316" t="n">
+        <v>25</v>
+      </c>
+      <c r="N316" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="O316" t="n">
+        <v>92</v>
+      </c>
+      <c r="P316" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="R316" t="n">
+        <v>22</v>
+      </c>
+      <c r="S316" t="n">
+        <v>19</v>
+      </c>
+      <c r="T316" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U316" t="n">
+        <v>6</v>
+      </c>
+      <c r="V316" t="n">
+        <v>5</v>
+      </c>
+      <c r="W316" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X316" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:45:08</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="C317" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="D317" t="n">
+        <v>193</v>
+      </c>
+      <c r="E317" t="n">
+        <v>175</v>
+      </c>
+      <c r="F317" t="n">
+        <v>30</v>
+      </c>
+      <c r="G317" t="n">
+        <v>26</v>
+      </c>
+      <c r="H317" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="I317" t="n">
+        <v>81</v>
+      </c>
+      <c r="J317" t="n">
+        <v>71</v>
+      </c>
+      <c r="K317" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L317" t="n">
+        <v>29</v>
+      </c>
+      <c r="M317" t="n">
+        <v>25</v>
+      </c>
+      <c r="N317" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="O317" t="n">
+        <v>93</v>
+      </c>
+      <c r="P317" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="R317" t="n">
+        <v>23</v>
+      </c>
+      <c r="S317" t="n">
+        <v>20</v>
+      </c>
+      <c r="T317" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U317" t="n">
+        <v>6</v>
+      </c>
+      <c r="V317" t="n">
+        <v>5</v>
+      </c>
+      <c r="W317" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X317" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:46:58</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="C318" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="D318" t="n">
+        <v>193</v>
+      </c>
+      <c r="E318" t="n">
+        <v>175</v>
+      </c>
+      <c r="F318" t="n">
+        <v>30</v>
+      </c>
+      <c r="G318" t="n">
+        <v>26</v>
+      </c>
+      <c r="H318" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="I318" t="n">
+        <v>81</v>
+      </c>
+      <c r="J318" t="n">
+        <v>71</v>
+      </c>
+      <c r="K318" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L318" t="n">
+        <v>29</v>
+      </c>
+      <c r="M318" t="n">
+        <v>25</v>
+      </c>
+      <c r="N318" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="O318" t="n">
+        <v>93</v>
+      </c>
+      <c r="P318" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="R318" t="n">
+        <v>23</v>
+      </c>
+      <c r="S318" t="n">
+        <v>20</v>
+      </c>
+      <c r="T318" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U318" t="n">
+        <v>6</v>
+      </c>
+      <c r="V318" t="n">
+        <v>5</v>
+      </c>
+      <c r="W318" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X318" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:48:58</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>87.48999999999999</v>
+      </c>
+      <c r="C319" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="D319" t="n">
+        <v>194</v>
+      </c>
+      <c r="E319" t="n">
+        <v>176</v>
+      </c>
+      <c r="F319" t="n">
+        <v>31</v>
+      </c>
+      <c r="G319" t="n">
+        <v>27</v>
+      </c>
+      <c r="H319" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I319" t="n">
+        <v>82</v>
+      </c>
+      <c r="J319" t="n">
+        <v>72</v>
+      </c>
+      <c r="K319" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L319" t="n">
+        <v>29</v>
+      </c>
+      <c r="M319" t="n">
+        <v>25</v>
+      </c>
+      <c r="N319" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="O319" t="n">
+        <v>93</v>
+      </c>
+      <c r="P319" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="R319" t="n">
+        <v>24</v>
+      </c>
+      <c r="S319" t="n">
+        <v>21</v>
+      </c>
+      <c r="T319" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U319" t="n">
+        <v>6</v>
+      </c>
+      <c r="V319" t="n">
+        <v>5</v>
+      </c>
+      <c r="W319" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X319" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:50:58</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="C320" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="D320" t="n">
+        <v>195</v>
+      </c>
+      <c r="E320" t="n">
+        <v>177</v>
+      </c>
+      <c r="F320" t="n">
+        <v>31</v>
+      </c>
+      <c r="G320" t="n">
+        <v>27</v>
+      </c>
+      <c r="H320" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I320" t="n">
+        <v>82</v>
+      </c>
+      <c r="J320" t="n">
+        <v>72</v>
+      </c>
+      <c r="K320" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L320" t="n">
+        <v>29</v>
+      </c>
+      <c r="M320" t="n">
+        <v>25</v>
+      </c>
+      <c r="N320" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="O320" t="n">
+        <v>94</v>
+      </c>
+      <c r="P320" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="R320" t="n">
+        <v>24</v>
+      </c>
+      <c r="S320" t="n">
+        <v>21</v>
+      </c>
+      <c r="T320" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U320" t="n">
+        <v>6</v>
+      </c>
+      <c r="V320" t="n">
+        <v>5</v>
+      </c>
+      <c r="W320" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X320" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:52:59</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="C321" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="D321" t="n">
+        <v>196</v>
+      </c>
+      <c r="E321" t="n">
+        <v>178</v>
+      </c>
+      <c r="F321" t="n">
+        <v>31</v>
+      </c>
+      <c r="G321" t="n">
+        <v>27</v>
+      </c>
+      <c r="H321" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I321" t="n">
+        <v>82</v>
+      </c>
+      <c r="J321" t="n">
+        <v>72</v>
+      </c>
+      <c r="K321" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L321" t="n">
+        <v>29</v>
+      </c>
+      <c r="M321" t="n">
+        <v>25</v>
+      </c>
+      <c r="N321" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="O321" t="n">
+        <v>95</v>
+      </c>
+      <c r="P321" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="R321" t="n">
+        <v>24</v>
+      </c>
+      <c r="S321" t="n">
+        <v>21</v>
+      </c>
+      <c r="T321" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U321" t="n">
+        <v>6</v>
+      </c>
+      <c r="V321" t="n">
+        <v>5</v>
+      </c>
+      <c r="W321" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X321" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:54:58</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C322" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D322" t="n">
+        <v>198</v>
+      </c>
+      <c r="E322" t="n">
+        <v>180</v>
+      </c>
+      <c r="F322" t="n">
+        <v>32</v>
+      </c>
+      <c r="G322" t="n">
+        <v>28</v>
+      </c>
+      <c r="H322" t="n">
+        <v>86</v>
+      </c>
+      <c r="I322" t="n">
+        <v>83</v>
+      </c>
+      <c r="J322" t="n">
+        <v>73</v>
+      </c>
+      <c r="K322" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L322" t="n">
+        <v>29</v>
+      </c>
+      <c r="M322" t="n">
+        <v>25</v>
+      </c>
+      <c r="N322" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="O322" t="n">
+        <v>96</v>
+      </c>
+      <c r="P322" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R322" t="n">
+        <v>25</v>
+      </c>
+      <c r="S322" t="n">
+        <v>22</v>
+      </c>
+      <c r="T322" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U322" t="n">
+        <v>6</v>
+      </c>
+      <c r="V322" t="n">
+        <v>5</v>
+      </c>
+      <c r="W322" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X322" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:56:58</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C323" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D323" t="n">
+        <v>199</v>
+      </c>
+      <c r="E323" t="n">
+        <v>181</v>
+      </c>
+      <c r="F323" t="n">
+        <v>32</v>
+      </c>
+      <c r="G323" t="n">
+        <v>28</v>
+      </c>
+      <c r="H323" t="n">
+        <v>86</v>
+      </c>
+      <c r="I323" t="n">
+        <v>84</v>
+      </c>
+      <c r="J323" t="n">
+        <v>74</v>
+      </c>
+      <c r="K323" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L323" t="n">
+        <v>29</v>
+      </c>
+      <c r="M323" t="n">
+        <v>25</v>
+      </c>
+      <c r="N323" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="O323" t="n">
+        <v>96</v>
+      </c>
+      <c r="P323" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R323" t="n">
+        <v>25</v>
+      </c>
+      <c r="S323" t="n">
+        <v>22</v>
+      </c>
+      <c r="T323" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U323" t="n">
+        <v>6</v>
+      </c>
+      <c r="V323" t="n">
+        <v>5</v>
+      </c>
+      <c r="W323" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X323" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:58:59</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C324" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D324" t="n">
+        <v>199</v>
+      </c>
+      <c r="E324" t="n">
+        <v>181</v>
+      </c>
+      <c r="F324" t="n">
+        <v>32</v>
+      </c>
+      <c r="G324" t="n">
+        <v>28</v>
+      </c>
+      <c r="H324" t="n">
+        <v>86</v>
+      </c>
+      <c r="I324" t="n">
+        <v>84</v>
+      </c>
+      <c r="J324" t="n">
+        <v>74</v>
+      </c>
+      <c r="K324" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L324" t="n">
+        <v>29</v>
+      </c>
+      <c r="M324" t="n">
+        <v>25</v>
+      </c>
+      <c r="N324" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="O324" t="n">
+        <v>96</v>
+      </c>
+      <c r="P324" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R324" t="n">
+        <v>25</v>
+      </c>
+      <c r="S324" t="n">
+        <v>22</v>
+      </c>
+      <c r="T324" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U324" t="n">
+        <v>6</v>
+      </c>
+      <c r="V324" t="n">
+        <v>5</v>
+      </c>
+      <c r="W324" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X324" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:01:01</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>88.69</v>
+      </c>
+      <c r="C325" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D325" t="n">
+        <v>201</v>
+      </c>
+      <c r="E325" t="n">
+        <v>183</v>
+      </c>
+      <c r="F325" t="n">
+        <v>32</v>
+      </c>
+      <c r="G325" t="n">
+        <v>28</v>
+      </c>
+      <c r="H325" t="n">
+        <v>86</v>
+      </c>
+      <c r="I325" t="n">
+        <v>84</v>
+      </c>
+      <c r="J325" t="n">
+        <v>74</v>
+      </c>
+      <c r="K325" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L325" t="n">
+        <v>30</v>
+      </c>
+      <c r="M325" t="n">
+        <v>26</v>
+      </c>
+      <c r="N325" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="O325" t="n">
+        <v>97</v>
+      </c>
+      <c r="P325" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R325" t="n">
+        <v>25</v>
+      </c>
+      <c r="S325" t="n">
+        <v>22</v>
+      </c>
+      <c r="T325" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U325" t="n">
+        <v>6</v>
+      </c>
+      <c r="V325" t="n">
+        <v>5</v>
+      </c>
+      <c r="W325" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X325" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:03:02</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="C326" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D326" t="n">
+        <v>202</v>
+      </c>
+      <c r="E326" t="n">
+        <v>184</v>
+      </c>
+      <c r="F326" t="n">
+        <v>32</v>
+      </c>
+      <c r="G326" t="n">
+        <v>28</v>
+      </c>
+      <c r="H326" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="I326" t="n">
+        <v>85</v>
+      </c>
+      <c r="J326" t="n">
+        <v>75</v>
+      </c>
+      <c r="K326" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L326" t="n">
+        <v>30</v>
+      </c>
+      <c r="M326" t="n">
+        <v>26</v>
+      </c>
+      <c r="N326" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="O326" t="n">
+        <v>97</v>
+      </c>
+      <c r="P326" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R326" t="n">
+        <v>25</v>
+      </c>
+      <c r="S326" t="n">
+        <v>22</v>
+      </c>
+      <c r="T326" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U326" t="n">
+        <v>6</v>
+      </c>
+      <c r="V326" t="n">
+        <v>5</v>
+      </c>
+      <c r="W326" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X326" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:05:01</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="C327" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D327" t="n">
+        <v>202</v>
+      </c>
+      <c r="E327" t="n">
+        <v>184</v>
+      </c>
+      <c r="F327" t="n">
+        <v>32</v>
+      </c>
+      <c r="G327" t="n">
+        <v>28</v>
+      </c>
+      <c r="H327" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="I327" t="n">
+        <v>85</v>
+      </c>
+      <c r="J327" t="n">
+        <v>75</v>
+      </c>
+      <c r="K327" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L327" t="n">
+        <v>30</v>
+      </c>
+      <c r="M327" t="n">
+        <v>26</v>
+      </c>
+      <c r="N327" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="O327" t="n">
+        <v>97</v>
+      </c>
+      <c r="P327" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R327" t="n">
+        <v>25</v>
+      </c>
+      <c r="S327" t="n">
+        <v>22</v>
+      </c>
+      <c r="T327" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U327" t="n">
+        <v>6</v>
+      </c>
+      <c r="V327" t="n">
+        <v>5</v>
+      </c>
+      <c r="W327" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X327" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:07:02</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="C328" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="D328" t="n">
+        <v>202</v>
+      </c>
+      <c r="E328" t="n">
+        <v>184</v>
+      </c>
+      <c r="F328" t="n">
+        <v>32</v>
+      </c>
+      <c r="G328" t="n">
+        <v>28</v>
+      </c>
+      <c r="H328" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="I328" t="n">
+        <v>85</v>
+      </c>
+      <c r="J328" t="n">
+        <v>75</v>
+      </c>
+      <c r="K328" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="L328" t="n">
+        <v>30</v>
+      </c>
+      <c r="M328" t="n">
+        <v>26</v>
+      </c>
+      <c r="N328" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="O328" t="n">
+        <v>97</v>
+      </c>
+      <c r="P328" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="R328" t="n">
+        <v>25</v>
+      </c>
+      <c r="S328" t="n">
+        <v>22</v>
+      </c>
+      <c r="T328" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U328" t="n">
+        <v>6</v>
+      </c>
+      <c r="V328" t="n">
+        <v>5</v>
+      </c>
+      <c r="W328" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="X328" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:42:01</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="C329" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D329" t="n">
+        <v>252</v>
+      </c>
+      <c r="E329" t="n">
+        <v>232</v>
+      </c>
+      <c r="F329" t="n">
+        <v>45</v>
+      </c>
+      <c r="G329" t="n">
+        <v>40</v>
+      </c>
+      <c r="H329" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I329" t="n">
+        <v>102</v>
+      </c>
+      <c r="J329" t="n">
+        <v>92</v>
+      </c>
+      <c r="K329" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L329" t="n">
+        <v>39</v>
+      </c>
+      <c r="M329" t="n">
+        <v>34</v>
+      </c>
+      <c r="N329" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="O329" t="n">
+        <v>126</v>
+      </c>
+      <c r="P329" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R329" t="n">
+        <v>33</v>
+      </c>
+      <c r="S329" t="n">
+        <v>29</v>
+      </c>
+      <c r="T329" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U329" t="n">
+        <v>9</v>
+      </c>
+      <c r="V329" t="n">
+        <v>6</v>
+      </c>
+      <c r="W329" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X329" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:49:46</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="C330" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D330" t="n">
+        <v>260</v>
+      </c>
+      <c r="E330" t="n">
+        <v>241</v>
+      </c>
+      <c r="F330" t="n">
+        <v>45</v>
+      </c>
+      <c r="G330" t="n">
+        <v>40</v>
+      </c>
+      <c r="H330" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I330" t="n">
+        <v>104</v>
+      </c>
+      <c r="J330" t="n">
+        <v>94</v>
+      </c>
+      <c r="K330" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L330" t="n">
+        <v>40</v>
+      </c>
+      <c r="M330" t="n">
+        <v>36</v>
+      </c>
+      <c r="N330" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="O330" t="n">
+        <v>131</v>
+      </c>
+      <c r="P330" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R330" t="n">
+        <v>33</v>
+      </c>
+      <c r="S330" t="n">
+        <v>29</v>
+      </c>
+      <c r="T330" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U330" t="n">
+        <v>9</v>
+      </c>
+      <c r="V330" t="n">
+        <v>6</v>
+      </c>
+      <c r="W330" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X330" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:51:46</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="C331" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D331" t="n">
+        <v>260</v>
+      </c>
+      <c r="E331" t="n">
+        <v>241</v>
+      </c>
+      <c r="F331" t="n">
+        <v>45</v>
+      </c>
+      <c r="G331" t="n">
+        <v>40</v>
+      </c>
+      <c r="H331" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I331" t="n">
+        <v>104</v>
+      </c>
+      <c r="J331" t="n">
+        <v>94</v>
+      </c>
+      <c r="K331" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L331" t="n">
+        <v>40</v>
+      </c>
+      <c r="M331" t="n">
+        <v>36</v>
+      </c>
+      <c r="N331" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="O331" t="n">
+        <v>131</v>
+      </c>
+      <c r="P331" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R331" t="n">
+        <v>33</v>
+      </c>
+      <c r="S331" t="n">
+        <v>29</v>
+      </c>
+      <c r="T331" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U331" t="n">
+        <v>9</v>
+      </c>
+      <c r="V331" t="n">
+        <v>6</v>
+      </c>
+      <c r="W331" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X331" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:53:48</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="C332" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D332" t="n">
+        <v>262</v>
+      </c>
+      <c r="E332" t="n">
+        <v>243</v>
+      </c>
+      <c r="F332" t="n">
+        <v>45</v>
+      </c>
+      <c r="G332" t="n">
+        <v>40</v>
+      </c>
+      <c r="H332" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I332" t="n">
+        <v>106</v>
+      </c>
+      <c r="J332" t="n">
+        <v>96</v>
+      </c>
+      <c r="K332" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L332" t="n">
+        <v>41</v>
+      </c>
+      <c r="M332" t="n">
+        <v>37</v>
+      </c>
+      <c r="N332" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="O332" t="n">
+        <v>131</v>
+      </c>
+      <c r="P332" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R332" t="n">
+        <v>33</v>
+      </c>
+      <c r="S332" t="n">
+        <v>29</v>
+      </c>
+      <c r="T332" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U332" t="n">
+        <v>9</v>
+      </c>
+      <c r="V332" t="n">
+        <v>6</v>
+      </c>
+      <c r="W332" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:55:47</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="C333" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D333" t="n">
+        <v>263</v>
+      </c>
+      <c r="E333" t="n">
+        <v>244</v>
+      </c>
+      <c r="F333" t="n">
+        <v>45</v>
+      </c>
+      <c r="G333" t="n">
+        <v>40</v>
+      </c>
+      <c r="H333" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I333" t="n">
+        <v>106</v>
+      </c>
+      <c r="J333" t="n">
+        <v>96</v>
+      </c>
+      <c r="K333" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L333" t="n">
+        <v>41</v>
+      </c>
+      <c r="M333" t="n">
+        <v>37</v>
+      </c>
+      <c r="N333" t="n">
+        <v>93.93000000000001</v>
+      </c>
+      <c r="O333" t="n">
+        <v>132</v>
+      </c>
+      <c r="P333" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R333" t="n">
+        <v>33</v>
+      </c>
+      <c r="S333" t="n">
+        <v>29</v>
+      </c>
+      <c r="T333" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U333" t="n">
+        <v>9</v>
+      </c>
+      <c r="V333" t="n">
+        <v>6</v>
+      </c>
+      <c r="W333" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X333" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:57:47</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="C334" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D334" t="n">
+        <v>264</v>
+      </c>
+      <c r="E334" t="n">
+        <v>245</v>
+      </c>
+      <c r="F334" t="n">
+        <v>45</v>
+      </c>
+      <c r="G334" t="n">
+        <v>40</v>
+      </c>
+      <c r="H334" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I334" t="n">
+        <v>106</v>
+      </c>
+      <c r="J334" t="n">
+        <v>96</v>
+      </c>
+      <c r="K334" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L334" t="n">
+        <v>41</v>
+      </c>
+      <c r="M334" t="n">
+        <v>37</v>
+      </c>
+      <c r="N334" t="n">
+        <v>93.93000000000001</v>
+      </c>
+      <c r="O334" t="n">
+        <v>133</v>
+      </c>
+      <c r="P334" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R334" t="n">
+        <v>33</v>
+      </c>
+      <c r="S334" t="n">
+        <v>29</v>
+      </c>
+      <c r="T334" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U334" t="n">
+        <v>9</v>
+      </c>
+      <c r="V334" t="n">
+        <v>6</v>
+      </c>
+      <c r="W334" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X334" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:59:46</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>91.61</v>
+      </c>
+      <c r="C335" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D335" t="n">
+        <v>266</v>
+      </c>
+      <c r="E335" t="n">
+        <v>247</v>
+      </c>
+      <c r="F335" t="n">
+        <v>45</v>
+      </c>
+      <c r="G335" t="n">
+        <v>40</v>
+      </c>
+      <c r="H335" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I335" t="n">
+        <v>107</v>
+      </c>
+      <c r="J335" t="n">
+        <v>97</v>
+      </c>
+      <c r="K335" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L335" t="n">
+        <v>41</v>
+      </c>
+      <c r="M335" t="n">
+        <v>37</v>
+      </c>
+      <c r="N335" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="O335" t="n">
+        <v>134</v>
+      </c>
+      <c r="P335" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R335" t="n">
+        <v>33</v>
+      </c>
+      <c r="S335" t="n">
+        <v>29</v>
+      </c>
+      <c r="T335" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U335" t="n">
+        <v>9</v>
+      </c>
+      <c r="V335" t="n">
+        <v>6</v>
+      </c>
+      <c r="W335" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X335" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:01:46</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>91.61</v>
+      </c>
+      <c r="C336" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D336" t="n">
+        <v>268</v>
+      </c>
+      <c r="E336" t="n">
+        <v>249</v>
+      </c>
+      <c r="F336" t="n">
+        <v>45</v>
+      </c>
+      <c r="G336" t="n">
+        <v>40</v>
+      </c>
+      <c r="H336" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I336" t="n">
+        <v>107</v>
+      </c>
+      <c r="J336" t="n">
+        <v>97</v>
+      </c>
+      <c r="K336" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L336" t="n">
+        <v>41</v>
+      </c>
+      <c r="M336" t="n">
+        <v>37</v>
+      </c>
+      <c r="N336" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="O336" t="n">
+        <v>136</v>
+      </c>
+      <c r="P336" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R336" t="n">
+        <v>33</v>
+      </c>
+      <c r="S336" t="n">
+        <v>29</v>
+      </c>
+      <c r="T336" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U336" t="n">
+        <v>9</v>
+      </c>
+      <c r="V336" t="n">
+        <v>6</v>
+      </c>
+      <c r="W336" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X336" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:03:48</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="C337" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D337" t="n">
+        <v>270</v>
+      </c>
+      <c r="E337" t="n">
+        <v>251</v>
+      </c>
+      <c r="F337" t="n">
+        <v>45</v>
+      </c>
+      <c r="G337" t="n">
+        <v>40</v>
+      </c>
+      <c r="H337" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I337" t="n">
+        <v>107</v>
+      </c>
+      <c r="J337" t="n">
+        <v>97</v>
+      </c>
+      <c r="K337" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L337" t="n">
+        <v>41</v>
+      </c>
+      <c r="M337" t="n">
+        <v>37</v>
+      </c>
+      <c r="N337" t="n">
+        <v>94.02</v>
+      </c>
+      <c r="O337" t="n">
+        <v>138</v>
+      </c>
+      <c r="P337" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R337" t="n">
+        <v>33</v>
+      </c>
+      <c r="S337" t="n">
+        <v>29</v>
+      </c>
+      <c r="T337" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U337" t="n">
+        <v>9</v>
+      </c>
+      <c r="V337" t="n">
+        <v>6</v>
+      </c>
+      <c r="W337" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X337" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:05:46</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="C338" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D338" t="n">
+        <v>272</v>
+      </c>
+      <c r="E338" t="n">
+        <v>253</v>
+      </c>
+      <c r="F338" t="n">
+        <v>45</v>
+      </c>
+      <c r="G338" t="n">
+        <v>40</v>
+      </c>
+      <c r="H338" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I338" t="n">
+        <v>107</v>
+      </c>
+      <c r="J338" t="n">
+        <v>97</v>
+      </c>
+      <c r="K338" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L338" t="n">
+        <v>41</v>
+      </c>
+      <c r="M338" t="n">
+        <v>37</v>
+      </c>
+      <c r="N338" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="O338" t="n">
+        <v>140</v>
+      </c>
+      <c r="P338" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R338" t="n">
+        <v>33</v>
+      </c>
+      <c r="S338" t="n">
+        <v>29</v>
+      </c>
+      <c r="T338" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U338" t="n">
+        <v>9</v>
+      </c>
+      <c r="V338" t="n">
+        <v>6</v>
+      </c>
+      <c r="W338" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X338" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:07:47</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="C339" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D339" t="n">
+        <v>272</v>
+      </c>
+      <c r="E339" t="n">
+        <v>253</v>
+      </c>
+      <c r="F339" t="n">
+        <v>45</v>
+      </c>
+      <c r="G339" t="n">
+        <v>40</v>
+      </c>
+      <c r="H339" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I339" t="n">
+        <v>107</v>
+      </c>
+      <c r="J339" t="n">
+        <v>97</v>
+      </c>
+      <c r="K339" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L339" t="n">
+        <v>41</v>
+      </c>
+      <c r="M339" t="n">
+        <v>37</v>
+      </c>
+      <c r="N339" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="O339" t="n">
+        <v>140</v>
+      </c>
+      <c r="P339" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R339" t="n">
+        <v>33</v>
+      </c>
+      <c r="S339" t="n">
+        <v>29</v>
+      </c>
+      <c r="T339" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U339" t="n">
+        <v>9</v>
+      </c>
+      <c r="V339" t="n">
+        <v>6</v>
+      </c>
+      <c r="W339" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X339" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:09:46</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="C340" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D340" t="n">
+        <v>274</v>
+      </c>
+      <c r="E340" t="n">
+        <v>255</v>
+      </c>
+      <c r="F340" t="n">
+        <v>45</v>
+      </c>
+      <c r="G340" t="n">
+        <v>40</v>
+      </c>
+      <c r="H340" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I340" t="n">
+        <v>107</v>
+      </c>
+      <c r="J340" t="n">
+        <v>97</v>
+      </c>
+      <c r="K340" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L340" t="n">
+        <v>41</v>
+      </c>
+      <c r="M340" t="n">
+        <v>37</v>
+      </c>
+      <c r="N340" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="O340" t="n">
+        <v>142</v>
+      </c>
+      <c r="P340" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R340" t="n">
+        <v>33</v>
+      </c>
+      <c r="S340" t="n">
+        <v>29</v>
+      </c>
+      <c r="T340" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U340" t="n">
+        <v>9</v>
+      </c>
+      <c r="V340" t="n">
+        <v>6</v>
+      </c>
+      <c r="W340" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X340" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:11:46</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="C341" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D341" t="n">
+        <v>275</v>
+      </c>
+      <c r="E341" t="n">
+        <v>256</v>
+      </c>
+      <c r="F341" t="n">
+        <v>45</v>
+      </c>
+      <c r="G341" t="n">
+        <v>40</v>
+      </c>
+      <c r="H341" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I341" t="n">
+        <v>108</v>
+      </c>
+      <c r="J341" t="n">
+        <v>98</v>
+      </c>
+      <c r="K341" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="L341" t="n">
+        <v>41</v>
+      </c>
+      <c r="M341" t="n">
+        <v>37</v>
+      </c>
+      <c r="N341" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="O341" t="n">
+        <v>142</v>
+      </c>
+      <c r="P341" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R341" t="n">
+        <v>33</v>
+      </c>
+      <c r="S341" t="n">
+        <v>29</v>
+      </c>
+      <c r="T341" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="U341" t="n">
+        <v>9</v>
+      </c>
+      <c r="V341" t="n">
+        <v>6</v>
+      </c>
+      <c r="W341" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X341" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:13:40</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="C342" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="D342" t="n">
+        <v>276</v>
+      </c>
+      <c r="E342" t="n">
+        <v>257</v>
+      </c>
+      <c r="F342" t="n">
+        <v>46</v>
+      </c>
+      <c r="G342" t="n">
+        <v>41</v>
+      </c>
+      <c r="H342" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I342" t="n">
+        <v>109</v>
+      </c>
+      <c r="J342" t="n">
+        <v>99</v>
+      </c>
+      <c r="K342" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L342" t="n">
+        <v>42</v>
+      </c>
+      <c r="M342" t="n">
+        <v>38</v>
+      </c>
+      <c r="N342" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="O342" t="n">
+        <v>142</v>
+      </c>
+      <c r="P342" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R342" t="n">
+        <v>34</v>
+      </c>
+      <c r="S342" t="n">
+        <v>30</v>
+      </c>
+      <c r="T342" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U342" t="n">
+        <v>10</v>
+      </c>
+      <c r="V342" t="n">
+        <v>7</v>
+      </c>
+      <c r="W342" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X342" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:13:41</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="C343" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="D343" t="n">
+        <v>276</v>
+      </c>
+      <c r="E343" t="n">
+        <v>257</v>
+      </c>
+      <c r="F343" t="n">
+        <v>46</v>
+      </c>
+      <c r="G343" t="n">
+        <v>41</v>
+      </c>
+      <c r="H343" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I343" t="n">
+        <v>109</v>
+      </c>
+      <c r="J343" t="n">
+        <v>99</v>
+      </c>
+      <c r="K343" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L343" t="n">
+        <v>42</v>
+      </c>
+      <c r="M343" t="n">
+        <v>38</v>
+      </c>
+      <c r="N343" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="O343" t="n">
+        <v>142</v>
+      </c>
+      <c r="P343" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R343" t="n">
+        <v>34</v>
+      </c>
+      <c r="S343" t="n">
+        <v>30</v>
+      </c>
+      <c r="T343" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U343" t="n">
+        <v>10</v>
+      </c>
+      <c r="V343" t="n">
+        <v>7</v>
+      </c>
+      <c r="W343" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X343" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:13:47</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="C344" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="D344" t="n">
+        <v>276</v>
+      </c>
+      <c r="E344" t="n">
+        <v>257</v>
+      </c>
+      <c r="F344" t="n">
+        <v>46</v>
+      </c>
+      <c r="G344" t="n">
+        <v>41</v>
+      </c>
+      <c r="H344" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I344" t="n">
+        <v>109</v>
+      </c>
+      <c r="J344" t="n">
+        <v>99</v>
+      </c>
+      <c r="K344" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L344" t="n">
+        <v>42</v>
+      </c>
+      <c r="M344" t="n">
+        <v>38</v>
+      </c>
+      <c r="N344" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="O344" t="n">
+        <v>142</v>
+      </c>
+      <c r="P344" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R344" t="n">
+        <v>34</v>
+      </c>
+      <c r="S344" t="n">
+        <v>30</v>
+      </c>
+      <c r="T344" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U344" t="n">
+        <v>10</v>
+      </c>
+      <c r="V344" t="n">
+        <v>7</v>
+      </c>
+      <c r="W344" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X344" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:15:46</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C345" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D345" t="n">
+        <v>277</v>
+      </c>
+      <c r="E345" t="n">
+        <v>258</v>
+      </c>
+      <c r="F345" t="n">
+        <v>47</v>
+      </c>
+      <c r="G345" t="n">
+        <v>42</v>
+      </c>
+      <c r="H345" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I345" t="n">
+        <v>109</v>
+      </c>
+      <c r="J345" t="n">
+        <v>99</v>
+      </c>
+      <c r="K345" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L345" t="n">
+        <v>42</v>
+      </c>
+      <c r="M345" t="n">
+        <v>38</v>
+      </c>
+      <c r="N345" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="O345" t="n">
+        <v>143</v>
+      </c>
+      <c r="P345" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R345" t="n">
+        <v>34</v>
+      </c>
+      <c r="S345" t="n">
+        <v>30</v>
+      </c>
+      <c r="T345" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U345" t="n">
+        <v>10</v>
+      </c>
+      <c r="V345" t="n">
+        <v>7</v>
+      </c>
+      <c r="W345" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X345" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:17:46</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C346" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D346" t="n">
+        <v>278</v>
+      </c>
+      <c r="E346" t="n">
+        <v>259</v>
+      </c>
+      <c r="F346" t="n">
+        <v>47</v>
+      </c>
+      <c r="G346" t="n">
+        <v>42</v>
+      </c>
+      <c r="H346" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I346" t="n">
+        <v>110</v>
+      </c>
+      <c r="J346" t="n">
+        <v>100</v>
+      </c>
+      <c r="K346" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L346" t="n">
+        <v>42</v>
+      </c>
+      <c r="M346" t="n">
+        <v>38</v>
+      </c>
+      <c r="N346" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="O346" t="n">
+        <v>143</v>
+      </c>
+      <c r="P346" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R346" t="n">
+        <v>34</v>
+      </c>
+      <c r="S346" t="n">
+        <v>30</v>
+      </c>
+      <c r="T346" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U346" t="n">
+        <v>10</v>
+      </c>
+      <c r="V346" t="n">
+        <v>7</v>
+      </c>
+      <c r="W346" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X346" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:19:46</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C347" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D347" t="n">
+        <v>279</v>
+      </c>
+      <c r="E347" t="n">
+        <v>260</v>
+      </c>
+      <c r="F347" t="n">
+        <v>47</v>
+      </c>
+      <c r="G347" t="n">
+        <v>42</v>
+      </c>
+      <c r="H347" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I347" t="n">
+        <v>110</v>
+      </c>
+      <c r="J347" t="n">
+        <v>100</v>
+      </c>
+      <c r="K347" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L347" t="n">
+        <v>42</v>
+      </c>
+      <c r="M347" t="n">
+        <v>38</v>
+      </c>
+      <c r="N347" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="O347" t="n">
+        <v>144</v>
+      </c>
+      <c r="P347" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R347" t="n">
+        <v>34</v>
+      </c>
+      <c r="S347" t="n">
+        <v>30</v>
+      </c>
+      <c r="T347" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U347" t="n">
+        <v>10</v>
+      </c>
+      <c r="V347" t="n">
+        <v>7</v>
+      </c>
+      <c r="W347" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X347" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:21:46</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C348" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D348" t="n">
+        <v>279</v>
+      </c>
+      <c r="E348" t="n">
+        <v>260</v>
+      </c>
+      <c r="F348" t="n">
+        <v>47</v>
+      </c>
+      <c r="G348" t="n">
+        <v>42</v>
+      </c>
+      <c r="H348" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I348" t="n">
+        <v>110</v>
+      </c>
+      <c r="J348" t="n">
+        <v>100</v>
+      </c>
+      <c r="K348" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L348" t="n">
+        <v>42</v>
+      </c>
+      <c r="M348" t="n">
+        <v>38</v>
+      </c>
+      <c r="N348" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="O348" t="n">
+        <v>144</v>
+      </c>
+      <c r="P348" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R348" t="n">
+        <v>34</v>
+      </c>
+      <c r="S348" t="n">
+        <v>30</v>
+      </c>
+      <c r="T348" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U348" t="n">
+        <v>10</v>
+      </c>
+      <c r="V348" t="n">
+        <v>7</v>
+      </c>
+      <c r="W348" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X348" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:23:47</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C349" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D349" t="n">
+        <v>280</v>
+      </c>
+      <c r="E349" t="n">
+        <v>261</v>
+      </c>
+      <c r="F349" t="n">
+        <v>47</v>
+      </c>
+      <c r="G349" t="n">
+        <v>42</v>
+      </c>
+      <c r="H349" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I349" t="n">
+        <v>110</v>
+      </c>
+      <c r="J349" t="n">
+        <v>100</v>
+      </c>
+      <c r="K349" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L349" t="n">
+        <v>42</v>
+      </c>
+      <c r="M349" t="n">
+        <v>38</v>
+      </c>
+      <c r="N349" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="O349" t="n">
+        <v>145</v>
+      </c>
+      <c r="P349" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R349" t="n">
+        <v>34</v>
+      </c>
+      <c r="S349" t="n">
+        <v>30</v>
+      </c>
+      <c r="T349" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U349" t="n">
+        <v>10</v>
+      </c>
+      <c r="V349" t="n">
+        <v>7</v>
+      </c>
+      <c r="W349" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X349" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:25:46</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C350" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D350" t="n">
+        <v>280</v>
+      </c>
+      <c r="E350" t="n">
+        <v>261</v>
+      </c>
+      <c r="F350" t="n">
+        <v>47</v>
+      </c>
+      <c r="G350" t="n">
+        <v>42</v>
+      </c>
+      <c r="H350" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I350" t="n">
+        <v>110</v>
+      </c>
+      <c r="J350" t="n">
+        <v>100</v>
+      </c>
+      <c r="K350" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L350" t="n">
+        <v>42</v>
+      </c>
+      <c r="M350" t="n">
+        <v>38</v>
+      </c>
+      <c r="N350" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="O350" t="n">
+        <v>145</v>
+      </c>
+      <c r="P350" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R350" t="n">
+        <v>34</v>
+      </c>
+      <c r="S350" t="n">
+        <v>30</v>
+      </c>
+      <c r="T350" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U350" t="n">
+        <v>10</v>
+      </c>
+      <c r="V350" t="n">
+        <v>7</v>
+      </c>
+      <c r="W350" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X350" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:27:46</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="C351" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="D351" t="n">
+        <v>280</v>
+      </c>
+      <c r="E351" t="n">
+        <v>261</v>
+      </c>
+      <c r="F351" t="n">
+        <v>47</v>
+      </c>
+      <c r="G351" t="n">
+        <v>42</v>
+      </c>
+      <c r="H351" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I351" t="n">
+        <v>110</v>
+      </c>
+      <c r="J351" t="n">
+        <v>100</v>
+      </c>
+      <c r="K351" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L351" t="n">
+        <v>42</v>
+      </c>
+      <c r="M351" t="n">
+        <v>38</v>
+      </c>
+      <c r="N351" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="O351" t="n">
+        <v>145</v>
+      </c>
+      <c r="P351" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R351" t="n">
+        <v>34</v>
+      </c>
+      <c r="S351" t="n">
+        <v>30</v>
+      </c>
+      <c r="T351" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U351" t="n">
+        <v>10</v>
+      </c>
+      <c r="V351" t="n">
+        <v>7</v>
+      </c>
+      <c r="W351" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="X351" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:29:33</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C352" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D352" t="n">
+        <v>284</v>
+      </c>
+      <c r="E352" t="n">
+        <v>265</v>
+      </c>
+      <c r="F352" t="n">
+        <v>48</v>
+      </c>
+      <c r="G352" t="n">
+        <v>43</v>
+      </c>
+      <c r="H352" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I352" t="n">
+        <v>110</v>
+      </c>
+      <c r="J352" t="n">
+        <v>100</v>
+      </c>
+      <c r="K352" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L352" t="n">
+        <v>42</v>
+      </c>
+      <c r="M352" t="n">
+        <v>38</v>
+      </c>
+      <c r="N352" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="O352" t="n">
+        <v>149</v>
+      </c>
+      <c r="P352" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R352" t="n">
+        <v>34</v>
+      </c>
+      <c r="S352" t="n">
+        <v>30</v>
+      </c>
+      <c r="T352" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U352" t="n">
+        <v>10</v>
+      </c>
+      <c r="V352" t="n">
+        <v>7</v>
+      </c>
+      <c r="W352" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X352" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:31:30</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C353" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D353" t="n">
+        <v>285</v>
+      </c>
+      <c r="E353" t="n">
+        <v>266</v>
+      </c>
+      <c r="F353" t="n">
+        <v>48</v>
+      </c>
+      <c r="G353" t="n">
+        <v>43</v>
+      </c>
+      <c r="H353" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I353" t="n">
+        <v>111</v>
+      </c>
+      <c r="J353" t="n">
+        <v>101</v>
+      </c>
+      <c r="K353" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L353" t="n">
+        <v>42</v>
+      </c>
+      <c r="M353" t="n">
+        <v>38</v>
+      </c>
+      <c r="N353" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="O353" t="n">
+        <v>149</v>
+      </c>
+      <c r="P353" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R353" t="n">
+        <v>34</v>
+      </c>
+      <c r="S353" t="n">
+        <v>30</v>
+      </c>
+      <c r="T353" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U353" t="n">
+        <v>10</v>
+      </c>
+      <c r="V353" t="n">
+        <v>7</v>
+      </c>
+      <c r="W353" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X353" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:31:35</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C354" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D354" t="n">
+        <v>285</v>
+      </c>
+      <c r="E354" t="n">
+        <v>266</v>
+      </c>
+      <c r="F354" t="n">
+        <v>48</v>
+      </c>
+      <c r="G354" t="n">
+        <v>43</v>
+      </c>
+      <c r="H354" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I354" t="n">
+        <v>111</v>
+      </c>
+      <c r="J354" t="n">
+        <v>101</v>
+      </c>
+      <c r="K354" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L354" t="n">
+        <v>42</v>
+      </c>
+      <c r="M354" t="n">
+        <v>38</v>
+      </c>
+      <c r="N354" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="O354" t="n">
+        <v>149</v>
+      </c>
+      <c r="P354" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R354" t="n">
+        <v>34</v>
+      </c>
+      <c r="S354" t="n">
+        <v>30</v>
+      </c>
+      <c r="T354" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U354" t="n">
+        <v>10</v>
+      </c>
+      <c r="V354" t="n">
+        <v>7</v>
+      </c>
+      <c r="W354" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X354" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:33:33</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C355" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D355" t="n">
+        <v>285</v>
+      </c>
+      <c r="E355" t="n">
+        <v>266</v>
+      </c>
+      <c r="F355" t="n">
+        <v>48</v>
+      </c>
+      <c r="G355" t="n">
+        <v>43</v>
+      </c>
+      <c r="H355" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I355" t="n">
+        <v>111</v>
+      </c>
+      <c r="J355" t="n">
+        <v>101</v>
+      </c>
+      <c r="K355" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L355" t="n">
+        <v>42</v>
+      </c>
+      <c r="M355" t="n">
+        <v>38</v>
+      </c>
+      <c r="N355" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="O355" t="n">
+        <v>149</v>
+      </c>
+      <c r="P355" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R355" t="n">
+        <v>34</v>
+      </c>
+      <c r="S355" t="n">
+        <v>30</v>
+      </c>
+      <c r="T355" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U355" t="n">
+        <v>10</v>
+      </c>
+      <c r="V355" t="n">
+        <v>7</v>
+      </c>
+      <c r="W355" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X355" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:35:33</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C356" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D356" t="n">
+        <v>285</v>
+      </c>
+      <c r="E356" t="n">
+        <v>266</v>
+      </c>
+      <c r="F356" t="n">
+        <v>49</v>
+      </c>
+      <c r="G356" t="n">
+        <v>44</v>
+      </c>
+      <c r="H356" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I356" t="n">
+        <v>111</v>
+      </c>
+      <c r="J356" t="n">
+        <v>101</v>
+      </c>
+      <c r="K356" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L356" t="n">
+        <v>42</v>
+      </c>
+      <c r="M356" t="n">
+        <v>38</v>
+      </c>
+      <c r="N356" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="O356" t="n">
+        <v>149</v>
+      </c>
+      <c r="P356" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R356" t="n">
+        <v>35</v>
+      </c>
+      <c r="S356" t="n">
+        <v>31</v>
+      </c>
+      <c r="T356" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U356" t="n">
+        <v>11</v>
+      </c>
+      <c r="V356" t="n">
+        <v>8</v>
+      </c>
+      <c r="W356" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X356" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:37:34</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C357" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D357" t="n">
+        <v>288</v>
+      </c>
+      <c r="E357" t="n">
+        <v>269</v>
+      </c>
+      <c r="F357" t="n">
+        <v>49</v>
+      </c>
+      <c r="G357" t="n">
+        <v>44</v>
+      </c>
+      <c r="H357" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="I357" t="n">
+        <v>111</v>
+      </c>
+      <c r="J357" t="n">
+        <v>101</v>
+      </c>
+      <c r="K357" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L357" t="n">
+        <v>42</v>
+      </c>
+      <c r="M357" t="n">
+        <v>38</v>
+      </c>
+      <c r="N357" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="O357" t="n">
+        <v>152</v>
+      </c>
+      <c r="P357" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R357" t="n">
+        <v>35</v>
+      </c>
+      <c r="S357" t="n">
+        <v>31</v>
+      </c>
+      <c r="T357" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U357" t="n">
+        <v>11</v>
+      </c>
+      <c r="V357" t="n">
+        <v>8</v>
+      </c>
+      <c r="W357" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X357" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:39:34</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>92.01000000000001</v>
+      </c>
+      <c r="C358" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="D358" t="n">
+        <v>289</v>
+      </c>
+      <c r="E358" t="n">
+        <v>270</v>
+      </c>
+      <c r="F358" t="n">
+        <v>49</v>
+      </c>
+      <c r="G358" t="n">
+        <v>44</v>
+      </c>
+      <c r="H358" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="I358" t="n">
+        <v>112</v>
+      </c>
+      <c r="J358" t="n">
+        <v>102</v>
+      </c>
+      <c r="K358" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L358" t="n">
+        <v>42</v>
+      </c>
+      <c r="M358" t="n">
+        <v>38</v>
+      </c>
+      <c r="N358" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="O358" t="n">
+        <v>152</v>
+      </c>
+      <c r="P358" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="R358" t="n">
+        <v>35</v>
+      </c>
+      <c r="S358" t="n">
+        <v>31</v>
+      </c>
+      <c r="T358" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U358" t="n">
+        <v>11</v>
+      </c>
+      <c r="V358" t="n">
+        <v>8</v>
+      </c>
+      <c r="W358" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X358" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:41:33</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="C359" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="D359" t="n">
+        <v>290</v>
+      </c>
+      <c r="E359" t="n">
+        <v>271</v>
+      </c>
+      <c r="F359" t="n">
+        <v>50</v>
+      </c>
+      <c r="G359" t="n">
+        <v>45</v>
+      </c>
+      <c r="H359" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="I359" t="n">
+        <v>113</v>
+      </c>
+      <c r="J359" t="n">
+        <v>103</v>
+      </c>
+      <c r="K359" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L359" t="n">
+        <v>42</v>
+      </c>
+      <c r="M359" t="n">
+        <v>38</v>
+      </c>
+      <c r="N359" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="O359" t="n">
+        <v>152</v>
+      </c>
+      <c r="P359" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="R359" t="n">
+        <v>36</v>
+      </c>
+      <c r="S359" t="n">
+        <v>32</v>
+      </c>
+      <c r="T359" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U359" t="n">
+        <v>11</v>
+      </c>
+      <c r="V359" t="n">
+        <v>8</v>
+      </c>
+      <c r="W359" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X359" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:43:33</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="C360" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="D360" t="n">
+        <v>291</v>
+      </c>
+      <c r="E360" t="n">
+        <v>272</v>
+      </c>
+      <c r="F360" t="n">
+        <v>50</v>
+      </c>
+      <c r="G360" t="n">
+        <v>45</v>
+      </c>
+      <c r="H360" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="I360" t="n">
+        <v>114</v>
+      </c>
+      <c r="J360" t="n">
+        <v>104</v>
+      </c>
+      <c r="K360" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L360" t="n">
+        <v>42</v>
+      </c>
+      <c r="M360" t="n">
+        <v>38</v>
+      </c>
+      <c r="N360" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="O360" t="n">
+        <v>152</v>
+      </c>
+      <c r="P360" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="R360" t="n">
+        <v>36</v>
+      </c>
+      <c r="S360" t="n">
+        <v>32</v>
+      </c>
+      <c r="T360" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U360" t="n">
+        <v>11</v>
+      </c>
+      <c r="V360" t="n">
+        <v>8</v>
+      </c>
+      <c r="W360" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X360" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:46:01</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="C361" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="D361" t="n">
+        <v>292</v>
+      </c>
+      <c r="E361" t="n">
+        <v>273</v>
+      </c>
+      <c r="F361" t="n">
+        <v>50</v>
+      </c>
+      <c r="G361" t="n">
+        <v>45</v>
+      </c>
+      <c r="H361" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="I361" t="n">
+        <v>114</v>
+      </c>
+      <c r="J361" t="n">
+        <v>104</v>
+      </c>
+      <c r="K361" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L361" t="n">
+        <v>42</v>
+      </c>
+      <c r="M361" t="n">
+        <v>38</v>
+      </c>
+      <c r="N361" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="O361" t="n">
+        <v>153</v>
+      </c>
+      <c r="P361" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="R361" t="n">
+        <v>36</v>
+      </c>
+      <c r="S361" t="n">
+        <v>32</v>
+      </c>
+      <c r="T361" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U361" t="n">
+        <v>11</v>
+      </c>
+      <c r="V361" t="n">
+        <v>8</v>
+      </c>
+      <c r="W361" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="X361" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:52:21</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="C362" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="D362" t="n">
+        <v>296</v>
+      </c>
+      <c r="E362" t="n">
+        <v>276</v>
+      </c>
+      <c r="F362" t="n">
+        <v>51</v>
+      </c>
+      <c r="G362" t="n">
+        <v>46</v>
+      </c>
+      <c r="H362" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="I362" t="n">
+        <v>115</v>
+      </c>
+      <c r="J362" t="n">
+        <v>105</v>
+      </c>
+      <c r="K362" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L362" t="n">
+        <v>42</v>
+      </c>
+      <c r="M362" t="n">
+        <v>38</v>
+      </c>
+      <c r="N362" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="O362" t="n">
+        <v>156</v>
+      </c>
+      <c r="P362" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="R362" t="n">
+        <v>36</v>
+      </c>
+      <c r="S362" t="n">
+        <v>32</v>
+      </c>
+      <c r="T362" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U362" t="n">
+        <v>11</v>
+      </c>
+      <c r="V362" t="n">
+        <v>8</v>
+      </c>
+      <c r="W362" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X362" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:52:34</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="C363" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="D363" t="n">
+        <v>296</v>
+      </c>
+      <c r="E363" t="n">
+        <v>276</v>
+      </c>
+      <c r="F363" t="n">
+        <v>51</v>
+      </c>
+      <c r="G363" t="n">
+        <v>46</v>
+      </c>
+      <c r="H363" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="I363" t="n">
+        <v>115</v>
+      </c>
+      <c r="J363" t="n">
+        <v>105</v>
+      </c>
+      <c r="K363" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L363" t="n">
+        <v>42</v>
+      </c>
+      <c r="M363" t="n">
+        <v>38</v>
+      </c>
+      <c r="N363" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="O363" t="n">
+        <v>156</v>
+      </c>
+      <c r="P363" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="R363" t="n">
+        <v>36</v>
+      </c>
+      <c r="S363" t="n">
+        <v>32</v>
+      </c>
+      <c r="T363" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U363" t="n">
+        <v>11</v>
+      </c>
+      <c r="V363" t="n">
+        <v>8</v>
+      </c>
+      <c r="W363" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X363" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:54:34</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="C364" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="D364" t="n">
+        <v>299</v>
+      </c>
+      <c r="E364" t="n">
+        <v>279</v>
+      </c>
+      <c r="F364" t="n">
+        <v>52</v>
+      </c>
+      <c r="G364" t="n">
+        <v>47</v>
+      </c>
+      <c r="H364" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I364" t="n">
+        <v>116</v>
+      </c>
+      <c r="J364" t="n">
+        <v>106</v>
+      </c>
+      <c r="K364" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L364" t="n">
+        <v>42</v>
+      </c>
+      <c r="M364" t="n">
+        <v>38</v>
+      </c>
+      <c r="N364" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="O364" t="n">
+        <v>158</v>
+      </c>
+      <c r="P364" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R364" t="n">
+        <v>37</v>
+      </c>
+      <c r="S364" t="n">
+        <v>33</v>
+      </c>
+      <c r="T364" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U364" t="n">
+        <v>11</v>
+      </c>
+      <c r="V364" t="n">
+        <v>8</v>
+      </c>
+      <c r="W364" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X364" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:55:15</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="C365" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="D365" t="n">
+        <v>299</v>
+      </c>
+      <c r="E365" t="n">
+        <v>279</v>
+      </c>
+      <c r="F365" t="n">
+        <v>52</v>
+      </c>
+      <c r="G365" t="n">
+        <v>47</v>
+      </c>
+      <c r="H365" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I365" t="n">
+        <v>116</v>
+      </c>
+      <c r="J365" t="n">
+        <v>106</v>
+      </c>
+      <c r="K365" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L365" t="n">
+        <v>42</v>
+      </c>
+      <c r="M365" t="n">
+        <v>38</v>
+      </c>
+      <c r="N365" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="O365" t="n">
+        <v>158</v>
+      </c>
+      <c r="P365" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R365" t="n">
+        <v>37</v>
+      </c>
+      <c r="S365" t="n">
+        <v>33</v>
+      </c>
+      <c r="T365" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U365" t="n">
+        <v>11</v>
+      </c>
+      <c r="V365" t="n">
+        <v>8</v>
+      </c>
+      <c r="W365" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X365" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:57:14</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="C366" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="D366" t="n">
+        <v>301</v>
+      </c>
+      <c r="E366" t="n">
+        <v>281</v>
+      </c>
+      <c r="F366" t="n">
+        <v>53</v>
+      </c>
+      <c r="G366" t="n">
+        <v>48</v>
+      </c>
+      <c r="H366" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I366" t="n">
+        <v>116</v>
+      </c>
+      <c r="J366" t="n">
+        <v>106</v>
+      </c>
+      <c r="K366" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L366" t="n">
+        <v>43</v>
+      </c>
+      <c r="M366" t="n">
+        <v>39</v>
+      </c>
+      <c r="N366" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="O366" t="n">
+        <v>159</v>
+      </c>
+      <c r="P366" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R366" t="n">
+        <v>37</v>
+      </c>
+      <c r="S366" t="n">
+        <v>33</v>
+      </c>
+      <c r="T366" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U366" t="n">
+        <v>12</v>
+      </c>
+      <c r="V366" t="n">
+        <v>9</v>
+      </c>
+      <c r="W366" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X366" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:13</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="C367" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="D367" t="n">
+        <v>301</v>
+      </c>
+      <c r="E367" t="n">
+        <v>281</v>
+      </c>
+      <c r="F367" t="n">
+        <v>53</v>
+      </c>
+      <c r="G367" t="n">
+        <v>48</v>
+      </c>
+      <c r="H367" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I367" t="n">
+        <v>116</v>
+      </c>
+      <c r="J367" t="n">
+        <v>106</v>
+      </c>
+      <c r="K367" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L367" t="n">
+        <v>43</v>
+      </c>
+      <c r="M367" t="n">
+        <v>39</v>
+      </c>
+      <c r="N367" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="O367" t="n">
+        <v>159</v>
+      </c>
+      <c r="P367" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R367" t="n">
+        <v>37</v>
+      </c>
+      <c r="S367" t="n">
+        <v>33</v>
+      </c>
+      <c r="T367" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U367" t="n">
+        <v>12</v>
+      </c>
+      <c r="V367" t="n">
+        <v>9</v>
+      </c>
+      <c r="W367" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X367" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/regularite_history.xlsx
+++ b/regularite_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y367"/>
+  <dimension ref="A1:Y474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29457,6 +29457,8459 @@
         <v>11</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:00:13</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="C368" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="D368" t="n">
+        <v>301</v>
+      </c>
+      <c r="E368" t="n">
+        <v>281</v>
+      </c>
+      <c r="F368" t="n">
+        <v>53</v>
+      </c>
+      <c r="G368" t="n">
+        <v>48</v>
+      </c>
+      <c r="H368" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I368" t="n">
+        <v>116</v>
+      </c>
+      <c r="J368" t="n">
+        <v>106</v>
+      </c>
+      <c r="K368" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L368" t="n">
+        <v>43</v>
+      </c>
+      <c r="M368" t="n">
+        <v>39</v>
+      </c>
+      <c r="N368" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="O368" t="n">
+        <v>159</v>
+      </c>
+      <c r="P368" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R368" t="n">
+        <v>37</v>
+      </c>
+      <c r="S368" t="n">
+        <v>33</v>
+      </c>
+      <c r="T368" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U368" t="n">
+        <v>12</v>
+      </c>
+      <c r="V368" t="n">
+        <v>9</v>
+      </c>
+      <c r="W368" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X368" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y368" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:00:18</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="C369" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="D369" t="n">
+        <v>301</v>
+      </c>
+      <c r="E369" t="n">
+        <v>281</v>
+      </c>
+      <c r="F369" t="n">
+        <v>53</v>
+      </c>
+      <c r="G369" t="n">
+        <v>48</v>
+      </c>
+      <c r="H369" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I369" t="n">
+        <v>116</v>
+      </c>
+      <c r="J369" t="n">
+        <v>106</v>
+      </c>
+      <c r="K369" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L369" t="n">
+        <v>43</v>
+      </c>
+      <c r="M369" t="n">
+        <v>39</v>
+      </c>
+      <c r="N369" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="O369" t="n">
+        <v>159</v>
+      </c>
+      <c r="P369" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R369" t="n">
+        <v>37</v>
+      </c>
+      <c r="S369" t="n">
+        <v>33</v>
+      </c>
+      <c r="T369" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U369" t="n">
+        <v>12</v>
+      </c>
+      <c r="V369" t="n">
+        <v>9</v>
+      </c>
+      <c r="W369" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="X369" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:02:15</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="C370" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="D370" t="n">
+        <v>302</v>
+      </c>
+      <c r="E370" t="n">
+        <v>282</v>
+      </c>
+      <c r="F370" t="n">
+        <v>54</v>
+      </c>
+      <c r="G370" t="n">
+        <v>49</v>
+      </c>
+      <c r="H370" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="I370" t="n">
+        <v>116</v>
+      </c>
+      <c r="J370" t="n">
+        <v>106</v>
+      </c>
+      <c r="K370" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L370" t="n">
+        <v>43</v>
+      </c>
+      <c r="M370" t="n">
+        <v>39</v>
+      </c>
+      <c r="N370" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="O370" t="n">
+        <v>160</v>
+      </c>
+      <c r="P370" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R370" t="n">
+        <v>37</v>
+      </c>
+      <c r="S370" t="n">
+        <v>33</v>
+      </c>
+      <c r="T370" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U370" t="n">
+        <v>12</v>
+      </c>
+      <c r="V370" t="n">
+        <v>9</v>
+      </c>
+      <c r="W370" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="X370" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:04:15</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="C371" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="D371" t="n">
+        <v>305</v>
+      </c>
+      <c r="E371" t="n">
+        <v>285</v>
+      </c>
+      <c r="F371" t="n">
+        <v>54</v>
+      </c>
+      <c r="G371" t="n">
+        <v>49</v>
+      </c>
+      <c r="H371" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="I371" t="n">
+        <v>117</v>
+      </c>
+      <c r="J371" t="n">
+        <v>107</v>
+      </c>
+      <c r="K371" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L371" t="n">
+        <v>43</v>
+      </c>
+      <c r="M371" t="n">
+        <v>39</v>
+      </c>
+      <c r="N371" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="O371" t="n">
+        <v>162</v>
+      </c>
+      <c r="P371" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R371" t="n">
+        <v>37</v>
+      </c>
+      <c r="S371" t="n">
+        <v>33</v>
+      </c>
+      <c r="T371" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U371" t="n">
+        <v>12</v>
+      </c>
+      <c r="V371" t="n">
+        <v>9</v>
+      </c>
+      <c r="W371" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="X371" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:05:24</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C372" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="D372" t="n">
+        <v>307</v>
+      </c>
+      <c r="E372" t="n">
+        <v>287</v>
+      </c>
+      <c r="F372" t="n">
+        <v>55</v>
+      </c>
+      <c r="G372" t="n">
+        <v>50</v>
+      </c>
+      <c r="H372" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="I372" t="n">
+        <v>118</v>
+      </c>
+      <c r="J372" t="n">
+        <v>108</v>
+      </c>
+      <c r="K372" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L372" t="n">
+        <v>43</v>
+      </c>
+      <c r="M372" t="n">
+        <v>39</v>
+      </c>
+      <c r="N372" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="O372" t="n">
+        <v>163</v>
+      </c>
+      <c r="P372" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R372" t="n">
+        <v>37</v>
+      </c>
+      <c r="S372" t="n">
+        <v>33</v>
+      </c>
+      <c r="T372" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U372" t="n">
+        <v>12</v>
+      </c>
+      <c r="V372" t="n">
+        <v>9</v>
+      </c>
+      <c r="W372" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X372" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y372" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:07:24</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C373" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="D373" t="n">
+        <v>307</v>
+      </c>
+      <c r="E373" t="n">
+        <v>287</v>
+      </c>
+      <c r="F373" t="n">
+        <v>55</v>
+      </c>
+      <c r="G373" t="n">
+        <v>50</v>
+      </c>
+      <c r="H373" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="I373" t="n">
+        <v>118</v>
+      </c>
+      <c r="J373" t="n">
+        <v>108</v>
+      </c>
+      <c r="K373" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L373" t="n">
+        <v>43</v>
+      </c>
+      <c r="M373" t="n">
+        <v>39</v>
+      </c>
+      <c r="N373" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="O373" t="n">
+        <v>163</v>
+      </c>
+      <c r="P373" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R373" t="n">
+        <v>37</v>
+      </c>
+      <c r="S373" t="n">
+        <v>33</v>
+      </c>
+      <c r="T373" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U373" t="n">
+        <v>12</v>
+      </c>
+      <c r="V373" t="n">
+        <v>9</v>
+      </c>
+      <c r="W373" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X373" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y373" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:09:24</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="C374" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="D374" t="n">
+        <v>309</v>
+      </c>
+      <c r="E374" t="n">
+        <v>289</v>
+      </c>
+      <c r="F374" t="n">
+        <v>55</v>
+      </c>
+      <c r="G374" t="n">
+        <v>50</v>
+      </c>
+      <c r="H374" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="I374" t="n">
+        <v>118</v>
+      </c>
+      <c r="J374" t="n">
+        <v>108</v>
+      </c>
+      <c r="K374" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L374" t="n">
+        <v>43</v>
+      </c>
+      <c r="M374" t="n">
+        <v>39</v>
+      </c>
+      <c r="N374" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O374" t="n">
+        <v>165</v>
+      </c>
+      <c r="P374" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R374" t="n">
+        <v>37</v>
+      </c>
+      <c r="S374" t="n">
+        <v>33</v>
+      </c>
+      <c r="T374" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U374" t="n">
+        <v>12</v>
+      </c>
+      <c r="V374" t="n">
+        <v>9</v>
+      </c>
+      <c r="W374" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X374" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y374" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:11:24</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="C375" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="D375" t="n">
+        <v>309</v>
+      </c>
+      <c r="E375" t="n">
+        <v>289</v>
+      </c>
+      <c r="F375" t="n">
+        <v>55</v>
+      </c>
+      <c r="G375" t="n">
+        <v>50</v>
+      </c>
+      <c r="H375" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="I375" t="n">
+        <v>118</v>
+      </c>
+      <c r="J375" t="n">
+        <v>108</v>
+      </c>
+      <c r="K375" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L375" t="n">
+        <v>43</v>
+      </c>
+      <c r="M375" t="n">
+        <v>39</v>
+      </c>
+      <c r="N375" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O375" t="n">
+        <v>165</v>
+      </c>
+      <c r="P375" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R375" t="n">
+        <v>37</v>
+      </c>
+      <c r="S375" t="n">
+        <v>33</v>
+      </c>
+      <c r="T375" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U375" t="n">
+        <v>12</v>
+      </c>
+      <c r="V375" t="n">
+        <v>9</v>
+      </c>
+      <c r="W375" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X375" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:13:24</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C376" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="D376" t="n">
+        <v>310</v>
+      </c>
+      <c r="E376" t="n">
+        <v>289</v>
+      </c>
+      <c r="F376" t="n">
+        <v>55</v>
+      </c>
+      <c r="G376" t="n">
+        <v>50</v>
+      </c>
+      <c r="H376" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I376" t="n">
+        <v>119</v>
+      </c>
+      <c r="J376" t="n">
+        <v>108</v>
+      </c>
+      <c r="K376" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L376" t="n">
+        <v>43</v>
+      </c>
+      <c r="M376" t="n">
+        <v>39</v>
+      </c>
+      <c r="N376" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O376" t="n">
+        <v>165</v>
+      </c>
+      <c r="P376" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R376" t="n">
+        <v>37</v>
+      </c>
+      <c r="S376" t="n">
+        <v>33</v>
+      </c>
+      <c r="T376" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U376" t="n">
+        <v>12</v>
+      </c>
+      <c r="V376" t="n">
+        <v>9</v>
+      </c>
+      <c r="W376" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X376" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y376" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:15:24</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C377" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="D377" t="n">
+        <v>310</v>
+      </c>
+      <c r="E377" t="n">
+        <v>289</v>
+      </c>
+      <c r="F377" t="n">
+        <v>55</v>
+      </c>
+      <c r="G377" t="n">
+        <v>50</v>
+      </c>
+      <c r="H377" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I377" t="n">
+        <v>119</v>
+      </c>
+      <c r="J377" t="n">
+        <v>108</v>
+      </c>
+      <c r="K377" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L377" t="n">
+        <v>43</v>
+      </c>
+      <c r="M377" t="n">
+        <v>39</v>
+      </c>
+      <c r="N377" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O377" t="n">
+        <v>165</v>
+      </c>
+      <c r="P377" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="R377" t="n">
+        <v>37</v>
+      </c>
+      <c r="S377" t="n">
+        <v>33</v>
+      </c>
+      <c r="T377" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U377" t="n">
+        <v>12</v>
+      </c>
+      <c r="V377" t="n">
+        <v>9</v>
+      </c>
+      <c r="W377" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X377" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y377" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:17:25</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="C378" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D378" t="n">
+        <v>311</v>
+      </c>
+      <c r="E378" t="n">
+        <v>290</v>
+      </c>
+      <c r="F378" t="n">
+        <v>56</v>
+      </c>
+      <c r="G378" t="n">
+        <v>51</v>
+      </c>
+      <c r="H378" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="I378" t="n">
+        <v>120</v>
+      </c>
+      <c r="J378" t="n">
+        <v>109</v>
+      </c>
+      <c r="K378" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L378" t="n">
+        <v>43</v>
+      </c>
+      <c r="M378" t="n">
+        <v>39</v>
+      </c>
+      <c r="N378" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O378" t="n">
+        <v>165</v>
+      </c>
+      <c r="P378" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R378" t="n">
+        <v>38</v>
+      </c>
+      <c r="S378" t="n">
+        <v>34</v>
+      </c>
+      <c r="T378" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U378" t="n">
+        <v>12</v>
+      </c>
+      <c r="V378" t="n">
+        <v>9</v>
+      </c>
+      <c r="W378" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X378" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y378" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:20:03</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="C379" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D379" t="n">
+        <v>311</v>
+      </c>
+      <c r="E379" t="n">
+        <v>290</v>
+      </c>
+      <c r="F379" t="n">
+        <v>56</v>
+      </c>
+      <c r="G379" t="n">
+        <v>51</v>
+      </c>
+      <c r="H379" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="I379" t="n">
+        <v>120</v>
+      </c>
+      <c r="J379" t="n">
+        <v>109</v>
+      </c>
+      <c r="K379" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L379" t="n">
+        <v>43</v>
+      </c>
+      <c r="M379" t="n">
+        <v>39</v>
+      </c>
+      <c r="N379" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O379" t="n">
+        <v>165</v>
+      </c>
+      <c r="P379" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R379" t="n">
+        <v>38</v>
+      </c>
+      <c r="S379" t="n">
+        <v>34</v>
+      </c>
+      <c r="T379" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U379" t="n">
+        <v>12</v>
+      </c>
+      <c r="V379" t="n">
+        <v>9</v>
+      </c>
+      <c r="W379" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X379" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y379" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:28:50</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="C380" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D380" t="n">
+        <v>318</v>
+      </c>
+      <c r="E380" t="n">
+        <v>297</v>
+      </c>
+      <c r="F380" t="n">
+        <v>56</v>
+      </c>
+      <c r="G380" t="n">
+        <v>51</v>
+      </c>
+      <c r="H380" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="I380" t="n">
+        <v>123</v>
+      </c>
+      <c r="J380" t="n">
+        <v>112</v>
+      </c>
+      <c r="K380" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L380" t="n">
+        <v>44</v>
+      </c>
+      <c r="M380" t="n">
+        <v>40</v>
+      </c>
+      <c r="N380" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O380" t="n">
+        <v>169</v>
+      </c>
+      <c r="P380" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R380" t="n">
+        <v>38</v>
+      </c>
+      <c r="S380" t="n">
+        <v>34</v>
+      </c>
+      <c r="T380" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U380" t="n">
+        <v>12</v>
+      </c>
+      <c r="V380" t="n">
+        <v>9</v>
+      </c>
+      <c r="W380" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X380" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y380" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:28:54</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="C381" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D381" t="n">
+        <v>318</v>
+      </c>
+      <c r="E381" t="n">
+        <v>297</v>
+      </c>
+      <c r="F381" t="n">
+        <v>56</v>
+      </c>
+      <c r="G381" t="n">
+        <v>51</v>
+      </c>
+      <c r="H381" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="I381" t="n">
+        <v>123</v>
+      </c>
+      <c r="J381" t="n">
+        <v>112</v>
+      </c>
+      <c r="K381" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L381" t="n">
+        <v>44</v>
+      </c>
+      <c r="M381" t="n">
+        <v>40</v>
+      </c>
+      <c r="N381" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O381" t="n">
+        <v>169</v>
+      </c>
+      <c r="P381" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R381" t="n">
+        <v>38</v>
+      </c>
+      <c r="S381" t="n">
+        <v>34</v>
+      </c>
+      <c r="T381" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U381" t="n">
+        <v>12</v>
+      </c>
+      <c r="V381" t="n">
+        <v>9</v>
+      </c>
+      <c r="W381" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X381" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y381" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:30:52</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="C382" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D382" t="n">
+        <v>320</v>
+      </c>
+      <c r="E382" t="n">
+        <v>299</v>
+      </c>
+      <c r="F382" t="n">
+        <v>56</v>
+      </c>
+      <c r="G382" t="n">
+        <v>51</v>
+      </c>
+      <c r="H382" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="I382" t="n">
+        <v>123</v>
+      </c>
+      <c r="J382" t="n">
+        <v>112</v>
+      </c>
+      <c r="K382" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L382" t="n">
+        <v>44</v>
+      </c>
+      <c r="M382" t="n">
+        <v>40</v>
+      </c>
+      <c r="N382" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O382" t="n">
+        <v>171</v>
+      </c>
+      <c r="P382" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R382" t="n">
+        <v>38</v>
+      </c>
+      <c r="S382" t="n">
+        <v>34</v>
+      </c>
+      <c r="T382" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U382" t="n">
+        <v>12</v>
+      </c>
+      <c r="V382" t="n">
+        <v>9</v>
+      </c>
+      <c r="W382" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X382" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y382" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:32:52</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="C383" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D383" t="n">
+        <v>321</v>
+      </c>
+      <c r="E383" t="n">
+        <v>299</v>
+      </c>
+      <c r="F383" t="n">
+        <v>56</v>
+      </c>
+      <c r="G383" t="n">
+        <v>51</v>
+      </c>
+      <c r="H383" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="I383" t="n">
+        <v>123</v>
+      </c>
+      <c r="J383" t="n">
+        <v>112</v>
+      </c>
+      <c r="K383" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L383" t="n">
+        <v>44</v>
+      </c>
+      <c r="M383" t="n">
+        <v>40</v>
+      </c>
+      <c r="N383" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O383" t="n">
+        <v>172</v>
+      </c>
+      <c r="P383" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R383" t="n">
+        <v>38</v>
+      </c>
+      <c r="S383" t="n">
+        <v>34</v>
+      </c>
+      <c r="T383" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U383" t="n">
+        <v>12</v>
+      </c>
+      <c r="V383" t="n">
+        <v>9</v>
+      </c>
+      <c r="W383" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X383" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y383" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:34:53</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="C384" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D384" t="n">
+        <v>321</v>
+      </c>
+      <c r="E384" t="n">
+        <v>299</v>
+      </c>
+      <c r="F384" t="n">
+        <v>56</v>
+      </c>
+      <c r="G384" t="n">
+        <v>51</v>
+      </c>
+      <c r="H384" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="I384" t="n">
+        <v>123</v>
+      </c>
+      <c r="J384" t="n">
+        <v>112</v>
+      </c>
+      <c r="K384" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L384" t="n">
+        <v>44</v>
+      </c>
+      <c r="M384" t="n">
+        <v>40</v>
+      </c>
+      <c r="N384" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O384" t="n">
+        <v>172</v>
+      </c>
+      <c r="P384" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R384" t="n">
+        <v>38</v>
+      </c>
+      <c r="S384" t="n">
+        <v>34</v>
+      </c>
+      <c r="T384" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U384" t="n">
+        <v>12</v>
+      </c>
+      <c r="V384" t="n">
+        <v>9</v>
+      </c>
+      <c r="W384" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X384" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y384" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:36:53</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="C385" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D385" t="n">
+        <v>321</v>
+      </c>
+      <c r="E385" t="n">
+        <v>299</v>
+      </c>
+      <c r="F385" t="n">
+        <v>56</v>
+      </c>
+      <c r="G385" t="n">
+        <v>51</v>
+      </c>
+      <c r="H385" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="I385" t="n">
+        <v>123</v>
+      </c>
+      <c r="J385" t="n">
+        <v>112</v>
+      </c>
+      <c r="K385" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L385" t="n">
+        <v>44</v>
+      </c>
+      <c r="M385" t="n">
+        <v>40</v>
+      </c>
+      <c r="N385" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O385" t="n">
+        <v>172</v>
+      </c>
+      <c r="P385" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R385" t="n">
+        <v>38</v>
+      </c>
+      <c r="S385" t="n">
+        <v>34</v>
+      </c>
+      <c r="T385" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U385" t="n">
+        <v>12</v>
+      </c>
+      <c r="V385" t="n">
+        <v>9</v>
+      </c>
+      <c r="W385" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X385" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:38:53</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="C386" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D386" t="n">
+        <v>323</v>
+      </c>
+      <c r="E386" t="n">
+        <v>301</v>
+      </c>
+      <c r="F386" t="n">
+        <v>56</v>
+      </c>
+      <c r="G386" t="n">
+        <v>51</v>
+      </c>
+      <c r="H386" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="I386" t="n">
+        <v>125</v>
+      </c>
+      <c r="J386" t="n">
+        <v>114</v>
+      </c>
+      <c r="K386" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L386" t="n">
+        <v>45</v>
+      </c>
+      <c r="M386" t="n">
+        <v>41</v>
+      </c>
+      <c r="N386" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O386" t="n">
+        <v>172</v>
+      </c>
+      <c r="P386" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R386" t="n">
+        <v>38</v>
+      </c>
+      <c r="S386" t="n">
+        <v>34</v>
+      </c>
+      <c r="T386" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U386" t="n">
+        <v>12</v>
+      </c>
+      <c r="V386" t="n">
+        <v>9</v>
+      </c>
+      <c r="W386" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X386" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:40:53</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="C387" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D387" t="n">
+        <v>323</v>
+      </c>
+      <c r="E387" t="n">
+        <v>301</v>
+      </c>
+      <c r="F387" t="n">
+        <v>56</v>
+      </c>
+      <c r="G387" t="n">
+        <v>51</v>
+      </c>
+      <c r="H387" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="I387" t="n">
+        <v>125</v>
+      </c>
+      <c r="J387" t="n">
+        <v>114</v>
+      </c>
+      <c r="K387" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L387" t="n">
+        <v>45</v>
+      </c>
+      <c r="M387" t="n">
+        <v>41</v>
+      </c>
+      <c r="N387" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O387" t="n">
+        <v>172</v>
+      </c>
+      <c r="P387" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R387" t="n">
+        <v>38</v>
+      </c>
+      <c r="S387" t="n">
+        <v>34</v>
+      </c>
+      <c r="T387" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U387" t="n">
+        <v>12</v>
+      </c>
+      <c r="V387" t="n">
+        <v>9</v>
+      </c>
+      <c r="W387" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X387" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y387" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:43:04</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="C388" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D388" t="n">
+        <v>324</v>
+      </c>
+      <c r="E388" t="n">
+        <v>302</v>
+      </c>
+      <c r="F388" t="n">
+        <v>56</v>
+      </c>
+      <c r="G388" t="n">
+        <v>51</v>
+      </c>
+      <c r="H388" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="I388" t="n">
+        <v>126</v>
+      </c>
+      <c r="J388" t="n">
+        <v>115</v>
+      </c>
+      <c r="K388" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L388" t="n">
+        <v>45</v>
+      </c>
+      <c r="M388" t="n">
+        <v>41</v>
+      </c>
+      <c r="N388" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O388" t="n">
+        <v>172</v>
+      </c>
+      <c r="P388" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R388" t="n">
+        <v>38</v>
+      </c>
+      <c r="S388" t="n">
+        <v>34</v>
+      </c>
+      <c r="T388" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U388" t="n">
+        <v>12</v>
+      </c>
+      <c r="V388" t="n">
+        <v>9</v>
+      </c>
+      <c r="W388" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X388" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y388" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:45:04</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="C389" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D389" t="n">
+        <v>325</v>
+      </c>
+      <c r="E389" t="n">
+        <v>303</v>
+      </c>
+      <c r="F389" t="n">
+        <v>56</v>
+      </c>
+      <c r="G389" t="n">
+        <v>51</v>
+      </c>
+      <c r="H389" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="I389" t="n">
+        <v>127</v>
+      </c>
+      <c r="J389" t="n">
+        <v>116</v>
+      </c>
+      <c r="K389" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L389" t="n">
+        <v>45</v>
+      </c>
+      <c r="M389" t="n">
+        <v>41</v>
+      </c>
+      <c r="N389" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O389" t="n">
+        <v>172</v>
+      </c>
+      <c r="P389" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R389" t="n">
+        <v>38</v>
+      </c>
+      <c r="S389" t="n">
+        <v>34</v>
+      </c>
+      <c r="T389" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U389" t="n">
+        <v>12</v>
+      </c>
+      <c r="V389" t="n">
+        <v>9</v>
+      </c>
+      <c r="W389" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X389" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:47:03</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="C390" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D390" t="n">
+        <v>325</v>
+      </c>
+      <c r="E390" t="n">
+        <v>303</v>
+      </c>
+      <c r="F390" t="n">
+        <v>56</v>
+      </c>
+      <c r="G390" t="n">
+        <v>51</v>
+      </c>
+      <c r="H390" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="I390" t="n">
+        <v>127</v>
+      </c>
+      <c r="J390" t="n">
+        <v>116</v>
+      </c>
+      <c r="K390" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L390" t="n">
+        <v>45</v>
+      </c>
+      <c r="M390" t="n">
+        <v>41</v>
+      </c>
+      <c r="N390" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O390" t="n">
+        <v>172</v>
+      </c>
+      <c r="P390" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R390" t="n">
+        <v>38</v>
+      </c>
+      <c r="S390" t="n">
+        <v>34</v>
+      </c>
+      <c r="T390" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U390" t="n">
+        <v>12</v>
+      </c>
+      <c r="V390" t="n">
+        <v>9</v>
+      </c>
+      <c r="W390" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X390" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y390" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:49:03</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>92.94</v>
+      </c>
+      <c r="C391" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="D391" t="n">
+        <v>326</v>
+      </c>
+      <c r="E391" t="n">
+        <v>304</v>
+      </c>
+      <c r="F391" t="n">
+        <v>56</v>
+      </c>
+      <c r="G391" t="n">
+        <v>51</v>
+      </c>
+      <c r="H391" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="I391" t="n">
+        <v>128</v>
+      </c>
+      <c r="J391" t="n">
+        <v>117</v>
+      </c>
+      <c r="K391" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L391" t="n">
+        <v>45</v>
+      </c>
+      <c r="M391" t="n">
+        <v>41</v>
+      </c>
+      <c r="N391" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O391" t="n">
+        <v>172</v>
+      </c>
+      <c r="P391" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="R391" t="n">
+        <v>38</v>
+      </c>
+      <c r="S391" t="n">
+        <v>34</v>
+      </c>
+      <c r="T391" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U391" t="n">
+        <v>12</v>
+      </c>
+      <c r="V391" t="n">
+        <v>9</v>
+      </c>
+      <c r="W391" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X391" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y391" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:51:03</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="C392" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="D392" t="n">
+        <v>327</v>
+      </c>
+      <c r="E392" t="n">
+        <v>305</v>
+      </c>
+      <c r="F392" t="n">
+        <v>57</v>
+      </c>
+      <c r="G392" t="n">
+        <v>52</v>
+      </c>
+      <c r="H392" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I392" t="n">
+        <v>129</v>
+      </c>
+      <c r="J392" t="n">
+        <v>118</v>
+      </c>
+      <c r="K392" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L392" t="n">
+        <v>45</v>
+      </c>
+      <c r="M392" t="n">
+        <v>41</v>
+      </c>
+      <c r="N392" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="O392" t="n">
+        <v>172</v>
+      </c>
+      <c r="P392" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="R392" t="n">
+        <v>39</v>
+      </c>
+      <c r="S392" t="n">
+        <v>35</v>
+      </c>
+      <c r="T392" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U392" t="n">
+        <v>12</v>
+      </c>
+      <c r="V392" t="n">
+        <v>9</v>
+      </c>
+      <c r="W392" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X392" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:53:03</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="C393" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="D393" t="n">
+        <v>328</v>
+      </c>
+      <c r="E393" t="n">
+        <v>306</v>
+      </c>
+      <c r="F393" t="n">
+        <v>58</v>
+      </c>
+      <c r="G393" t="n">
+        <v>53</v>
+      </c>
+      <c r="H393" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I393" t="n">
+        <v>129</v>
+      </c>
+      <c r="J393" t="n">
+        <v>118</v>
+      </c>
+      <c r="K393" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L393" t="n">
+        <v>45</v>
+      </c>
+      <c r="M393" t="n">
+        <v>41</v>
+      </c>
+      <c r="N393" t="n">
+        <v>94.73</v>
+      </c>
+      <c r="O393" t="n">
+        <v>173</v>
+      </c>
+      <c r="P393" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R393" t="n">
+        <v>40</v>
+      </c>
+      <c r="S393" t="n">
+        <v>36</v>
+      </c>
+      <c r="T393" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U393" t="n">
+        <v>12</v>
+      </c>
+      <c r="V393" t="n">
+        <v>9</v>
+      </c>
+      <c r="W393" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="X393" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:55:03</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="C394" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D394" t="n">
+        <v>330</v>
+      </c>
+      <c r="E394" t="n">
+        <v>308</v>
+      </c>
+      <c r="F394" t="n">
+        <v>60</v>
+      </c>
+      <c r="G394" t="n">
+        <v>55</v>
+      </c>
+      <c r="H394" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I394" t="n">
+        <v>129</v>
+      </c>
+      <c r="J394" t="n">
+        <v>118</v>
+      </c>
+      <c r="K394" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L394" t="n">
+        <v>45</v>
+      </c>
+      <c r="M394" t="n">
+        <v>41</v>
+      </c>
+      <c r="N394" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="O394" t="n">
+        <v>175</v>
+      </c>
+      <c r="P394" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R394" t="n">
+        <v>40</v>
+      </c>
+      <c r="S394" t="n">
+        <v>36</v>
+      </c>
+      <c r="T394" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U394" t="n">
+        <v>12</v>
+      </c>
+      <c r="V394" t="n">
+        <v>9</v>
+      </c>
+      <c r="W394" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X394" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:57:03</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="C395" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D395" t="n">
+        <v>334</v>
+      </c>
+      <c r="E395" t="n">
+        <v>312</v>
+      </c>
+      <c r="F395" t="n">
+        <v>60</v>
+      </c>
+      <c r="G395" t="n">
+        <v>55</v>
+      </c>
+      <c r="H395" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I395" t="n">
+        <v>131</v>
+      </c>
+      <c r="J395" t="n">
+        <v>120</v>
+      </c>
+      <c r="K395" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L395" t="n">
+        <v>46</v>
+      </c>
+      <c r="M395" t="n">
+        <v>42</v>
+      </c>
+      <c r="N395" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="O395" t="n">
+        <v>177</v>
+      </c>
+      <c r="P395" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R395" t="n">
+        <v>40</v>
+      </c>
+      <c r="S395" t="n">
+        <v>36</v>
+      </c>
+      <c r="T395" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U395" t="n">
+        <v>12</v>
+      </c>
+      <c r="V395" t="n">
+        <v>9</v>
+      </c>
+      <c r="W395" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X395" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y395" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-27 15:59:03</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="C396" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D396" t="n">
+        <v>335</v>
+      </c>
+      <c r="E396" t="n">
+        <v>313</v>
+      </c>
+      <c r="F396" t="n">
+        <v>60</v>
+      </c>
+      <c r="G396" t="n">
+        <v>55</v>
+      </c>
+      <c r="H396" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I396" t="n">
+        <v>131</v>
+      </c>
+      <c r="J396" t="n">
+        <v>120</v>
+      </c>
+      <c r="K396" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L396" t="n">
+        <v>46</v>
+      </c>
+      <c r="M396" t="n">
+        <v>42</v>
+      </c>
+      <c r="N396" t="n">
+        <v>95</v>
+      </c>
+      <c r="O396" t="n">
+        <v>178</v>
+      </c>
+      <c r="P396" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R396" t="n">
+        <v>40</v>
+      </c>
+      <c r="S396" t="n">
+        <v>36</v>
+      </c>
+      <c r="T396" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="U396" t="n">
+        <v>12</v>
+      </c>
+      <c r="V396" t="n">
+        <v>9</v>
+      </c>
+      <c r="W396" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X396" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y396" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:01:04</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="C397" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D397" t="n">
+        <v>335</v>
+      </c>
+      <c r="E397" t="n">
+        <v>313</v>
+      </c>
+      <c r="F397" t="n">
+        <v>61</v>
+      </c>
+      <c r="G397" t="n">
+        <v>56</v>
+      </c>
+      <c r="H397" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I397" t="n">
+        <v>131</v>
+      </c>
+      <c r="J397" t="n">
+        <v>120</v>
+      </c>
+      <c r="K397" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L397" t="n">
+        <v>46</v>
+      </c>
+      <c r="M397" t="n">
+        <v>42</v>
+      </c>
+      <c r="N397" t="n">
+        <v>95</v>
+      </c>
+      <c r="O397" t="n">
+        <v>178</v>
+      </c>
+      <c r="P397" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R397" t="n">
+        <v>40</v>
+      </c>
+      <c r="S397" t="n">
+        <v>36</v>
+      </c>
+      <c r="T397" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U397" t="n">
+        <v>13</v>
+      </c>
+      <c r="V397" t="n">
+        <v>10</v>
+      </c>
+      <c r="W397" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X397" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:03:03</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="C398" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D398" t="n">
+        <v>335</v>
+      </c>
+      <c r="E398" t="n">
+        <v>313</v>
+      </c>
+      <c r="F398" t="n">
+        <v>61</v>
+      </c>
+      <c r="G398" t="n">
+        <v>56</v>
+      </c>
+      <c r="H398" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I398" t="n">
+        <v>131</v>
+      </c>
+      <c r="J398" t="n">
+        <v>120</v>
+      </c>
+      <c r="K398" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L398" t="n">
+        <v>46</v>
+      </c>
+      <c r="M398" t="n">
+        <v>42</v>
+      </c>
+      <c r="N398" t="n">
+        <v>95</v>
+      </c>
+      <c r="O398" t="n">
+        <v>178</v>
+      </c>
+      <c r="P398" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R398" t="n">
+        <v>40</v>
+      </c>
+      <c r="S398" t="n">
+        <v>36</v>
+      </c>
+      <c r="T398" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U398" t="n">
+        <v>13</v>
+      </c>
+      <c r="V398" t="n">
+        <v>10</v>
+      </c>
+      <c r="W398" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X398" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y398" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:05:03</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C399" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D399" t="n">
+        <v>339</v>
+      </c>
+      <c r="E399" t="n">
+        <v>317</v>
+      </c>
+      <c r="F399" t="n">
+        <v>61</v>
+      </c>
+      <c r="G399" t="n">
+        <v>56</v>
+      </c>
+      <c r="H399" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I399" t="n">
+        <v>131</v>
+      </c>
+      <c r="J399" t="n">
+        <v>120</v>
+      </c>
+      <c r="K399" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L399" t="n">
+        <v>47</v>
+      </c>
+      <c r="M399" t="n">
+        <v>43</v>
+      </c>
+      <c r="N399" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O399" t="n">
+        <v>181</v>
+      </c>
+      <c r="P399" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R399" t="n">
+        <v>40</v>
+      </c>
+      <c r="S399" t="n">
+        <v>36</v>
+      </c>
+      <c r="T399" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U399" t="n">
+        <v>13</v>
+      </c>
+      <c r="V399" t="n">
+        <v>10</v>
+      </c>
+      <c r="W399" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X399" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:07:03</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C400" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D400" t="n">
+        <v>340</v>
+      </c>
+      <c r="E400" t="n">
+        <v>318</v>
+      </c>
+      <c r="F400" t="n">
+        <v>61</v>
+      </c>
+      <c r="G400" t="n">
+        <v>56</v>
+      </c>
+      <c r="H400" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I400" t="n">
+        <v>131</v>
+      </c>
+      <c r="J400" t="n">
+        <v>120</v>
+      </c>
+      <c r="K400" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L400" t="n">
+        <v>47</v>
+      </c>
+      <c r="M400" t="n">
+        <v>43</v>
+      </c>
+      <c r="N400" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O400" t="n">
+        <v>182</v>
+      </c>
+      <c r="P400" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R400" t="n">
+        <v>40</v>
+      </c>
+      <c r="S400" t="n">
+        <v>36</v>
+      </c>
+      <c r="T400" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U400" t="n">
+        <v>13</v>
+      </c>
+      <c r="V400" t="n">
+        <v>10</v>
+      </c>
+      <c r="W400" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X400" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y400" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:09:03</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C401" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D401" t="n">
+        <v>341</v>
+      </c>
+      <c r="E401" t="n">
+        <v>319</v>
+      </c>
+      <c r="F401" t="n">
+        <v>61</v>
+      </c>
+      <c r="G401" t="n">
+        <v>56</v>
+      </c>
+      <c r="H401" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I401" t="n">
+        <v>132</v>
+      </c>
+      <c r="J401" t="n">
+        <v>121</v>
+      </c>
+      <c r="K401" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L401" t="n">
+        <v>47</v>
+      </c>
+      <c r="M401" t="n">
+        <v>43</v>
+      </c>
+      <c r="N401" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O401" t="n">
+        <v>182</v>
+      </c>
+      <c r="P401" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R401" t="n">
+        <v>40</v>
+      </c>
+      <c r="S401" t="n">
+        <v>36</v>
+      </c>
+      <c r="T401" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U401" t="n">
+        <v>13</v>
+      </c>
+      <c r="V401" t="n">
+        <v>10</v>
+      </c>
+      <c r="W401" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X401" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:11:03</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C402" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D402" t="n">
+        <v>342</v>
+      </c>
+      <c r="E402" t="n">
+        <v>320</v>
+      </c>
+      <c r="F402" t="n">
+        <v>61</v>
+      </c>
+      <c r="G402" t="n">
+        <v>56</v>
+      </c>
+      <c r="H402" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I402" t="n">
+        <v>133</v>
+      </c>
+      <c r="J402" t="n">
+        <v>122</v>
+      </c>
+      <c r="K402" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L402" t="n">
+        <v>47</v>
+      </c>
+      <c r="M402" t="n">
+        <v>43</v>
+      </c>
+      <c r="N402" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O402" t="n">
+        <v>182</v>
+      </c>
+      <c r="P402" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R402" t="n">
+        <v>40</v>
+      </c>
+      <c r="S402" t="n">
+        <v>36</v>
+      </c>
+      <c r="T402" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U402" t="n">
+        <v>13</v>
+      </c>
+      <c r="V402" t="n">
+        <v>10</v>
+      </c>
+      <c r="W402" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X402" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y402" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:13:03</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C403" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D403" t="n">
+        <v>342</v>
+      </c>
+      <c r="E403" t="n">
+        <v>320</v>
+      </c>
+      <c r="F403" t="n">
+        <v>61</v>
+      </c>
+      <c r="G403" t="n">
+        <v>56</v>
+      </c>
+      <c r="H403" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I403" t="n">
+        <v>133</v>
+      </c>
+      <c r="J403" t="n">
+        <v>122</v>
+      </c>
+      <c r="K403" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L403" t="n">
+        <v>47</v>
+      </c>
+      <c r="M403" t="n">
+        <v>43</v>
+      </c>
+      <c r="N403" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O403" t="n">
+        <v>182</v>
+      </c>
+      <c r="P403" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R403" t="n">
+        <v>40</v>
+      </c>
+      <c r="S403" t="n">
+        <v>36</v>
+      </c>
+      <c r="T403" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U403" t="n">
+        <v>13</v>
+      </c>
+      <c r="V403" t="n">
+        <v>10</v>
+      </c>
+      <c r="W403" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X403" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y403" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:15:03</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C404" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D404" t="n">
+        <v>342</v>
+      </c>
+      <c r="E404" t="n">
+        <v>320</v>
+      </c>
+      <c r="F404" t="n">
+        <v>61</v>
+      </c>
+      <c r="G404" t="n">
+        <v>56</v>
+      </c>
+      <c r="H404" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I404" t="n">
+        <v>133</v>
+      </c>
+      <c r="J404" t="n">
+        <v>122</v>
+      </c>
+      <c r="K404" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L404" t="n">
+        <v>47</v>
+      </c>
+      <c r="M404" t="n">
+        <v>43</v>
+      </c>
+      <c r="N404" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O404" t="n">
+        <v>182</v>
+      </c>
+      <c r="P404" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R404" t="n">
+        <v>40</v>
+      </c>
+      <c r="S404" t="n">
+        <v>36</v>
+      </c>
+      <c r="T404" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U404" t="n">
+        <v>13</v>
+      </c>
+      <c r="V404" t="n">
+        <v>10</v>
+      </c>
+      <c r="W404" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X404" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y404" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:17:03</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C405" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D405" t="n">
+        <v>343</v>
+      </c>
+      <c r="E405" t="n">
+        <v>321</v>
+      </c>
+      <c r="F405" t="n">
+        <v>61</v>
+      </c>
+      <c r="G405" t="n">
+        <v>56</v>
+      </c>
+      <c r="H405" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I405" t="n">
+        <v>134</v>
+      </c>
+      <c r="J405" t="n">
+        <v>123</v>
+      </c>
+      <c r="K405" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L405" t="n">
+        <v>47</v>
+      </c>
+      <c r="M405" t="n">
+        <v>43</v>
+      </c>
+      <c r="N405" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O405" t="n">
+        <v>182</v>
+      </c>
+      <c r="P405" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R405" t="n">
+        <v>40</v>
+      </c>
+      <c r="S405" t="n">
+        <v>36</v>
+      </c>
+      <c r="T405" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U405" t="n">
+        <v>13</v>
+      </c>
+      <c r="V405" t="n">
+        <v>10</v>
+      </c>
+      <c r="W405" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X405" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:18:56</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C406" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D406" t="n">
+        <v>344</v>
+      </c>
+      <c r="E406" t="n">
+        <v>322</v>
+      </c>
+      <c r="F406" t="n">
+        <v>61</v>
+      </c>
+      <c r="G406" t="n">
+        <v>56</v>
+      </c>
+      <c r="H406" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I406" t="n">
+        <v>135</v>
+      </c>
+      <c r="J406" t="n">
+        <v>124</v>
+      </c>
+      <c r="K406" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L406" t="n">
+        <v>48</v>
+      </c>
+      <c r="M406" t="n">
+        <v>44</v>
+      </c>
+      <c r="N406" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O406" t="n">
+        <v>182</v>
+      </c>
+      <c r="P406" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R406" t="n">
+        <v>40</v>
+      </c>
+      <c r="S406" t="n">
+        <v>36</v>
+      </c>
+      <c r="T406" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U406" t="n">
+        <v>13</v>
+      </c>
+      <c r="V406" t="n">
+        <v>10</v>
+      </c>
+      <c r="W406" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X406" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y406" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:19:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C407" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D407" t="n">
+        <v>344</v>
+      </c>
+      <c r="E407" t="n">
+        <v>322</v>
+      </c>
+      <c r="F407" t="n">
+        <v>61</v>
+      </c>
+      <c r="G407" t="n">
+        <v>56</v>
+      </c>
+      <c r="H407" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I407" t="n">
+        <v>135</v>
+      </c>
+      <c r="J407" t="n">
+        <v>124</v>
+      </c>
+      <c r="K407" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L407" t="n">
+        <v>48</v>
+      </c>
+      <c r="M407" t="n">
+        <v>44</v>
+      </c>
+      <c r="N407" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O407" t="n">
+        <v>182</v>
+      </c>
+      <c r="P407" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R407" t="n">
+        <v>40</v>
+      </c>
+      <c r="S407" t="n">
+        <v>36</v>
+      </c>
+      <c r="T407" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U407" t="n">
+        <v>13</v>
+      </c>
+      <c r="V407" t="n">
+        <v>10</v>
+      </c>
+      <c r="W407" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X407" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:20:57</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C408" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D408" t="n">
+        <v>344</v>
+      </c>
+      <c r="E408" t="n">
+        <v>322</v>
+      </c>
+      <c r="F408" t="n">
+        <v>61</v>
+      </c>
+      <c r="G408" t="n">
+        <v>56</v>
+      </c>
+      <c r="H408" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I408" t="n">
+        <v>135</v>
+      </c>
+      <c r="J408" t="n">
+        <v>124</v>
+      </c>
+      <c r="K408" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L408" t="n">
+        <v>48</v>
+      </c>
+      <c r="M408" t="n">
+        <v>44</v>
+      </c>
+      <c r="N408" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O408" t="n">
+        <v>182</v>
+      </c>
+      <c r="P408" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R408" t="n">
+        <v>40</v>
+      </c>
+      <c r="S408" t="n">
+        <v>36</v>
+      </c>
+      <c r="T408" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U408" t="n">
+        <v>13</v>
+      </c>
+      <c r="V408" t="n">
+        <v>10</v>
+      </c>
+      <c r="W408" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X408" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:22:57</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C409" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D409" t="n">
+        <v>344</v>
+      </c>
+      <c r="E409" t="n">
+        <v>322</v>
+      </c>
+      <c r="F409" t="n">
+        <v>61</v>
+      </c>
+      <c r="G409" t="n">
+        <v>56</v>
+      </c>
+      <c r="H409" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I409" t="n">
+        <v>135</v>
+      </c>
+      <c r="J409" t="n">
+        <v>124</v>
+      </c>
+      <c r="K409" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L409" t="n">
+        <v>48</v>
+      </c>
+      <c r="M409" t="n">
+        <v>44</v>
+      </c>
+      <c r="N409" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="O409" t="n">
+        <v>182</v>
+      </c>
+      <c r="P409" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R409" t="n">
+        <v>40</v>
+      </c>
+      <c r="S409" t="n">
+        <v>36</v>
+      </c>
+      <c r="T409" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U409" t="n">
+        <v>13</v>
+      </c>
+      <c r="V409" t="n">
+        <v>10</v>
+      </c>
+      <c r="W409" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X409" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y409" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:24:01</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="C410" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D410" t="n">
+        <v>346</v>
+      </c>
+      <c r="E410" t="n">
+        <v>324</v>
+      </c>
+      <c r="F410" t="n">
+        <v>61</v>
+      </c>
+      <c r="G410" t="n">
+        <v>56</v>
+      </c>
+      <c r="H410" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I410" t="n">
+        <v>135</v>
+      </c>
+      <c r="J410" t="n">
+        <v>124</v>
+      </c>
+      <c r="K410" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L410" t="n">
+        <v>48</v>
+      </c>
+      <c r="M410" t="n">
+        <v>44</v>
+      </c>
+      <c r="N410" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O410" t="n">
+        <v>184</v>
+      </c>
+      <c r="P410" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R410" t="n">
+        <v>40</v>
+      </c>
+      <c r="S410" t="n">
+        <v>36</v>
+      </c>
+      <c r="T410" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U410" t="n">
+        <v>13</v>
+      </c>
+      <c r="V410" t="n">
+        <v>10</v>
+      </c>
+      <c r="W410" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X410" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y410" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:26:02</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="C411" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D411" t="n">
+        <v>347</v>
+      </c>
+      <c r="E411" t="n">
+        <v>325</v>
+      </c>
+      <c r="F411" t="n">
+        <v>61</v>
+      </c>
+      <c r="G411" t="n">
+        <v>56</v>
+      </c>
+      <c r="H411" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="I411" t="n">
+        <v>136</v>
+      </c>
+      <c r="J411" t="n">
+        <v>125</v>
+      </c>
+      <c r="K411" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L411" t="n">
+        <v>48</v>
+      </c>
+      <c r="M411" t="n">
+        <v>44</v>
+      </c>
+      <c r="N411" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O411" t="n">
+        <v>184</v>
+      </c>
+      <c r="P411" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R411" t="n">
+        <v>40</v>
+      </c>
+      <c r="S411" t="n">
+        <v>36</v>
+      </c>
+      <c r="T411" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U411" t="n">
+        <v>13</v>
+      </c>
+      <c r="V411" t="n">
+        <v>10</v>
+      </c>
+      <c r="W411" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X411" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y411" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:28:02</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="C412" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="D412" t="n">
+        <v>349</v>
+      </c>
+      <c r="E412" t="n">
+        <v>327</v>
+      </c>
+      <c r="F412" t="n">
+        <v>61</v>
+      </c>
+      <c r="G412" t="n">
+        <v>56</v>
+      </c>
+      <c r="H412" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="I412" t="n">
+        <v>138</v>
+      </c>
+      <c r="J412" t="n">
+        <v>127</v>
+      </c>
+      <c r="K412" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L412" t="n">
+        <v>48</v>
+      </c>
+      <c r="M412" t="n">
+        <v>44</v>
+      </c>
+      <c r="N412" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O412" t="n">
+        <v>184</v>
+      </c>
+      <c r="P412" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="R412" t="n">
+        <v>40</v>
+      </c>
+      <c r="S412" t="n">
+        <v>36</v>
+      </c>
+      <c r="T412" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U412" t="n">
+        <v>13</v>
+      </c>
+      <c r="V412" t="n">
+        <v>10</v>
+      </c>
+      <c r="W412" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X412" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y412" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:30:01</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="C413" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="D413" t="n">
+        <v>350</v>
+      </c>
+      <c r="E413" t="n">
+        <v>328</v>
+      </c>
+      <c r="F413" t="n">
+        <v>63</v>
+      </c>
+      <c r="G413" t="n">
+        <v>58</v>
+      </c>
+      <c r="H413" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="I413" t="n">
+        <v>138</v>
+      </c>
+      <c r="J413" t="n">
+        <v>127</v>
+      </c>
+      <c r="K413" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L413" t="n">
+        <v>48</v>
+      </c>
+      <c r="M413" t="n">
+        <v>44</v>
+      </c>
+      <c r="N413" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O413" t="n">
+        <v>185</v>
+      </c>
+      <c r="P413" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="R413" t="n">
+        <v>42</v>
+      </c>
+      <c r="S413" t="n">
+        <v>38</v>
+      </c>
+      <c r="T413" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U413" t="n">
+        <v>13</v>
+      </c>
+      <c r="V413" t="n">
+        <v>10</v>
+      </c>
+      <c r="W413" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X413" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y413" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:32:01</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="C414" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="D414" t="n">
+        <v>351</v>
+      </c>
+      <c r="E414" t="n">
+        <v>329</v>
+      </c>
+      <c r="F414" t="n">
+        <v>63</v>
+      </c>
+      <c r="G414" t="n">
+        <v>58</v>
+      </c>
+      <c r="H414" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="I414" t="n">
+        <v>139</v>
+      </c>
+      <c r="J414" t="n">
+        <v>128</v>
+      </c>
+      <c r="K414" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L414" t="n">
+        <v>48</v>
+      </c>
+      <c r="M414" t="n">
+        <v>44</v>
+      </c>
+      <c r="N414" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="O414" t="n">
+        <v>185</v>
+      </c>
+      <c r="P414" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="R414" t="n">
+        <v>42</v>
+      </c>
+      <c r="S414" t="n">
+        <v>38</v>
+      </c>
+      <c r="T414" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U414" t="n">
+        <v>13</v>
+      </c>
+      <c r="V414" t="n">
+        <v>10</v>
+      </c>
+      <c r="W414" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X414" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y414" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:34:05</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="C415" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="D415" t="n">
+        <v>352</v>
+      </c>
+      <c r="E415" t="n">
+        <v>329</v>
+      </c>
+      <c r="F415" t="n">
+        <v>63</v>
+      </c>
+      <c r="G415" t="n">
+        <v>58</v>
+      </c>
+      <c r="H415" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="I415" t="n">
+        <v>139</v>
+      </c>
+      <c r="J415" t="n">
+        <v>128</v>
+      </c>
+      <c r="K415" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L415" t="n">
+        <v>48</v>
+      </c>
+      <c r="M415" t="n">
+        <v>44</v>
+      </c>
+      <c r="N415" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="O415" t="n">
+        <v>186</v>
+      </c>
+      <c r="P415" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="R415" t="n">
+        <v>42</v>
+      </c>
+      <c r="S415" t="n">
+        <v>38</v>
+      </c>
+      <c r="T415" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U415" t="n">
+        <v>13</v>
+      </c>
+      <c r="V415" t="n">
+        <v>10</v>
+      </c>
+      <c r="W415" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X415" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y415" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:36:02</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="C416" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="D416" t="n">
+        <v>354</v>
+      </c>
+      <c r="E416" t="n">
+        <v>331</v>
+      </c>
+      <c r="F416" t="n">
+        <v>65</v>
+      </c>
+      <c r="G416" t="n">
+        <v>60</v>
+      </c>
+      <c r="H416" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="I416" t="n">
+        <v>141</v>
+      </c>
+      <c r="J416" t="n">
+        <v>130</v>
+      </c>
+      <c r="K416" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L416" t="n">
+        <v>48</v>
+      </c>
+      <c r="M416" t="n">
+        <v>44</v>
+      </c>
+      <c r="N416" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="O416" t="n">
+        <v>186</v>
+      </c>
+      <c r="P416" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="R416" t="n">
+        <v>44</v>
+      </c>
+      <c r="S416" t="n">
+        <v>40</v>
+      </c>
+      <c r="T416" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U416" t="n">
+        <v>13</v>
+      </c>
+      <c r="V416" t="n">
+        <v>10</v>
+      </c>
+      <c r="W416" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X416" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y416" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:38:02</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="C417" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="D417" t="n">
+        <v>357</v>
+      </c>
+      <c r="E417" t="n">
+        <v>334</v>
+      </c>
+      <c r="F417" t="n">
+        <v>65</v>
+      </c>
+      <c r="G417" t="n">
+        <v>60</v>
+      </c>
+      <c r="H417" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="I417" t="n">
+        <v>141</v>
+      </c>
+      <c r="J417" t="n">
+        <v>130</v>
+      </c>
+      <c r="K417" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L417" t="n">
+        <v>48</v>
+      </c>
+      <c r="M417" t="n">
+        <v>44</v>
+      </c>
+      <c r="N417" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O417" t="n">
+        <v>189</v>
+      </c>
+      <c r="P417" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="R417" t="n">
+        <v>44</v>
+      </c>
+      <c r="S417" t="n">
+        <v>40</v>
+      </c>
+      <c r="T417" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U417" t="n">
+        <v>13</v>
+      </c>
+      <c r="V417" t="n">
+        <v>10</v>
+      </c>
+      <c r="W417" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X417" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y417" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:40:02</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="C418" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="D418" t="n">
+        <v>357</v>
+      </c>
+      <c r="E418" t="n">
+        <v>334</v>
+      </c>
+      <c r="F418" t="n">
+        <v>65</v>
+      </c>
+      <c r="G418" t="n">
+        <v>60</v>
+      </c>
+      <c r="H418" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="I418" t="n">
+        <v>141</v>
+      </c>
+      <c r="J418" t="n">
+        <v>130</v>
+      </c>
+      <c r="K418" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L418" t="n">
+        <v>48</v>
+      </c>
+      <c r="M418" t="n">
+        <v>44</v>
+      </c>
+      <c r="N418" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O418" t="n">
+        <v>189</v>
+      </c>
+      <c r="P418" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="R418" t="n">
+        <v>44</v>
+      </c>
+      <c r="S418" t="n">
+        <v>40</v>
+      </c>
+      <c r="T418" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U418" t="n">
+        <v>13</v>
+      </c>
+      <c r="V418" t="n">
+        <v>10</v>
+      </c>
+      <c r="W418" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X418" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y418" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:42:01</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="C419" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="D419" t="n">
+        <v>357</v>
+      </c>
+      <c r="E419" t="n">
+        <v>334</v>
+      </c>
+      <c r="F419" t="n">
+        <v>65</v>
+      </c>
+      <c r="G419" t="n">
+        <v>60</v>
+      </c>
+      <c r="H419" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="I419" t="n">
+        <v>141</v>
+      </c>
+      <c r="J419" t="n">
+        <v>130</v>
+      </c>
+      <c r="K419" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L419" t="n">
+        <v>48</v>
+      </c>
+      <c r="M419" t="n">
+        <v>44</v>
+      </c>
+      <c r="N419" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O419" t="n">
+        <v>189</v>
+      </c>
+      <c r="P419" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="R419" t="n">
+        <v>44</v>
+      </c>
+      <c r="S419" t="n">
+        <v>40</v>
+      </c>
+      <c r="T419" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U419" t="n">
+        <v>13</v>
+      </c>
+      <c r="V419" t="n">
+        <v>10</v>
+      </c>
+      <c r="W419" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X419" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y419" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:44:02</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="C420" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="D420" t="n">
+        <v>357</v>
+      </c>
+      <c r="E420" t="n">
+        <v>334</v>
+      </c>
+      <c r="F420" t="n">
+        <v>65</v>
+      </c>
+      <c r="G420" t="n">
+        <v>60</v>
+      </c>
+      <c r="H420" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="I420" t="n">
+        <v>141</v>
+      </c>
+      <c r="J420" t="n">
+        <v>130</v>
+      </c>
+      <c r="K420" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L420" t="n">
+        <v>48</v>
+      </c>
+      <c r="M420" t="n">
+        <v>44</v>
+      </c>
+      <c r="N420" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O420" t="n">
+        <v>189</v>
+      </c>
+      <c r="P420" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="R420" t="n">
+        <v>44</v>
+      </c>
+      <c r="S420" t="n">
+        <v>40</v>
+      </c>
+      <c r="T420" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U420" t="n">
+        <v>13</v>
+      </c>
+      <c r="V420" t="n">
+        <v>10</v>
+      </c>
+      <c r="W420" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X420" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:46:02</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="C421" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="D421" t="n">
+        <v>360</v>
+      </c>
+      <c r="E421" t="n">
+        <v>336</v>
+      </c>
+      <c r="F421" t="n">
+        <v>66</v>
+      </c>
+      <c r="G421" t="n">
+        <v>60</v>
+      </c>
+      <c r="H421" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="I421" t="n">
+        <v>144</v>
+      </c>
+      <c r="J421" t="n">
+        <v>132</v>
+      </c>
+      <c r="K421" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L421" t="n">
+        <v>48</v>
+      </c>
+      <c r="M421" t="n">
+        <v>44</v>
+      </c>
+      <c r="N421" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O421" t="n">
+        <v>189</v>
+      </c>
+      <c r="P421" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="R421" t="n">
+        <v>45</v>
+      </c>
+      <c r="S421" t="n">
+        <v>40</v>
+      </c>
+      <c r="T421" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U421" t="n">
+        <v>13</v>
+      </c>
+      <c r="V421" t="n">
+        <v>10</v>
+      </c>
+      <c r="W421" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X421" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y421" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:48:02</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="C422" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="D422" t="n">
+        <v>361</v>
+      </c>
+      <c r="E422" t="n">
+        <v>337</v>
+      </c>
+      <c r="F422" t="n">
+        <v>66</v>
+      </c>
+      <c r="G422" t="n">
+        <v>60</v>
+      </c>
+      <c r="H422" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I422" t="n">
+        <v>145</v>
+      </c>
+      <c r="J422" t="n">
+        <v>133</v>
+      </c>
+      <c r="K422" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L422" t="n">
+        <v>48</v>
+      </c>
+      <c r="M422" t="n">
+        <v>44</v>
+      </c>
+      <c r="N422" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O422" t="n">
+        <v>189</v>
+      </c>
+      <c r="P422" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="R422" t="n">
+        <v>45</v>
+      </c>
+      <c r="S422" t="n">
+        <v>40</v>
+      </c>
+      <c r="T422" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U422" t="n">
+        <v>13</v>
+      </c>
+      <c r="V422" t="n">
+        <v>10</v>
+      </c>
+      <c r="W422" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X422" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y422" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:50:01</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="C423" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="D423" t="n">
+        <v>362</v>
+      </c>
+      <c r="E423" t="n">
+        <v>338</v>
+      </c>
+      <c r="F423" t="n">
+        <v>67</v>
+      </c>
+      <c r="G423" t="n">
+        <v>61</v>
+      </c>
+      <c r="H423" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I423" t="n">
+        <v>145</v>
+      </c>
+      <c r="J423" t="n">
+        <v>133</v>
+      </c>
+      <c r="K423" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L423" t="n">
+        <v>48</v>
+      </c>
+      <c r="M423" t="n">
+        <v>44</v>
+      </c>
+      <c r="N423" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="O423" t="n">
+        <v>190</v>
+      </c>
+      <c r="P423" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="R423" t="n">
+        <v>46</v>
+      </c>
+      <c r="S423" t="n">
+        <v>41</v>
+      </c>
+      <c r="T423" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U423" t="n">
+        <v>13</v>
+      </c>
+      <c r="V423" t="n">
+        <v>10</v>
+      </c>
+      <c r="W423" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X423" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:52:01</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="C424" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="D424" t="n">
+        <v>363</v>
+      </c>
+      <c r="E424" t="n">
+        <v>339</v>
+      </c>
+      <c r="F424" t="n">
+        <v>67</v>
+      </c>
+      <c r="G424" t="n">
+        <v>61</v>
+      </c>
+      <c r="H424" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I424" t="n">
+        <v>146</v>
+      </c>
+      <c r="J424" t="n">
+        <v>134</v>
+      </c>
+      <c r="K424" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L424" t="n">
+        <v>48</v>
+      </c>
+      <c r="M424" t="n">
+        <v>44</v>
+      </c>
+      <c r="N424" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="O424" t="n">
+        <v>190</v>
+      </c>
+      <c r="P424" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="R424" t="n">
+        <v>46</v>
+      </c>
+      <c r="S424" t="n">
+        <v>41</v>
+      </c>
+      <c r="T424" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U424" t="n">
+        <v>13</v>
+      </c>
+      <c r="V424" t="n">
+        <v>10</v>
+      </c>
+      <c r="W424" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X424" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:54:02</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="C425" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="D425" t="n">
+        <v>362</v>
+      </c>
+      <c r="E425" t="n">
+        <v>338</v>
+      </c>
+      <c r="F425" t="n">
+        <v>67</v>
+      </c>
+      <c r="G425" t="n">
+        <v>61</v>
+      </c>
+      <c r="H425" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="I425" t="n">
+        <v>146</v>
+      </c>
+      <c r="J425" t="n">
+        <v>134</v>
+      </c>
+      <c r="K425" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="L425" t="n">
+        <v>48</v>
+      </c>
+      <c r="M425" t="n">
+        <v>44</v>
+      </c>
+      <c r="N425" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="O425" t="n">
+        <v>189</v>
+      </c>
+      <c r="P425" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="R425" t="n">
+        <v>46</v>
+      </c>
+      <c r="S425" t="n">
+        <v>41</v>
+      </c>
+      <c r="T425" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="U425" t="n">
+        <v>13</v>
+      </c>
+      <c r="V425" t="n">
+        <v>10</v>
+      </c>
+      <c r="W425" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X425" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y425" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:56:02</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="C426" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D426" t="n">
+        <v>364</v>
+      </c>
+      <c r="E426" t="n">
+        <v>340</v>
+      </c>
+      <c r="F426" t="n">
+        <v>68</v>
+      </c>
+      <c r="G426" t="n">
+        <v>62</v>
+      </c>
+      <c r="H426" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I426" t="n">
+        <v>147</v>
+      </c>
+      <c r="J426" t="n">
+        <v>135</v>
+      </c>
+      <c r="K426" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L426" t="n">
+        <v>49</v>
+      </c>
+      <c r="M426" t="n">
+        <v>45</v>
+      </c>
+      <c r="N426" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="O426" t="n">
+        <v>190</v>
+      </c>
+      <c r="P426" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R426" t="n">
+        <v>47</v>
+      </c>
+      <c r="S426" t="n">
+        <v>42</v>
+      </c>
+      <c r="T426" t="n">
+        <v>74</v>
+      </c>
+      <c r="U426" t="n">
+        <v>14</v>
+      </c>
+      <c r="V426" t="n">
+        <v>11</v>
+      </c>
+      <c r="W426" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X426" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y426" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:58:01</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="C427" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D427" t="n">
+        <v>364</v>
+      </c>
+      <c r="E427" t="n">
+        <v>340</v>
+      </c>
+      <c r="F427" t="n">
+        <v>68</v>
+      </c>
+      <c r="G427" t="n">
+        <v>62</v>
+      </c>
+      <c r="H427" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I427" t="n">
+        <v>147</v>
+      </c>
+      <c r="J427" t="n">
+        <v>135</v>
+      </c>
+      <c r="K427" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L427" t="n">
+        <v>49</v>
+      </c>
+      <c r="M427" t="n">
+        <v>45</v>
+      </c>
+      <c r="N427" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="O427" t="n">
+        <v>190</v>
+      </c>
+      <c r="P427" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R427" t="n">
+        <v>47</v>
+      </c>
+      <c r="S427" t="n">
+        <v>42</v>
+      </c>
+      <c r="T427" t="n">
+        <v>74</v>
+      </c>
+      <c r="U427" t="n">
+        <v>14</v>
+      </c>
+      <c r="V427" t="n">
+        <v>11</v>
+      </c>
+      <c r="W427" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X427" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y427" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:00:02</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="C428" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D428" t="n">
+        <v>365</v>
+      </c>
+      <c r="E428" t="n">
+        <v>341</v>
+      </c>
+      <c r="F428" t="n">
+        <v>68</v>
+      </c>
+      <c r="G428" t="n">
+        <v>62</v>
+      </c>
+      <c r="H428" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I428" t="n">
+        <v>148</v>
+      </c>
+      <c r="J428" t="n">
+        <v>136</v>
+      </c>
+      <c r="K428" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L428" t="n">
+        <v>49</v>
+      </c>
+      <c r="M428" t="n">
+        <v>45</v>
+      </c>
+      <c r="N428" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="O428" t="n">
+        <v>190</v>
+      </c>
+      <c r="P428" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R428" t="n">
+        <v>47</v>
+      </c>
+      <c r="S428" t="n">
+        <v>42</v>
+      </c>
+      <c r="T428" t="n">
+        <v>74</v>
+      </c>
+      <c r="U428" t="n">
+        <v>14</v>
+      </c>
+      <c r="V428" t="n">
+        <v>11</v>
+      </c>
+      <c r="W428" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X428" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y428" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:02:02</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>92.53</v>
+      </c>
+      <c r="C429" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D429" t="n">
+        <v>368</v>
+      </c>
+      <c r="E429" t="n">
+        <v>344</v>
+      </c>
+      <c r="F429" t="n">
+        <v>68</v>
+      </c>
+      <c r="G429" t="n">
+        <v>62</v>
+      </c>
+      <c r="H429" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I429" t="n">
+        <v>148</v>
+      </c>
+      <c r="J429" t="n">
+        <v>136</v>
+      </c>
+      <c r="K429" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L429" t="n">
+        <v>49</v>
+      </c>
+      <c r="M429" t="n">
+        <v>45</v>
+      </c>
+      <c r="N429" t="n">
+        <v>95.03</v>
+      </c>
+      <c r="O429" t="n">
+        <v>193</v>
+      </c>
+      <c r="P429" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R429" t="n">
+        <v>47</v>
+      </c>
+      <c r="S429" t="n">
+        <v>42</v>
+      </c>
+      <c r="T429" t="n">
+        <v>74</v>
+      </c>
+      <c r="U429" t="n">
+        <v>14</v>
+      </c>
+      <c r="V429" t="n">
+        <v>11</v>
+      </c>
+      <c r="W429" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X429" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y429" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:04:01</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C430" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D430" t="n">
+        <v>369</v>
+      </c>
+      <c r="E430" t="n">
+        <v>345</v>
+      </c>
+      <c r="F430" t="n">
+        <v>68</v>
+      </c>
+      <c r="G430" t="n">
+        <v>62</v>
+      </c>
+      <c r="H430" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I430" t="n">
+        <v>148</v>
+      </c>
+      <c r="J430" t="n">
+        <v>136</v>
+      </c>
+      <c r="K430" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L430" t="n">
+        <v>49</v>
+      </c>
+      <c r="M430" t="n">
+        <v>45</v>
+      </c>
+      <c r="N430" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="O430" t="n">
+        <v>194</v>
+      </c>
+      <c r="P430" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R430" t="n">
+        <v>47</v>
+      </c>
+      <c r="S430" t="n">
+        <v>42</v>
+      </c>
+      <c r="T430" t="n">
+        <v>74</v>
+      </c>
+      <c r="U430" t="n">
+        <v>14</v>
+      </c>
+      <c r="V430" t="n">
+        <v>11</v>
+      </c>
+      <c r="W430" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X430" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y430" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:06:02</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C431" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D431" t="n">
+        <v>370</v>
+      </c>
+      <c r="E431" t="n">
+        <v>346</v>
+      </c>
+      <c r="F431" t="n">
+        <v>68</v>
+      </c>
+      <c r="G431" t="n">
+        <v>62</v>
+      </c>
+      <c r="H431" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I431" t="n">
+        <v>148</v>
+      </c>
+      <c r="J431" t="n">
+        <v>136</v>
+      </c>
+      <c r="K431" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L431" t="n">
+        <v>50</v>
+      </c>
+      <c r="M431" t="n">
+        <v>46</v>
+      </c>
+      <c r="N431" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="O431" t="n">
+        <v>194</v>
+      </c>
+      <c r="P431" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R431" t="n">
+        <v>47</v>
+      </c>
+      <c r="S431" t="n">
+        <v>42</v>
+      </c>
+      <c r="T431" t="n">
+        <v>74</v>
+      </c>
+      <c r="U431" t="n">
+        <v>14</v>
+      </c>
+      <c r="V431" t="n">
+        <v>11</v>
+      </c>
+      <c r="W431" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X431" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y431" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:08:02</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C432" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D432" t="n">
+        <v>371</v>
+      </c>
+      <c r="E432" t="n">
+        <v>347</v>
+      </c>
+      <c r="F432" t="n">
+        <v>68</v>
+      </c>
+      <c r="G432" t="n">
+        <v>62</v>
+      </c>
+      <c r="H432" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I432" t="n">
+        <v>149</v>
+      </c>
+      <c r="J432" t="n">
+        <v>137</v>
+      </c>
+      <c r="K432" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L432" t="n">
+        <v>51</v>
+      </c>
+      <c r="M432" t="n">
+        <v>47</v>
+      </c>
+      <c r="N432" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="O432" t="n">
+        <v>194</v>
+      </c>
+      <c r="P432" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R432" t="n">
+        <v>47</v>
+      </c>
+      <c r="S432" t="n">
+        <v>42</v>
+      </c>
+      <c r="T432" t="n">
+        <v>74</v>
+      </c>
+      <c r="U432" t="n">
+        <v>14</v>
+      </c>
+      <c r="V432" t="n">
+        <v>11</v>
+      </c>
+      <c r="W432" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X432" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y432" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:10:01</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C433" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D433" t="n">
+        <v>371</v>
+      </c>
+      <c r="E433" t="n">
+        <v>347</v>
+      </c>
+      <c r="F433" t="n">
+        <v>68</v>
+      </c>
+      <c r="G433" t="n">
+        <v>62</v>
+      </c>
+      <c r="H433" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I433" t="n">
+        <v>149</v>
+      </c>
+      <c r="J433" t="n">
+        <v>137</v>
+      </c>
+      <c r="K433" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L433" t="n">
+        <v>51</v>
+      </c>
+      <c r="M433" t="n">
+        <v>47</v>
+      </c>
+      <c r="N433" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="O433" t="n">
+        <v>194</v>
+      </c>
+      <c r="P433" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R433" t="n">
+        <v>47</v>
+      </c>
+      <c r="S433" t="n">
+        <v>42</v>
+      </c>
+      <c r="T433" t="n">
+        <v>74</v>
+      </c>
+      <c r="U433" t="n">
+        <v>14</v>
+      </c>
+      <c r="V433" t="n">
+        <v>11</v>
+      </c>
+      <c r="W433" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X433" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y433" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-05-27 17:12:03</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="C434" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="D434" t="n">
+        <v>373</v>
+      </c>
+      <c r="E434" t="n">
+        <v>349</v>
+      </c>
+      <c r="F434" t="n">
+        <v>68</v>
+      </c>
+      <c r="G434" t="n">
+        <v>62</v>
+      </c>
+      <c r="H434" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="I434" t="n">
+        <v>151</v>
+      </c>
+      <c r="J434" t="n">
+        <v>139</v>
+      </c>
+      <c r="K434" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L434" t="n">
+        <v>52</v>
+      </c>
+      <c r="M434" t="n">
+        <v>48</v>
+      </c>
+      <c r="N434" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="O434" t="n">
+        <v>194</v>
+      </c>
+      <c r="P434" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="R434" t="n">
+        <v>47</v>
+      </c>
+      <c r="S434" t="n">
+        <v>42</v>
+      </c>
+      <c r="T434" t="n">
+        <v>74</v>
+      </c>
+      <c r="U434" t="n">
+        <v>14</v>
+      </c>
+      <c r="V434" t="n">
+        <v>11</v>
+      </c>
+      <c r="W434" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="X434" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:54:15</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>96.83</v>
+      </c>
+      <c r="C435" t="n">
+        <v>100</v>
+      </c>
+      <c r="D435" t="n">
+        <v>134</v>
+      </c>
+      <c r="E435" t="n">
+        <v>121</v>
+      </c>
+      <c r="F435" t="n">
+        <v>17</v>
+      </c>
+      <c r="G435" t="n">
+        <v>17</v>
+      </c>
+      <c r="H435" t="n">
+        <v>100</v>
+      </c>
+      <c r="I435" t="n">
+        <v>57</v>
+      </c>
+      <c r="J435" t="n">
+        <v>57</v>
+      </c>
+      <c r="K435" t="n">
+        <v>100</v>
+      </c>
+      <c r="L435" t="n">
+        <v>21</v>
+      </c>
+      <c r="M435" t="n">
+        <v>21</v>
+      </c>
+      <c r="N435" t="n">
+        <v>89.45999999999999</v>
+      </c>
+      <c r="O435" t="n">
+        <v>62</v>
+      </c>
+      <c r="P435" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>100</v>
+      </c>
+      <c r="R435" t="n">
+        <v>12</v>
+      </c>
+      <c r="S435" t="n">
+        <v>12</v>
+      </c>
+      <c r="T435" t="n">
+        <v>100</v>
+      </c>
+      <c r="U435" t="n">
+        <v>1</v>
+      </c>
+      <c r="V435" t="n">
+        <v>1</v>
+      </c>
+      <c r="W435" t="n">
+        <v>100</v>
+      </c>
+      <c r="X435" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:59:14</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="C436" t="n">
+        <v>100</v>
+      </c>
+      <c r="D436" t="n">
+        <v>136</v>
+      </c>
+      <c r="E436" t="n">
+        <v>123</v>
+      </c>
+      <c r="F436" t="n">
+        <v>18</v>
+      </c>
+      <c r="G436" t="n">
+        <v>18</v>
+      </c>
+      <c r="H436" t="n">
+        <v>100</v>
+      </c>
+      <c r="I436" t="n">
+        <v>58</v>
+      </c>
+      <c r="J436" t="n">
+        <v>58</v>
+      </c>
+      <c r="K436" t="n">
+        <v>100</v>
+      </c>
+      <c r="L436" t="n">
+        <v>21</v>
+      </c>
+      <c r="M436" t="n">
+        <v>21</v>
+      </c>
+      <c r="N436" t="n">
+        <v>88</v>
+      </c>
+      <c r="O436" t="n">
+        <v>63</v>
+      </c>
+      <c r="P436" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>100</v>
+      </c>
+      <c r="R436" t="n">
+        <v>13</v>
+      </c>
+      <c r="S436" t="n">
+        <v>13</v>
+      </c>
+      <c r="T436" t="n">
+        <v>100</v>
+      </c>
+      <c r="U436" t="n">
+        <v>1</v>
+      </c>
+      <c r="V436" t="n">
+        <v>1</v>
+      </c>
+      <c r="W436" t="n">
+        <v>100</v>
+      </c>
+      <c r="X436" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:01:14</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="C437" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D437" t="n">
+        <v>139</v>
+      </c>
+      <c r="E437" t="n">
+        <v>125</v>
+      </c>
+      <c r="F437" t="n">
+        <v>19</v>
+      </c>
+      <c r="G437" t="n">
+        <v>18</v>
+      </c>
+      <c r="H437" t="n">
+        <v>94</v>
+      </c>
+      <c r="I437" t="n">
+        <v>60</v>
+      </c>
+      <c r="J437" t="n">
+        <v>59</v>
+      </c>
+      <c r="K437" t="n">
+        <v>100</v>
+      </c>
+      <c r="L437" t="n">
+        <v>21</v>
+      </c>
+      <c r="M437" t="n">
+        <v>21</v>
+      </c>
+      <c r="N437" t="n">
+        <v>88</v>
+      </c>
+      <c r="O437" t="n">
+        <v>64</v>
+      </c>
+      <c r="P437" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R437" t="n">
+        <v>14</v>
+      </c>
+      <c r="S437" t="n">
+        <v>13</v>
+      </c>
+      <c r="T437" t="n">
+        <v>100</v>
+      </c>
+      <c r="U437" t="n">
+        <v>1</v>
+      </c>
+      <c r="V437" t="n">
+        <v>1</v>
+      </c>
+      <c r="W437" t="n">
+        <v>100</v>
+      </c>
+      <c r="X437" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:03:13</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="C438" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D438" t="n">
+        <v>139</v>
+      </c>
+      <c r="E438" t="n">
+        <v>125</v>
+      </c>
+      <c r="F438" t="n">
+        <v>19</v>
+      </c>
+      <c r="G438" t="n">
+        <v>18</v>
+      </c>
+      <c r="H438" t="n">
+        <v>94</v>
+      </c>
+      <c r="I438" t="n">
+        <v>60</v>
+      </c>
+      <c r="J438" t="n">
+        <v>59</v>
+      </c>
+      <c r="K438" t="n">
+        <v>100</v>
+      </c>
+      <c r="L438" t="n">
+        <v>21</v>
+      </c>
+      <c r="M438" t="n">
+        <v>21</v>
+      </c>
+      <c r="N438" t="n">
+        <v>88</v>
+      </c>
+      <c r="O438" t="n">
+        <v>64</v>
+      </c>
+      <c r="P438" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R438" t="n">
+        <v>14</v>
+      </c>
+      <c r="S438" t="n">
+        <v>13</v>
+      </c>
+      <c r="T438" t="n">
+        <v>100</v>
+      </c>
+      <c r="U438" t="n">
+        <v>1</v>
+      </c>
+      <c r="V438" t="n">
+        <v>1</v>
+      </c>
+      <c r="W438" t="n">
+        <v>100</v>
+      </c>
+      <c r="X438" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:04:46</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="C439" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D439" t="n">
+        <v>139</v>
+      </c>
+      <c r="E439" t="n">
+        <v>125</v>
+      </c>
+      <c r="F439" t="n">
+        <v>19</v>
+      </c>
+      <c r="G439" t="n">
+        <v>18</v>
+      </c>
+      <c r="H439" t="n">
+        <v>94</v>
+      </c>
+      <c r="I439" t="n">
+        <v>60</v>
+      </c>
+      <c r="J439" t="n">
+        <v>59</v>
+      </c>
+      <c r="K439" t="n">
+        <v>100</v>
+      </c>
+      <c r="L439" t="n">
+        <v>21</v>
+      </c>
+      <c r="M439" t="n">
+        <v>21</v>
+      </c>
+      <c r="N439" t="n">
+        <v>88</v>
+      </c>
+      <c r="O439" t="n">
+        <v>64</v>
+      </c>
+      <c r="P439" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R439" t="n">
+        <v>14</v>
+      </c>
+      <c r="S439" t="n">
+        <v>13</v>
+      </c>
+      <c r="T439" t="n">
+        <v>100</v>
+      </c>
+      <c r="U439" t="n">
+        <v>1</v>
+      </c>
+      <c r="V439" t="n">
+        <v>1</v>
+      </c>
+      <c r="W439" t="n">
+        <v>100</v>
+      </c>
+      <c r="X439" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:05:12</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="C440" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D440" t="n">
+        <v>139</v>
+      </c>
+      <c r="E440" t="n">
+        <v>125</v>
+      </c>
+      <c r="F440" t="n">
+        <v>19</v>
+      </c>
+      <c r="G440" t="n">
+        <v>18</v>
+      </c>
+      <c r="H440" t="n">
+        <v>94</v>
+      </c>
+      <c r="I440" t="n">
+        <v>60</v>
+      </c>
+      <c r="J440" t="n">
+        <v>59</v>
+      </c>
+      <c r="K440" t="n">
+        <v>100</v>
+      </c>
+      <c r="L440" t="n">
+        <v>21</v>
+      </c>
+      <c r="M440" t="n">
+        <v>21</v>
+      </c>
+      <c r="N440" t="n">
+        <v>88</v>
+      </c>
+      <c r="O440" t="n">
+        <v>64</v>
+      </c>
+      <c r="P440" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R440" t="n">
+        <v>14</v>
+      </c>
+      <c r="S440" t="n">
+        <v>13</v>
+      </c>
+      <c r="T440" t="n">
+        <v>100</v>
+      </c>
+      <c r="U440" t="n">
+        <v>1</v>
+      </c>
+      <c r="V440" t="n">
+        <v>1</v>
+      </c>
+      <c r="W440" t="n">
+        <v>100</v>
+      </c>
+      <c r="X440" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:07:14</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="C441" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D441" t="n">
+        <v>140</v>
+      </c>
+      <c r="E441" t="n">
+        <v>126</v>
+      </c>
+      <c r="F441" t="n">
+        <v>19</v>
+      </c>
+      <c r="G441" t="n">
+        <v>18</v>
+      </c>
+      <c r="H441" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I441" t="n">
+        <v>61</v>
+      </c>
+      <c r="J441" t="n">
+        <v>60</v>
+      </c>
+      <c r="K441" t="n">
+        <v>100</v>
+      </c>
+      <c r="L441" t="n">
+        <v>21</v>
+      </c>
+      <c r="M441" t="n">
+        <v>21</v>
+      </c>
+      <c r="N441" t="n">
+        <v>88</v>
+      </c>
+      <c r="O441" t="n">
+        <v>64</v>
+      </c>
+      <c r="P441" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R441" t="n">
+        <v>14</v>
+      </c>
+      <c r="S441" t="n">
+        <v>13</v>
+      </c>
+      <c r="T441" t="n">
+        <v>100</v>
+      </c>
+      <c r="U441" t="n">
+        <v>1</v>
+      </c>
+      <c r="V441" t="n">
+        <v>1</v>
+      </c>
+      <c r="W441" t="n">
+        <v>100</v>
+      </c>
+      <c r="X441" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:09:13</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="C442" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D442" t="n">
+        <v>142</v>
+      </c>
+      <c r="E442" t="n">
+        <v>127</v>
+      </c>
+      <c r="F442" t="n">
+        <v>19</v>
+      </c>
+      <c r="G442" t="n">
+        <v>18</v>
+      </c>
+      <c r="H442" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I442" t="n">
+        <v>62</v>
+      </c>
+      <c r="J442" t="n">
+        <v>61</v>
+      </c>
+      <c r="K442" t="n">
+        <v>100</v>
+      </c>
+      <c r="L442" t="n">
+        <v>21</v>
+      </c>
+      <c r="M442" t="n">
+        <v>21</v>
+      </c>
+      <c r="N442" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="O442" t="n">
+        <v>65</v>
+      </c>
+      <c r="P442" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R442" t="n">
+        <v>14</v>
+      </c>
+      <c r="S442" t="n">
+        <v>13</v>
+      </c>
+      <c r="T442" t="n">
+        <v>100</v>
+      </c>
+      <c r="U442" t="n">
+        <v>1</v>
+      </c>
+      <c r="V442" t="n">
+        <v>1</v>
+      </c>
+      <c r="W442" t="n">
+        <v>100</v>
+      </c>
+      <c r="X442" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:11:13</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="C443" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D443" t="n">
+        <v>143</v>
+      </c>
+      <c r="E443" t="n">
+        <v>128</v>
+      </c>
+      <c r="F443" t="n">
+        <v>19</v>
+      </c>
+      <c r="G443" t="n">
+        <v>18</v>
+      </c>
+      <c r="H443" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I443" t="n">
+        <v>63</v>
+      </c>
+      <c r="J443" t="n">
+        <v>62</v>
+      </c>
+      <c r="K443" t="n">
+        <v>100</v>
+      </c>
+      <c r="L443" t="n">
+        <v>21</v>
+      </c>
+      <c r="M443" t="n">
+        <v>21</v>
+      </c>
+      <c r="N443" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="O443" t="n">
+        <v>65</v>
+      </c>
+      <c r="P443" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R443" t="n">
+        <v>14</v>
+      </c>
+      <c r="S443" t="n">
+        <v>13</v>
+      </c>
+      <c r="T443" t="n">
+        <v>100</v>
+      </c>
+      <c r="U443" t="n">
+        <v>1</v>
+      </c>
+      <c r="V443" t="n">
+        <v>1</v>
+      </c>
+      <c r="W443" t="n">
+        <v>100</v>
+      </c>
+      <c r="X443" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:13:15</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="C444" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D444" t="n">
+        <v>143</v>
+      </c>
+      <c r="E444" t="n">
+        <v>128</v>
+      </c>
+      <c r="F444" t="n">
+        <v>19</v>
+      </c>
+      <c r="G444" t="n">
+        <v>18</v>
+      </c>
+      <c r="H444" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I444" t="n">
+        <v>63</v>
+      </c>
+      <c r="J444" t="n">
+        <v>62</v>
+      </c>
+      <c r="K444" t="n">
+        <v>100</v>
+      </c>
+      <c r="L444" t="n">
+        <v>21</v>
+      </c>
+      <c r="M444" t="n">
+        <v>21</v>
+      </c>
+      <c r="N444" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="O444" t="n">
+        <v>65</v>
+      </c>
+      <c r="P444" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R444" t="n">
+        <v>14</v>
+      </c>
+      <c r="S444" t="n">
+        <v>13</v>
+      </c>
+      <c r="T444" t="n">
+        <v>100</v>
+      </c>
+      <c r="U444" t="n">
+        <v>1</v>
+      </c>
+      <c r="V444" t="n">
+        <v>1</v>
+      </c>
+      <c r="W444" t="n">
+        <v>100</v>
+      </c>
+      <c r="X444" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:16:12</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="C445" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D445" t="n">
+        <v>146</v>
+      </c>
+      <c r="E445" t="n">
+        <v>129</v>
+      </c>
+      <c r="F445" t="n">
+        <v>19</v>
+      </c>
+      <c r="G445" t="n">
+        <v>18</v>
+      </c>
+      <c r="H445" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I445" t="n">
+        <v>63</v>
+      </c>
+      <c r="J445" t="n">
+        <v>62</v>
+      </c>
+      <c r="K445" t="n">
+        <v>100</v>
+      </c>
+      <c r="L445" t="n">
+        <v>21</v>
+      </c>
+      <c r="M445" t="n">
+        <v>21</v>
+      </c>
+      <c r="N445" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="O445" t="n">
+        <v>68</v>
+      </c>
+      <c r="P445" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R445" t="n">
+        <v>14</v>
+      </c>
+      <c r="S445" t="n">
+        <v>13</v>
+      </c>
+      <c r="T445" t="n">
+        <v>100</v>
+      </c>
+      <c r="U445" t="n">
+        <v>1</v>
+      </c>
+      <c r="V445" t="n">
+        <v>1</v>
+      </c>
+      <c r="W445" t="n">
+        <v>100</v>
+      </c>
+      <c r="X445" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:17:15</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="C446" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="D446" t="n">
+        <v>146</v>
+      </c>
+      <c r="E446" t="n">
+        <v>129</v>
+      </c>
+      <c r="F446" t="n">
+        <v>19</v>
+      </c>
+      <c r="G446" t="n">
+        <v>18</v>
+      </c>
+      <c r="H446" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I446" t="n">
+        <v>63</v>
+      </c>
+      <c r="J446" t="n">
+        <v>62</v>
+      </c>
+      <c r="K446" t="n">
+        <v>100</v>
+      </c>
+      <c r="L446" t="n">
+        <v>21</v>
+      </c>
+      <c r="M446" t="n">
+        <v>21</v>
+      </c>
+      <c r="N446" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="O446" t="n">
+        <v>68</v>
+      </c>
+      <c r="P446" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="R446" t="n">
+        <v>14</v>
+      </c>
+      <c r="S446" t="n">
+        <v>13</v>
+      </c>
+      <c r="T446" t="n">
+        <v>100</v>
+      </c>
+      <c r="U446" t="n">
+        <v>1</v>
+      </c>
+      <c r="V446" t="n">
+        <v>1</v>
+      </c>
+      <c r="W446" t="n">
+        <v>100</v>
+      </c>
+      <c r="X446" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:19:15</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="C447" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="D447" t="n">
+        <v>145</v>
+      </c>
+      <c r="E447" t="n">
+        <v>128</v>
+      </c>
+      <c r="F447" t="n">
+        <v>20</v>
+      </c>
+      <c r="G447" t="n">
+        <v>19</v>
+      </c>
+      <c r="H447" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I447" t="n">
+        <v>62</v>
+      </c>
+      <c r="J447" t="n">
+        <v>61</v>
+      </c>
+      <c r="K447" t="n">
+        <v>100</v>
+      </c>
+      <c r="L447" t="n">
+        <v>21</v>
+      </c>
+      <c r="M447" t="n">
+        <v>21</v>
+      </c>
+      <c r="N447" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="O447" t="n">
+        <v>68</v>
+      </c>
+      <c r="P447" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="R447" t="n">
+        <v>15</v>
+      </c>
+      <c r="S447" t="n">
+        <v>14</v>
+      </c>
+      <c r="T447" t="n">
+        <v>100</v>
+      </c>
+      <c r="U447" t="n">
+        <v>2</v>
+      </c>
+      <c r="V447" t="n">
+        <v>2</v>
+      </c>
+      <c r="W447" t="n">
+        <v>100</v>
+      </c>
+      <c r="X447" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:22:09</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="C448" t="n">
+        <v>95</v>
+      </c>
+      <c r="D448" t="n">
+        <v>147</v>
+      </c>
+      <c r="E448" t="n">
+        <v>130</v>
+      </c>
+      <c r="F448" t="n">
+        <v>21</v>
+      </c>
+      <c r="G448" t="n">
+        <v>20</v>
+      </c>
+      <c r="H448" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I448" t="n">
+        <v>62</v>
+      </c>
+      <c r="J448" t="n">
+        <v>61</v>
+      </c>
+      <c r="K448" t="n">
+        <v>100</v>
+      </c>
+      <c r="L448" t="n">
+        <v>22</v>
+      </c>
+      <c r="M448" t="n">
+        <v>22</v>
+      </c>
+      <c r="N448" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="O448" t="n">
+        <v>69</v>
+      </c>
+      <c r="P448" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="R448" t="n">
+        <v>15</v>
+      </c>
+      <c r="S448" t="n">
+        <v>14</v>
+      </c>
+      <c r="T448" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="U448" t="n">
+        <v>3</v>
+      </c>
+      <c r="V448" t="n">
+        <v>2</v>
+      </c>
+      <c r="W448" t="n">
+        <v>100</v>
+      </c>
+      <c r="X448" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:23:55</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="C449" t="n">
+        <v>95</v>
+      </c>
+      <c r="D449" t="n">
+        <v>148</v>
+      </c>
+      <c r="E449" t="n">
+        <v>131</v>
+      </c>
+      <c r="F449" t="n">
+        <v>21</v>
+      </c>
+      <c r="G449" t="n">
+        <v>20</v>
+      </c>
+      <c r="H449" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="I449" t="n">
+        <v>63</v>
+      </c>
+      <c r="J449" t="n">
+        <v>62</v>
+      </c>
+      <c r="K449" t="n">
+        <v>100</v>
+      </c>
+      <c r="L449" t="n">
+        <v>22</v>
+      </c>
+      <c r="M449" t="n">
+        <v>22</v>
+      </c>
+      <c r="N449" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="O449" t="n">
+        <v>69</v>
+      </c>
+      <c r="P449" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="R449" t="n">
+        <v>15</v>
+      </c>
+      <c r="S449" t="n">
+        <v>14</v>
+      </c>
+      <c r="T449" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="U449" t="n">
+        <v>3</v>
+      </c>
+      <c r="V449" t="n">
+        <v>2</v>
+      </c>
+      <c r="W449" t="n">
+        <v>100</v>
+      </c>
+      <c r="X449" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:26:19</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="C450" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D450" t="n">
+        <v>188</v>
+      </c>
+      <c r="E450" t="n">
+        <v>164</v>
+      </c>
+      <c r="F450" t="n">
+        <v>30</v>
+      </c>
+      <c r="G450" t="n">
+        <v>27</v>
+      </c>
+      <c r="H450" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I450" t="n">
+        <v>81</v>
+      </c>
+      <c r="J450" t="n">
+        <v>76</v>
+      </c>
+      <c r="K450" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L450" t="n">
+        <v>29</v>
+      </c>
+      <c r="M450" t="n">
+        <v>27</v>
+      </c>
+      <c r="N450" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="O450" t="n">
+        <v>88</v>
+      </c>
+      <c r="P450" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R450" t="n">
+        <v>23</v>
+      </c>
+      <c r="S450" t="n">
+        <v>20</v>
+      </c>
+      <c r="T450" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U450" t="n">
+        <v>6</v>
+      </c>
+      <c r="V450" t="n">
+        <v>3</v>
+      </c>
+      <c r="W450" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X450" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y450" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:28:20</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="C451" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D451" t="n">
+        <v>188</v>
+      </c>
+      <c r="E451" t="n">
+        <v>164</v>
+      </c>
+      <c r="F451" t="n">
+        <v>30</v>
+      </c>
+      <c r="G451" t="n">
+        <v>27</v>
+      </c>
+      <c r="H451" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I451" t="n">
+        <v>81</v>
+      </c>
+      <c r="J451" t="n">
+        <v>76</v>
+      </c>
+      <c r="K451" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L451" t="n">
+        <v>29</v>
+      </c>
+      <c r="M451" t="n">
+        <v>27</v>
+      </c>
+      <c r="N451" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="O451" t="n">
+        <v>88</v>
+      </c>
+      <c r="P451" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R451" t="n">
+        <v>23</v>
+      </c>
+      <c r="S451" t="n">
+        <v>20</v>
+      </c>
+      <c r="T451" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U451" t="n">
+        <v>6</v>
+      </c>
+      <c r="V451" t="n">
+        <v>3</v>
+      </c>
+      <c r="W451" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X451" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y451" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:30:19</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="C452" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D452" t="n">
+        <v>188</v>
+      </c>
+      <c r="E452" t="n">
+        <v>164</v>
+      </c>
+      <c r="F452" t="n">
+        <v>30</v>
+      </c>
+      <c r="G452" t="n">
+        <v>27</v>
+      </c>
+      <c r="H452" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I452" t="n">
+        <v>81</v>
+      </c>
+      <c r="J452" t="n">
+        <v>76</v>
+      </c>
+      <c r="K452" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L452" t="n">
+        <v>29</v>
+      </c>
+      <c r="M452" t="n">
+        <v>27</v>
+      </c>
+      <c r="N452" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="O452" t="n">
+        <v>88</v>
+      </c>
+      <c r="P452" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R452" t="n">
+        <v>23</v>
+      </c>
+      <c r="S452" t="n">
+        <v>20</v>
+      </c>
+      <c r="T452" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U452" t="n">
+        <v>6</v>
+      </c>
+      <c r="V452" t="n">
+        <v>3</v>
+      </c>
+      <c r="W452" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X452" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:30:59</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="C453" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D453" t="n">
+        <v>188</v>
+      </c>
+      <c r="E453" t="n">
+        <v>164</v>
+      </c>
+      <c r="F453" t="n">
+        <v>30</v>
+      </c>
+      <c r="G453" t="n">
+        <v>27</v>
+      </c>
+      <c r="H453" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I453" t="n">
+        <v>81</v>
+      </c>
+      <c r="J453" t="n">
+        <v>76</v>
+      </c>
+      <c r="K453" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L453" t="n">
+        <v>29</v>
+      </c>
+      <c r="M453" t="n">
+        <v>27</v>
+      </c>
+      <c r="N453" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="O453" t="n">
+        <v>88</v>
+      </c>
+      <c r="P453" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R453" t="n">
+        <v>23</v>
+      </c>
+      <c r="S453" t="n">
+        <v>20</v>
+      </c>
+      <c r="T453" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U453" t="n">
+        <v>6</v>
+      </c>
+      <c r="V453" t="n">
+        <v>3</v>
+      </c>
+      <c r="W453" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X453" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:31:09</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="C454" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D454" t="n">
+        <v>188</v>
+      </c>
+      <c r="E454" t="n">
+        <v>164</v>
+      </c>
+      <c r="F454" t="n">
+        <v>30</v>
+      </c>
+      <c r="G454" t="n">
+        <v>27</v>
+      </c>
+      <c r="H454" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I454" t="n">
+        <v>81</v>
+      </c>
+      <c r="J454" t="n">
+        <v>76</v>
+      </c>
+      <c r="K454" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L454" t="n">
+        <v>29</v>
+      </c>
+      <c r="M454" t="n">
+        <v>27</v>
+      </c>
+      <c r="N454" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="O454" t="n">
+        <v>88</v>
+      </c>
+      <c r="P454" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R454" t="n">
+        <v>23</v>
+      </c>
+      <c r="S454" t="n">
+        <v>20</v>
+      </c>
+      <c r="T454" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U454" t="n">
+        <v>6</v>
+      </c>
+      <c r="V454" t="n">
+        <v>3</v>
+      </c>
+      <c r="W454" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X454" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:32:20</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="C455" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D455" t="n">
+        <v>188</v>
+      </c>
+      <c r="E455" t="n">
+        <v>164</v>
+      </c>
+      <c r="F455" t="n">
+        <v>30</v>
+      </c>
+      <c r="G455" t="n">
+        <v>27</v>
+      </c>
+      <c r="H455" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I455" t="n">
+        <v>81</v>
+      </c>
+      <c r="J455" t="n">
+        <v>76</v>
+      </c>
+      <c r="K455" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L455" t="n">
+        <v>29</v>
+      </c>
+      <c r="M455" t="n">
+        <v>27</v>
+      </c>
+      <c r="N455" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="O455" t="n">
+        <v>88</v>
+      </c>
+      <c r="P455" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R455" t="n">
+        <v>23</v>
+      </c>
+      <c r="S455" t="n">
+        <v>20</v>
+      </c>
+      <c r="T455" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U455" t="n">
+        <v>6</v>
+      </c>
+      <c r="V455" t="n">
+        <v>3</v>
+      </c>
+      <c r="W455" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X455" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:33:50</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="C456" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D456" t="n">
+        <v>189</v>
+      </c>
+      <c r="E456" t="n">
+        <v>165</v>
+      </c>
+      <c r="F456" t="n">
+        <v>30</v>
+      </c>
+      <c r="G456" t="n">
+        <v>27</v>
+      </c>
+      <c r="H456" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I456" t="n">
+        <v>81</v>
+      </c>
+      <c r="J456" t="n">
+        <v>76</v>
+      </c>
+      <c r="K456" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L456" t="n">
+        <v>29</v>
+      </c>
+      <c r="M456" t="n">
+        <v>27</v>
+      </c>
+      <c r="N456" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="O456" t="n">
+        <v>89</v>
+      </c>
+      <c r="P456" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R456" t="n">
+        <v>23</v>
+      </c>
+      <c r="S456" t="n">
+        <v>20</v>
+      </c>
+      <c r="T456" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U456" t="n">
+        <v>6</v>
+      </c>
+      <c r="V456" t="n">
+        <v>3</v>
+      </c>
+      <c r="W456" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X456" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:35:50</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="C457" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D457" t="n">
+        <v>189</v>
+      </c>
+      <c r="E457" t="n">
+        <v>165</v>
+      </c>
+      <c r="F457" t="n">
+        <v>30</v>
+      </c>
+      <c r="G457" t="n">
+        <v>27</v>
+      </c>
+      <c r="H457" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I457" t="n">
+        <v>81</v>
+      </c>
+      <c r="J457" t="n">
+        <v>76</v>
+      </c>
+      <c r="K457" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L457" t="n">
+        <v>29</v>
+      </c>
+      <c r="M457" t="n">
+        <v>27</v>
+      </c>
+      <c r="N457" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="O457" t="n">
+        <v>89</v>
+      </c>
+      <c r="P457" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R457" t="n">
+        <v>23</v>
+      </c>
+      <c r="S457" t="n">
+        <v>20</v>
+      </c>
+      <c r="T457" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U457" t="n">
+        <v>6</v>
+      </c>
+      <c r="V457" t="n">
+        <v>3</v>
+      </c>
+      <c r="W457" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X457" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:37:50</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="C458" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D458" t="n">
+        <v>189</v>
+      </c>
+      <c r="E458" t="n">
+        <v>165</v>
+      </c>
+      <c r="F458" t="n">
+        <v>30</v>
+      </c>
+      <c r="G458" t="n">
+        <v>27</v>
+      </c>
+      <c r="H458" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I458" t="n">
+        <v>81</v>
+      </c>
+      <c r="J458" t="n">
+        <v>76</v>
+      </c>
+      <c r="K458" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L458" t="n">
+        <v>29</v>
+      </c>
+      <c r="M458" t="n">
+        <v>27</v>
+      </c>
+      <c r="N458" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="O458" t="n">
+        <v>89</v>
+      </c>
+      <c r="P458" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R458" t="n">
+        <v>23</v>
+      </c>
+      <c r="S458" t="n">
+        <v>20</v>
+      </c>
+      <c r="T458" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U458" t="n">
+        <v>6</v>
+      </c>
+      <c r="V458" t="n">
+        <v>3</v>
+      </c>
+      <c r="W458" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X458" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:39:50</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="C459" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D459" t="n">
+        <v>189</v>
+      </c>
+      <c r="E459" t="n">
+        <v>165</v>
+      </c>
+      <c r="F459" t="n">
+        <v>30</v>
+      </c>
+      <c r="G459" t="n">
+        <v>27</v>
+      </c>
+      <c r="H459" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I459" t="n">
+        <v>81</v>
+      </c>
+      <c r="J459" t="n">
+        <v>76</v>
+      </c>
+      <c r="K459" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L459" t="n">
+        <v>29</v>
+      </c>
+      <c r="M459" t="n">
+        <v>27</v>
+      </c>
+      <c r="N459" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="O459" t="n">
+        <v>89</v>
+      </c>
+      <c r="P459" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R459" t="n">
+        <v>23</v>
+      </c>
+      <c r="S459" t="n">
+        <v>20</v>
+      </c>
+      <c r="T459" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U459" t="n">
+        <v>6</v>
+      </c>
+      <c r="V459" t="n">
+        <v>3</v>
+      </c>
+      <c r="W459" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X459" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:41:50</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="C460" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D460" t="n">
+        <v>189</v>
+      </c>
+      <c r="E460" t="n">
+        <v>165</v>
+      </c>
+      <c r="F460" t="n">
+        <v>30</v>
+      </c>
+      <c r="G460" t="n">
+        <v>27</v>
+      </c>
+      <c r="H460" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I460" t="n">
+        <v>81</v>
+      </c>
+      <c r="J460" t="n">
+        <v>76</v>
+      </c>
+      <c r="K460" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L460" t="n">
+        <v>29</v>
+      </c>
+      <c r="M460" t="n">
+        <v>27</v>
+      </c>
+      <c r="N460" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="O460" t="n">
+        <v>89</v>
+      </c>
+      <c r="P460" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R460" t="n">
+        <v>23</v>
+      </c>
+      <c r="S460" t="n">
+        <v>20</v>
+      </c>
+      <c r="T460" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U460" t="n">
+        <v>6</v>
+      </c>
+      <c r="V460" t="n">
+        <v>3</v>
+      </c>
+      <c r="W460" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X460" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:43:50</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>89.81</v>
+      </c>
+      <c r="C461" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="D461" t="n">
+        <v>190</v>
+      </c>
+      <c r="E461" t="n">
+        <v>166</v>
+      </c>
+      <c r="F461" t="n">
+        <v>30</v>
+      </c>
+      <c r="G461" t="n">
+        <v>27</v>
+      </c>
+      <c r="H461" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="I461" t="n">
+        <v>81</v>
+      </c>
+      <c r="J461" t="n">
+        <v>76</v>
+      </c>
+      <c r="K461" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L461" t="n">
+        <v>29</v>
+      </c>
+      <c r="M461" t="n">
+        <v>27</v>
+      </c>
+      <c r="N461" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="O461" t="n">
+        <v>90</v>
+      </c>
+      <c r="P461" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="R461" t="n">
+        <v>23</v>
+      </c>
+      <c r="S461" t="n">
+        <v>20</v>
+      </c>
+      <c r="T461" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U461" t="n">
+        <v>6</v>
+      </c>
+      <c r="V461" t="n">
+        <v>3</v>
+      </c>
+      <c r="W461" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X461" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:45:51</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="C462" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="D462" t="n">
+        <v>191</v>
+      </c>
+      <c r="E462" t="n">
+        <v>167</v>
+      </c>
+      <c r="F462" t="n">
+        <v>31</v>
+      </c>
+      <c r="G462" t="n">
+        <v>28</v>
+      </c>
+      <c r="H462" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="I462" t="n">
+        <v>82</v>
+      </c>
+      <c r="J462" t="n">
+        <v>77</v>
+      </c>
+      <c r="K462" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L462" t="n">
+        <v>29</v>
+      </c>
+      <c r="M462" t="n">
+        <v>27</v>
+      </c>
+      <c r="N462" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="O462" t="n">
+        <v>90</v>
+      </c>
+      <c r="P462" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="R462" t="n">
+        <v>24</v>
+      </c>
+      <c r="S462" t="n">
+        <v>21</v>
+      </c>
+      <c r="T462" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U462" t="n">
+        <v>6</v>
+      </c>
+      <c r="V462" t="n">
+        <v>3</v>
+      </c>
+      <c r="W462" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X462" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y462" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:47:51</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="C463" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="D463" t="n">
+        <v>191</v>
+      </c>
+      <c r="E463" t="n">
+        <v>167</v>
+      </c>
+      <c r="F463" t="n">
+        <v>31</v>
+      </c>
+      <c r="G463" t="n">
+        <v>28</v>
+      </c>
+      <c r="H463" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="I463" t="n">
+        <v>82</v>
+      </c>
+      <c r="J463" t="n">
+        <v>77</v>
+      </c>
+      <c r="K463" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L463" t="n">
+        <v>29</v>
+      </c>
+      <c r="M463" t="n">
+        <v>27</v>
+      </c>
+      <c r="N463" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="O463" t="n">
+        <v>90</v>
+      </c>
+      <c r="P463" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="R463" t="n">
+        <v>24</v>
+      </c>
+      <c r="S463" t="n">
+        <v>21</v>
+      </c>
+      <c r="T463" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U463" t="n">
+        <v>6</v>
+      </c>
+      <c r="V463" t="n">
+        <v>3</v>
+      </c>
+      <c r="W463" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X463" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y463" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:49:50</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="C464" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D464" t="n">
+        <v>195</v>
+      </c>
+      <c r="E464" t="n">
+        <v>169</v>
+      </c>
+      <c r="F464" t="n">
+        <v>32</v>
+      </c>
+      <c r="G464" t="n">
+        <v>29</v>
+      </c>
+      <c r="H464" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I464" t="n">
+        <v>83</v>
+      </c>
+      <c r="J464" t="n">
+        <v>78</v>
+      </c>
+      <c r="K464" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L464" t="n">
+        <v>29</v>
+      </c>
+      <c r="M464" t="n">
+        <v>27</v>
+      </c>
+      <c r="N464" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="O464" t="n">
+        <v>93</v>
+      </c>
+      <c r="P464" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R464" t="n">
+        <v>25</v>
+      </c>
+      <c r="S464" t="n">
+        <v>22</v>
+      </c>
+      <c r="T464" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U464" t="n">
+        <v>6</v>
+      </c>
+      <c r="V464" t="n">
+        <v>3</v>
+      </c>
+      <c r="W464" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X464" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:51:51</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="C465" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D465" t="n">
+        <v>195</v>
+      </c>
+      <c r="E465" t="n">
+        <v>169</v>
+      </c>
+      <c r="F465" t="n">
+        <v>32</v>
+      </c>
+      <c r="G465" t="n">
+        <v>29</v>
+      </c>
+      <c r="H465" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I465" t="n">
+        <v>83</v>
+      </c>
+      <c r="J465" t="n">
+        <v>78</v>
+      </c>
+      <c r="K465" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L465" t="n">
+        <v>29</v>
+      </c>
+      <c r="M465" t="n">
+        <v>27</v>
+      </c>
+      <c r="N465" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="O465" t="n">
+        <v>93</v>
+      </c>
+      <c r="P465" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R465" t="n">
+        <v>25</v>
+      </c>
+      <c r="S465" t="n">
+        <v>22</v>
+      </c>
+      <c r="T465" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U465" t="n">
+        <v>6</v>
+      </c>
+      <c r="V465" t="n">
+        <v>3</v>
+      </c>
+      <c r="W465" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X465" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:53:50</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="C466" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D466" t="n">
+        <v>197</v>
+      </c>
+      <c r="E466" t="n">
+        <v>171</v>
+      </c>
+      <c r="F466" t="n">
+        <v>32</v>
+      </c>
+      <c r="G466" t="n">
+        <v>29</v>
+      </c>
+      <c r="H466" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I466" t="n">
+        <v>83</v>
+      </c>
+      <c r="J466" t="n">
+        <v>78</v>
+      </c>
+      <c r="K466" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L466" t="n">
+        <v>29</v>
+      </c>
+      <c r="M466" t="n">
+        <v>27</v>
+      </c>
+      <c r="N466" t="n">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="O466" t="n">
+        <v>95</v>
+      </c>
+      <c r="P466" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R466" t="n">
+        <v>25</v>
+      </c>
+      <c r="S466" t="n">
+        <v>22</v>
+      </c>
+      <c r="T466" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U466" t="n">
+        <v>6</v>
+      </c>
+      <c r="V466" t="n">
+        <v>3</v>
+      </c>
+      <c r="W466" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X466" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y466" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:55:50</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="C467" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D467" t="n">
+        <v>198</v>
+      </c>
+      <c r="E467" t="n">
+        <v>171</v>
+      </c>
+      <c r="F467" t="n">
+        <v>32</v>
+      </c>
+      <c r="G467" t="n">
+        <v>29</v>
+      </c>
+      <c r="H467" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I467" t="n">
+        <v>83</v>
+      </c>
+      <c r="J467" t="n">
+        <v>78</v>
+      </c>
+      <c r="K467" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L467" t="n">
+        <v>29</v>
+      </c>
+      <c r="M467" t="n">
+        <v>27</v>
+      </c>
+      <c r="N467" t="n">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="O467" t="n">
+        <v>96</v>
+      </c>
+      <c r="P467" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R467" t="n">
+        <v>25</v>
+      </c>
+      <c r="S467" t="n">
+        <v>22</v>
+      </c>
+      <c r="T467" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U467" t="n">
+        <v>6</v>
+      </c>
+      <c r="V467" t="n">
+        <v>3</v>
+      </c>
+      <c r="W467" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X467" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y467" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:57:50</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="C468" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D468" t="n">
+        <v>199</v>
+      </c>
+      <c r="E468" t="n">
+        <v>172</v>
+      </c>
+      <c r="F468" t="n">
+        <v>32</v>
+      </c>
+      <c r="G468" t="n">
+        <v>29</v>
+      </c>
+      <c r="H468" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I468" t="n">
+        <v>84</v>
+      </c>
+      <c r="J468" t="n">
+        <v>79</v>
+      </c>
+      <c r="K468" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L468" t="n">
+        <v>29</v>
+      </c>
+      <c r="M468" t="n">
+        <v>27</v>
+      </c>
+      <c r="N468" t="n">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="O468" t="n">
+        <v>96</v>
+      </c>
+      <c r="P468" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R468" t="n">
+        <v>25</v>
+      </c>
+      <c r="S468" t="n">
+        <v>22</v>
+      </c>
+      <c r="T468" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U468" t="n">
+        <v>6</v>
+      </c>
+      <c r="V468" t="n">
+        <v>3</v>
+      </c>
+      <c r="W468" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X468" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y468" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:59:50</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="C469" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D469" t="n">
+        <v>199</v>
+      </c>
+      <c r="E469" t="n">
+        <v>172</v>
+      </c>
+      <c r="F469" t="n">
+        <v>32</v>
+      </c>
+      <c r="G469" t="n">
+        <v>29</v>
+      </c>
+      <c r="H469" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I469" t="n">
+        <v>84</v>
+      </c>
+      <c r="J469" t="n">
+        <v>79</v>
+      </c>
+      <c r="K469" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="L469" t="n">
+        <v>29</v>
+      </c>
+      <c r="M469" t="n">
+        <v>27</v>
+      </c>
+      <c r="N469" t="n">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="O469" t="n">
+        <v>96</v>
+      </c>
+      <c r="P469" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R469" t="n">
+        <v>25</v>
+      </c>
+      <c r="S469" t="n">
+        <v>22</v>
+      </c>
+      <c r="T469" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U469" t="n">
+        <v>6</v>
+      </c>
+      <c r="V469" t="n">
+        <v>3</v>
+      </c>
+      <c r="W469" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X469" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y469" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:01:36</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C470" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D470" t="n">
+        <v>201</v>
+      </c>
+      <c r="E470" t="n">
+        <v>174</v>
+      </c>
+      <c r="F470" t="n">
+        <v>32</v>
+      </c>
+      <c r="G470" t="n">
+        <v>29</v>
+      </c>
+      <c r="H470" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I470" t="n">
+        <v>84</v>
+      </c>
+      <c r="J470" t="n">
+        <v>79</v>
+      </c>
+      <c r="K470" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="L470" t="n">
+        <v>30</v>
+      </c>
+      <c r="M470" t="n">
+        <v>28</v>
+      </c>
+      <c r="N470" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="O470" t="n">
+        <v>97</v>
+      </c>
+      <c r="P470" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R470" t="n">
+        <v>25</v>
+      </c>
+      <c r="S470" t="n">
+        <v>22</v>
+      </c>
+      <c r="T470" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U470" t="n">
+        <v>6</v>
+      </c>
+      <c r="V470" t="n">
+        <v>3</v>
+      </c>
+      <c r="W470" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X470" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y470" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:01:50</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C471" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D471" t="n">
+        <v>201</v>
+      </c>
+      <c r="E471" t="n">
+        <v>174</v>
+      </c>
+      <c r="F471" t="n">
+        <v>32</v>
+      </c>
+      <c r="G471" t="n">
+        <v>29</v>
+      </c>
+      <c r="H471" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I471" t="n">
+        <v>84</v>
+      </c>
+      <c r="J471" t="n">
+        <v>79</v>
+      </c>
+      <c r="K471" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="L471" t="n">
+        <v>30</v>
+      </c>
+      <c r="M471" t="n">
+        <v>28</v>
+      </c>
+      <c r="N471" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="O471" t="n">
+        <v>97</v>
+      </c>
+      <c r="P471" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R471" t="n">
+        <v>25</v>
+      </c>
+      <c r="S471" t="n">
+        <v>22</v>
+      </c>
+      <c r="T471" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U471" t="n">
+        <v>6</v>
+      </c>
+      <c r="V471" t="n">
+        <v>3</v>
+      </c>
+      <c r="W471" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X471" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y471" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:03:50</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C472" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D472" t="n">
+        <v>201</v>
+      </c>
+      <c r="E472" t="n">
+        <v>174</v>
+      </c>
+      <c r="F472" t="n">
+        <v>32</v>
+      </c>
+      <c r="G472" t="n">
+        <v>29</v>
+      </c>
+      <c r="H472" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I472" t="n">
+        <v>84</v>
+      </c>
+      <c r="J472" t="n">
+        <v>79</v>
+      </c>
+      <c r="K472" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="L472" t="n">
+        <v>30</v>
+      </c>
+      <c r="M472" t="n">
+        <v>28</v>
+      </c>
+      <c r="N472" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="O472" t="n">
+        <v>97</v>
+      </c>
+      <c r="P472" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R472" t="n">
+        <v>25</v>
+      </c>
+      <c r="S472" t="n">
+        <v>22</v>
+      </c>
+      <c r="T472" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U472" t="n">
+        <v>6</v>
+      </c>
+      <c r="V472" t="n">
+        <v>3</v>
+      </c>
+      <c r="W472" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X472" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:05:42</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C473" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D473" t="n">
+        <v>201</v>
+      </c>
+      <c r="E473" t="n">
+        <v>174</v>
+      </c>
+      <c r="F473" t="n">
+        <v>32</v>
+      </c>
+      <c r="G473" t="n">
+        <v>29</v>
+      </c>
+      <c r="H473" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I473" t="n">
+        <v>84</v>
+      </c>
+      <c r="J473" t="n">
+        <v>79</v>
+      </c>
+      <c r="K473" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="L473" t="n">
+        <v>30</v>
+      </c>
+      <c r="M473" t="n">
+        <v>28</v>
+      </c>
+      <c r="N473" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="O473" t="n">
+        <v>97</v>
+      </c>
+      <c r="P473" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R473" t="n">
+        <v>25</v>
+      </c>
+      <c r="S473" t="n">
+        <v>22</v>
+      </c>
+      <c r="T473" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U473" t="n">
+        <v>6</v>
+      </c>
+      <c r="V473" t="n">
+        <v>3</v>
+      </c>
+      <c r="W473" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X473" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y473" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:05:51</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="C474" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D474" t="n">
+        <v>201</v>
+      </c>
+      <c r="E474" t="n">
+        <v>174</v>
+      </c>
+      <c r="F474" t="n">
+        <v>32</v>
+      </c>
+      <c r="G474" t="n">
+        <v>29</v>
+      </c>
+      <c r="H474" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="I474" t="n">
+        <v>84</v>
+      </c>
+      <c r="J474" t="n">
+        <v>79</v>
+      </c>
+      <c r="K474" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="L474" t="n">
+        <v>30</v>
+      </c>
+      <c r="M474" t="n">
+        <v>28</v>
+      </c>
+      <c r="N474" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="O474" t="n">
+        <v>97</v>
+      </c>
+      <c r="P474" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="R474" t="n">
+        <v>25</v>
+      </c>
+      <c r="S474" t="n">
+        <v>22</v>
+      </c>
+      <c r="T474" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="U474" t="n">
+        <v>6</v>
+      </c>
+      <c r="V474" t="n">
+        <v>3</v>
+      </c>
+      <c r="W474" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="X474" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
